--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>1.41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
@@ -890,7 +890,7 @@
         <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
         <v>7</v>
@@ -1652,7 +1652,7 @@
         <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.5</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -2372,28 +2372,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="G8" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.7</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -2626,50 +2626,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.8</v>
       </c>
-      <c r="H9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,61 +2880,61 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.81</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2943,176 +2943,176 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -3129,66 +3129,66 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="U11" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -3197,176 +3197,430 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN11" t="n">
         <v>32</v>
       </c>
-      <c r="AA11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AT11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY11" t="n">
         <v>16</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-17 04:40:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="n">
         <v>32</v>
       </c>
-      <c r="BB11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD12" t="n">
         <v>25</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BE12" t="n">
         <v>29</v>
       </c>
-      <c r="BF11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH11" t="n">
+      <c r="BF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH12" t="n">
         <v>1000</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BI12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BJ12" t="n">
         <v>1000</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BK12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BL12" t="n">
         <v>1000</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BM12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BN12" t="n">
         <v>1000</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BO12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BP12" t="n">
         <v>1000</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="BR12" t="n">
         <v>1000</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="BS12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="BT12" t="n">
         <v>1000</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="BU12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="BV12" t="n">
         <v>1000</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="BW12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="BX12" t="n">
         <v>1000</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="BY12" t="n">
         <v>1.04</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="BZ12" t="n">
         <v>1000</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CA12" t="n">
         <v>1.04</v>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-05-17 02:09:00</t>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -860,7 +860,7 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H2" t="n">
         <v>8.800000000000001</v>
@@ -869,7 +869,7 @@
         <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
@@ -890,7 +890,7 @@
         <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
         <v>2.94</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
         <v>1.77</v>
@@ -2136,7 +2136,7 @@
         <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
         <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
         <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.85</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>1.79</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
         <v>4.5</v>
@@ -3179,7 +3179,7 @@
         <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S11" t="n">
         <v>2.26</v>
@@ -3203,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA11" t="n">
         <v>23</v>
@@ -3218,13 +3218,13 @@
         <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF11" t="n">
         <v>42</v>
       </c>
       <c r="AG11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
@@ -3239,7 +3239,7 @@
         <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>55</v>
@@ -3263,13 +3263,13 @@
         <v>18.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AU11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
         <v>14</v>
@@ -3293,13 +3293,13 @@
         <v>36</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BG11" t="n">
         <v>6.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
         <v>3.7</v>
@@ -3412,7 +3412,7 @@
         <v>3.85</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
         <v>42</v>
@@ -3544,83 +3544,83 @@
         <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
         <v>29</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
         <v>19</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 04:40:06</t>
+          <t>2026-05-17 07:11:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,237 +857,237 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I2" t="n">
-        <v>870</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
         <v>5.6</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU3" t="n">
         <v>4.2</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Shanghai Port FC</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X5" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.6</v>
       </c>
-      <c r="G5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
         <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.66</v>
+        <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.91</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,33 +3129,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>4.6</v>
+        <v>1.74</v>
       </c>
       <c r="H11" t="n">
-        <v>1.79</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.81</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>4.5</v>
@@ -3164,31 +3164,31 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -3197,430 +3197,1446 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BZ11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Westerlo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Charleroi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Oud-Heverlee Leuven</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Genk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Antwerp</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>English Premier League</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Man City</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Tottenham</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F16" t="n">
         <v>2.08</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="G16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H16" t="n">
         <v>3.7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I16" t="n">
         <v>3.75</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J16" t="n">
         <v>3.85</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K16" t="n">
         <v>3.9</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1.04</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N16" t="n">
         <v>5.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O16" t="n">
         <v>1.22</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P16" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q16" t="n">
         <v>1.67</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R16" t="n">
         <v>1.57</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S16" t="n">
         <v>2.64</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T16" t="n">
         <v>1.59</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U16" t="n">
         <v>2.56</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>23</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y16" t="n">
         <v>19</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z16" t="n">
         <v>32</v>
       </c>
-      <c r="AA12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AA16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE16" t="n">
         <v>40</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AF16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AG16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AH16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AI16" t="n">
         <v>42</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AJ16" t="n">
         <v>26</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK16" t="n">
         <v>20</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AL16" t="n">
         <v>32</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AM16" t="n">
         <v>60</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AN16" t="n">
         <v>11</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AO16" t="n">
         <v>30</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AP16" t="n">
         <v>19</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AR12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AR16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA16" t="n">
         <v>32</v>
       </c>
-      <c r="AT12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BB16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV16" t="n">
         <v>32</v>
       </c>
-      <c r="BB12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>100</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW12" t="n">
+      <c r="BW16" t="n">
         <v>4.1</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="BX16" t="n">
         <v>38</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="BY16" t="n">
         <v>4.2</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="BZ16" t="n">
         <v>21</v>
       </c>
-      <c r="CA12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-05-17 07:11:33</t>
+      <c r="CA16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -878,7 +878,7 @@
         <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
         <v>5.8</v>
@@ -890,19 +890,19 @@
         <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
         <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
@@ -965,13 +965,13 @@
         <v>210</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
@@ -983,10 +983,10 @@
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
         <v>8.4</v>
@@ -1007,16 +1007,16 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>1.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>3.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>130</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
@@ -1028,13 +1028,13 @@
         <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL2" t="n">
         <v>140</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BN2" t="n">
         <v>4.5</v>
@@ -1052,35 +1052,35 @@
         <v>24</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT2" t="n">
         <v>16</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
         <v>95</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX2" t="n">
         <v>80</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2" t="n">
         <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
         <v>3.1</v>
@@ -1144,16 +1144,16 @@
         <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
         <v>1.86</v>
@@ -1219,10 +1219,10 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
         <v>12</v>
@@ -1231,13 +1231,13 @@
         <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
         <v>4.4</v>
@@ -1249,7 +1249,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
         <v>4.6</v>
@@ -1282,13 +1282,13 @@
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL3" t="n">
         <v>170</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN3" t="n">
         <v>7.2</v>
@@ -1300,13 +1300,13 @@
         <v>32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR3" t="n">
         <v>50</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT3" t="n">
         <v>6.2</v>
@@ -1318,23 +1318,23 @@
         <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ3" t="n">
         <v>40</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.58</v>
       </c>
       <c r="I4" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1383,7 +1383,7 @@
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1395,10 +1395,10 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -1407,16 +1407,16 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1536,13 +1536,13 @@
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BL4" t="n">
         <v>140</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN4" t="n">
         <v>7.2</v>
@@ -1554,13 +1554,13 @@
         <v>27</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR4" t="n">
         <v>40</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT4" t="n">
         <v>6.8</v>
@@ -1572,23 +1572,23 @@
         <v>24</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BX4" t="n">
         <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1637,10 +1637,10 @@
         <v>5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
         <v>6.2</v>
@@ -1649,22 +1649,22 @@
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.54</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
@@ -1685,7 +1685,7 @@
         <v>190</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
         <v>15</v>
@@ -1709,7 +1709,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>18</v>
@@ -1727,13 +1727,13 @@
         <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
         <v>4.3</v>
@@ -1748,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1769,7 +1769,7 @@
         <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
         <v>4.2</v>
@@ -1778,7 +1778,7 @@
         <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>5.7</v>
@@ -1790,13 +1790,13 @@
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL5" t="n">
         <v>100</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN5" t="n">
         <v>5.3</v>
@@ -1808,41 +1808,41 @@
         <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BR5" t="n">
         <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BT5" t="n">
         <v>12.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV5" t="n">
         <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX5" t="n">
         <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5" t="n">
         <v>13.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>2.08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
@@ -1897,19 +1897,19 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
         <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
         <v>3.2</v>
@@ -1918,10 +1918,10 @@
         <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
         <v>1.33</v>
@@ -1954,7 +1954,7 @@
         <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>19.5</v>
@@ -1963,10 +1963,10 @@
         <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="n">
         <v>60</v>
@@ -1981,10 +1981,10 @@
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>10.5</v>
@@ -1996,13 +1996,13 @@
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>21</v>
@@ -2011,25 +2011,25 @@
         <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
         <v>12</v>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2062,13 +2062,13 @@
         <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2080,23 +2080,23 @@
         <v>18</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ6" t="n">
         <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>7</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
         <v>1.39</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2922,7 +2922,7 @@
         <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -3430,7 +3430,7 @@
         <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.9</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
         <v>1.73</v>
@@ -3914,7 +3914,7 @@
         <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -4171,10 +4171,10 @@
         <v>1.81</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>2.26</v>
       </c>
       <c r="T15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4219,13 +4219,13 @@
         <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AB15" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AC15" t="n">
         <v>11</v>
@@ -4234,28 +4234,28 @@
         <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH15" t="n">
         <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ15" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AK15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>55</v>
@@ -4267,7 +4267,7 @@
         <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AQ15" t="n">
         <v>13.5</v>
@@ -4279,10 +4279,10 @@
         <v>18.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV15" t="n">
         <v>9.4</v>
@@ -4291,7 +4291,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AY15" t="n">
         <v>16.5</v>
@@ -4300,22 +4300,22 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BB15" t="n">
         <v>38</v>
       </c>
       <c r="BC15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
         <v>40</v>
       </c>
       <c r="BF15" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BG15" t="n">
         <v>6.4</v>
@@ -4330,7 +4330,7 @@
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BL15" t="n">
         <v>85</v>
@@ -4342,7 +4342,7 @@
         <v>10</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP15" t="n">
         <v>36</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
         <v>2.12</v>
@@ -4428,7 +4428,7 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
         <v>19</v>
@@ -4485,7 +4485,7 @@
         <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
         <v>40</v>
@@ -4506,7 +4506,7 @@
         <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
         <v>32</v>
@@ -4527,7 +4527,7 @@
         <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
         <v>50</v>
@@ -4554,13 +4554,13 @@
         <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
         <v>25</v>
@@ -4569,10 +4569,10 @@
         <v>29</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="n">
         <v>4.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -869,7 +869,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
@@ -881,7 +881,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
@@ -896,7 +896,7 @@
         <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
         <v>1.8</v>
@@ -965,16 +965,16 @@
         <v>210</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -983,10 +983,10 @@
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>8.4</v>
@@ -1007,19 +1007,19 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
         <v>3.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI2" t="n">
         <v>3.8</v>
@@ -1031,10 +1031,10 @@
         <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.5</v>
@@ -1043,7 +1043,7 @@
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.7</v>
@@ -1055,32 +1055,32 @@
         <v>4.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BU2" t="n">
         <v>4.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY2" t="n">
         <v>5.3</v>
       </c>
       <c r="BZ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -1141,16 +1141,16 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
         <v>1.75</v>
@@ -1219,10 +1219,10 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>12</v>
@@ -1231,13 +1231,13 @@
         <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>4.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
         <v>2.82</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1395,28 +1395,28 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
         <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1649,28 +1649,28 @@
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="X5" t="n">
         <v>38</v>
@@ -1685,7 +1685,7 @@
         <v>190</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
         <v>15</v>
@@ -1694,13 +1694,13 @@
         <v>30</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
@@ -1709,34 +1709,34 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AO5" t="n">
         <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1769,22 +1769,22 @@
         <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH5" t="n">
         <v>5.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -1897,16 +1897,16 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
         <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
         <v>1.39</v>
@@ -1915,10 +1915,10 @@
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
         <v>1.81</v>
@@ -2038,22 +2038,22 @@
         <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BN6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO6" t="n">
         <v>5.5</v>
@@ -2062,41 +2062,41 @@
         <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU6" t="n">
         <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BZ6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
         <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
@@ -2145,202 +2145,202 @@
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
         <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
         <v>5.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
         <v>5.5</v>
@@ -3920,7 +3920,7 @@
         <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J15" t="n">
         <v>4.4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.5</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
@@ -4204,7 +4204,7 @@
         <v>1.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
         <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA15" t="n">
         <v>21</v>
@@ -4234,7 +4234,7 @@
         <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF15" t="n">
         <v>42</v>
@@ -4243,19 +4243,19 @@
         <v>18.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI15" t="n">
         <v>24</v>
       </c>
       <c r="AJ15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="n">
         <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
         <v>55</v>
@@ -4267,7 +4267,7 @@
         <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AQ15" t="n">
         <v>13.5</v>
@@ -4309,16 +4309,16 @@
         <v>36</v>
       </c>
       <c r="BD15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BF15" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH15" t="n">
         <v>5.7</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>
@@ -4419,16 +4419,16 @@
         <v>2.12</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.75</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4437,7 +4437,7 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
@@ -4449,16 +4449,16 @@
         <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
         <v>1.59</v>
       </c>
       <c r="U16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
         <v>19</v>
@@ -4479,13 +4479,13 @@
         <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>40</v>
@@ -4500,13 +4500,13 @@
         <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
         <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>32</v>
@@ -4527,16 +4527,16 @@
         <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AT16" t="n">
         <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
         <v>13.5</v>
@@ -4554,7 +4554,7 @@
         <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
@@ -4566,10 +4566,10 @@
         <v>25</v>
       </c>
       <c r="BE16" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG16" t="n">
         <v>26</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 12:08:29</t>
+          <t>2026-05-17 14:29:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H2" t="n">
         <v>10.5</v>
@@ -869,7 +869,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
@@ -878,10 +878,10 @@
         <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
@@ -890,25 +890,25 @@
         <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R2" t="n">
         <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.81</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
@@ -1019,7 +1019,7 @@
         <v>5.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI2" t="n">
         <v>3.8</v>
@@ -1031,10 +1031,10 @@
         <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN2" t="n">
         <v>4.5</v>
@@ -1043,7 +1043,7 @@
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.7</v>
@@ -1055,32 +1055,32 @@
         <v>4.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU2" t="n">
         <v>4.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
         <v>5.3</v>
       </c>
       <c r="BZ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -1150,13 +1150,13 @@
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.57</v>
@@ -1285,7 +1285,7 @@
         <v>3.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
         <v>5.5</v>
@@ -1297,13 +1297,13 @@
         <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
         <v>4.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
         <v>5.1</v>
@@ -1321,20 +1321,20 @@
         <v>4.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
         <v>4.9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1395,10 +1395,10 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1410,7 +1410,7 @@
         <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
         <v>1.55</v>
@@ -1527,68 +1527,68 @@
         <v>17</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
         <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
         <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU4" t="n">
         <v>4.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -1781,68 +1781,68 @@
         <v>4.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BI5" t="n">
         <v>3.75</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO5" t="n">
         <v>3.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="BR5" t="n">
         <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
         <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>13.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -2035,25 +2035,25 @@
         <v>12</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI6" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
         <v>5.5</v>
@@ -2062,48 +2062,48 @@
         <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BU6" t="n">
         <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,165 +2113,165 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.87</v>
-      </c>
       <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.38</v>
       </c>
-      <c r="S7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.58</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG7" t="n">
         <v>14</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK7" t="n">
         <v>32</v>
       </c>
-      <c r="AF7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>38</v>
-      </c>
       <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO7" t="n">
         <v>48</v>
       </c>
-      <c r="AM7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>25</v>
-      </c>
       <c r="AP7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AQ7" t="n">
         <v>3.85</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
         <v>4.7</v>
@@ -2280,84 +2280,84 @@
         <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>25</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BY7" t="n">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR8" t="n">
         <v>4.3</v>
       </c>
-      <c r="I8" t="n">
+      <c r="AS8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE8" t="n">
         <v>5.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="BF8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH8" t="n">
         <v>3.95</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>1.74</v>
       </c>
       <c r="G9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="AY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF9" t="n">
         <v>7</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>1.51</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.65</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>5.9</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>2.88</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
         <v>4.2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.6</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
         <v>4.6</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.71</v>
       </c>
-      <c r="H14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="U14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD14" t="n">
         <v>6.8</v>
       </c>
-      <c r="J14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.5</v>
       </c>
-      <c r="G15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW15" t="n">
         <v>4.4</v>
       </c>
-      <c r="K15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AX15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR15" t="n">
         <v>30</v>
       </c>
-      <c r="Y15" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="BS15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT15" t="n">
         <v>11</v>
       </c>
-      <c r="AD15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6</v>
-      </c>
       <c r="BU15" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>23</v>
       </c>
-      <c r="BY15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>15</v>
-      </c>
       <c r="CA15" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 14:29:01</t>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>
@@ -4399,244 +4399,498 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Y16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS16" t="n">
         <v>19</v>
       </c>
-      <c r="Z16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AT16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC16" t="n">
         <v>40</v>
       </c>
-      <c r="AF16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="BD16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF16" t="n">
         <v>26</v>
       </c>
-      <c r="AK16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG16" t="n">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BL16" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:46:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL17" t="n">
         <v>100</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BM17" t="n">
         <v>4.5</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BN17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BO17" t="n">
         <v>4</v>
       </c>
-      <c r="BP16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ16" t="n">
+      <c r="BP17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>3.75</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="BR17" t="n">
         <v>28</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="BS17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW17" t="n">
         <v>4.1</v>
       </c>
-      <c r="BT16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BX16" t="n">
+      <c r="BX17" t="n">
         <v>38</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="BY17" t="n">
         <v>4.2</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="BZ17" t="n">
         <v>21</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CA17" t="n">
         <v>3.9</v>
       </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-05-17 14:29:01</t>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:46:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -869,7 +869,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
@@ -890,7 +890,7 @@
         <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
         <v>1.67</v>
@@ -899,10 +899,10 @@
         <v>2.24</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
@@ -962,10 +962,10 @@
         <v>4.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.8</v>
@@ -983,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
         <v>5.1</v>
@@ -1007,19 +1007,19 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
         <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG2" t="n">
         <v>5.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BI2" t="n">
         <v>3.8</v>
@@ -1028,16 +1028,16 @@
         <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
         <v>3.25</v>
@@ -1052,35 +1052,35 @@
         <v>24</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT2" t="n">
         <v>16</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -1141,16 +1141,16 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
         <v>1.86</v>
@@ -1165,46 +1165,46 @@
         <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
         <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1213,7 +1213,7 @@
         <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO3" t="n">
         <v>34</v>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
         <v>16.5</v>
@@ -1249,49 +1249,49 @@
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
         <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
         <v>2.56</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO3" t="n">
         <v>4.9</v>
@@ -1300,16 +1300,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BU3" t="n">
         <v>4.2</v>
@@ -1318,23 +1318,23 @@
         <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1401,7 +1401,7 @@
         <v>1.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
@@ -1410,7 +1410,7 @@
         <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.55</v>
@@ -1482,7 +1482,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1506,19 +1506,19 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.73</v>
@@ -1700,7 +1700,7 @@
         <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
@@ -1727,16 +1727,16 @@
         <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1769,16 +1769,16 @@
         <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
         <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -2011,25 +2011,25 @@
         <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG6" t="n">
         <v>12</v>
@@ -2044,16 +2044,16 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
         <v>5.5</v>
@@ -2062,13 +2062,13 @@
         <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
         <v>4.8</v>
@@ -2080,23 +2080,23 @@
         <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>3.6</v>
@@ -2148,10 +2148,10 @@
         <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -2166,19 +2166,19 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
         <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -2187,31 +2187,31 @@
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>55</v>
@@ -2220,73 +2220,73 @@
         <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
         <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="n">
         <v>3.85</v>
@@ -2298,59 +2298,59 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL7" t="n">
         <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BP7" t="n">
         <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR7" t="n">
         <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT7" t="n">
         <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BV7" t="n">
         <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX7" t="n">
         <v>48</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>34</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
@@ -2552,13 +2552,13 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL8" t="n">
         <v>130</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN8" t="n">
         <v>7</v>
@@ -2570,13 +2570,13 @@
         <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
         <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2588,13 +2588,13 @@
         <v>22</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX8" t="n">
         <v>36</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
@@ -2677,16 +2677,16 @@
         <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>25</v>
@@ -2806,13 +2806,13 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL9" t="n">
         <v>110</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN9" t="n">
         <v>5.3</v>
@@ -2824,41 +2824,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR9" t="n">
         <v>26</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT9" t="n">
         <v>9.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV9" t="n">
         <v>40</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX9" t="n">
         <v>46</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ9" t="n">
         <v>19.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3060,31 +3060,31 @@
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL10" t="n">
         <v>110</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN10" t="n">
         <v>13.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP10" t="n">
         <v>65</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR10" t="n">
         <v>60</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT10" t="n">
         <v>5.1</v>
@@ -3096,23 +3096,23 @@
         <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BX10" t="n">
         <v>23</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BZ10" t="n">
         <v>12.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
         <v>1.61</v>
@@ -3194,7 +3194,7 @@
         <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3314,13 +3314,13 @@
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL11" t="n">
         <v>110</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN11" t="n">
         <v>6.8</v>
@@ -3332,13 +3332,13 @@
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR11" t="n">
         <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT11" t="n">
         <v>6.8</v>
@@ -3350,23 +3350,23 @@
         <v>23</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX11" t="n">
         <v>34</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ11" t="n">
         <v>24</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3397,73 +3397,73 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="G12" t="n">
         <v>1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>2.38</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
@@ -3475,7 +3475,7 @@
         <v>110</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3505,40 +3505,40 @@
         <v>130</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
         <v>7.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,34 +3547,34 @@
         <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL12" t="n">
         <v>160</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN12" t="n">
         <v>4.8</v>
@@ -3586,41 +3586,41 @@
         <v>13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
         <v>32</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT12" t="n">
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV12" t="n">
         <v>60</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
         <v>1.35</v>
@@ -3711,7 +3711,7 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
         <v>65</v>
@@ -3822,13 +3822,13 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BL13" t="n">
         <v>110</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN13" t="n">
         <v>6.2</v>
@@ -3840,13 +3840,13 @@
         <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BR13" t="n">
         <v>29</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BT13" t="n">
         <v>8.6</v>
@@ -3858,23 +3858,23 @@
         <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX13" t="n">
         <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ13" t="n">
         <v>23</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>5.3</v>
@@ -3920,10 +3920,10 @@
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3935,28 +3935,28 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X14" t="n">
         <v>20</v>
@@ -3980,7 +3980,7 @@
         <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
         <v>12.5</v>
@@ -3992,7 +3992,7 @@
         <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>19.5</v>
@@ -4004,13 +4004,13 @@
         <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP14" t="n">
         <v>16</v>
@@ -4019,10 +4019,10 @@
         <v>16.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
@@ -4034,7 +4034,7 @@
         <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -4046,25 +4046,25 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="n">
         <v>4.4</v>
@@ -4076,13 +4076,13 @@
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL14" t="n">
         <v>120</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN14" t="n">
         <v>5.2</v>
@@ -4094,41 +4094,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR14" t="n">
         <v>28</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT14" t="n">
         <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV14" t="n">
         <v>44</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX14" t="n">
         <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ14" t="n">
         <v>21</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
         <v>5.5</v>
@@ -4171,13 +4171,13 @@
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -4195,7 +4195,7 @@
         <v>1.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -4204,13 +4204,13 @@
         <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -4330,13 +4330,13 @@
         <v>12</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL15" t="n">
         <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN15" t="n">
         <v>5.1</v>
@@ -4348,41 +4348,41 @@
         <v>13</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BR15" t="n">
         <v>30</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV15" t="n">
         <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX15" t="n">
         <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>23</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H16" t="n">
         <v>1.78</v>
@@ -4446,7 +4446,7 @@
         <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R16" t="n">
         <v>1.76</v>
@@ -4458,13 +4458,13 @@
         <v>1.53</v>
       </c>
       <c r="U16" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V16" t="n">
         <v>2.26</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
         <v>30</v>
@@ -4476,7 +4476,7 @@
         <v>14.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
         <v>27</v>
@@ -4503,22 +4503,22 @@
         <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK16" t="n">
         <v>44</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP16" t="n">
         <v>27</v>
@@ -4557,7 +4557,7 @@
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC16" t="n">
         <v>40</v>
@@ -4566,16 +4566,16 @@
         <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI16" t="n">
         <v>3.7</v>
@@ -4608,7 +4608,7 @@
         <v>38</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT16" t="n">
         <v>6</v>
@@ -4620,7 +4620,7 @@
         <v>13.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BX16" t="n">
         <v>24</v>
@@ -4629,14 +4629,14 @@
         <v>3.95</v>
       </c>
       <c r="BZ16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>
@@ -4697,10 +4697,10 @@
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
         <v>1.57</v>
@@ -4715,7 +4715,7 @@
         <v>2.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
         <v>1.87</v>
@@ -4751,7 +4751,7 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI17" t="n">
         <v>38</v>
@@ -4778,7 +4778,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR17" t="n">
         <v>27</v>
@@ -4805,7 +4805,7 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
         <v>36</v>
@@ -4850,7 +4850,7 @@
         <v>6.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP17" t="n">
         <v>17</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:26</t>
+          <t>2026-05-17 19:00:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,22 +887,22 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
@@ -959,22 +959,22 @@
         <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO2" t="n">
         <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -983,10 +983,10 @@
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
         <v>8.4</v>
@@ -1007,16 +1007,16 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
         <v>3.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1028,13 +1028,13 @@
         <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>4.1</v>
@@ -1043,7 +1043,7 @@
         <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.7</v>
@@ -1052,35 +1052,35 @@
         <v>24</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BT2" t="n">
         <v>16</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
@@ -1135,7 +1135,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
@@ -1144,7 +1144,7 @@
         <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
@@ -1159,7 +1159,7 @@
         <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.4</v>
@@ -1171,10 +1171,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
@@ -1189,7 +1189,7 @@
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1204,7 +1204,7 @@
         <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>16.5</v>
@@ -1282,13 +1282,13 @@
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>6.6</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>5.6</v>
@@ -1315,7 +1315,7 @@
         <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
         <v>6.8</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
         <v>2.94</v>
@@ -1395,19 +1395,19 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
         <v>2.2</v>
@@ -1431,10 +1431,10 @@
         <v>48</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>15</v>
@@ -1482,7 +1482,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1509,16 +1509,16 @@
         <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD4" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G5" t="n">
         <v>1.52</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5" t="n">
         <v>7.4</v>
@@ -1634,7 +1634,7 @@
         <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1664,10 +1664,10 @@
         <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
         <v>2.92</v>
@@ -1727,7 +1727,7 @@
         <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
         <v>5</v>
@@ -1760,7 +1760,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1769,10 +1769,10 @@
         <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
         <v>4.3</v>
@@ -1784,19 +1784,19 @@
         <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>4.7</v>
@@ -1808,41 +1808,41 @@
         <v>9.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
         <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
         <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1912,13 +1912,13 @@
         <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.81</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2489,46 +2489,46 @@
         <v>25</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS8" t="n">
         <v>4.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA8" t="n">
         <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD8" t="n">
         <v>4.9</v>
@@ -2537,7 +2537,7 @@
         <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG8" t="n">
         <v>16</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>1.39</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK9" t="n">
         <v>110</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AL9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>12</v>
       </c>
-      <c r="AC9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="BK9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>11</v>
       </c>
-      <c r="AH9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>110</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>19.5</v>
-      </c>
       <c r="CA9" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2880,67 +2880,67 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>9.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.39</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>1.51</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>2.96</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2949,94 +2949,94 @@
         <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.5</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="AK10" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1.05</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>10</v>
-      </c>
       <c r="AX10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA10" t="n">
         <v>1.01</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
         <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD10" t="n">
         <v>1.01</v>
@@ -3045,74 +3045,74 @@
         <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BL10" t="n">
         <v>110</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BN10" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW10" t="n">
         <v>4.4</v>
       </c>
-      <c r="BT10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BX10" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3134,187 +3134,187 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.52</v>
+        <v>1.73</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.24</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.53</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL11" t="n">
         <v>32</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
       </c>
       <c r="AM11" t="n">
         <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>14</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AW11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB11" t="n">
         <v>15</v>
       </c>
-      <c r="AS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BC11" t="n">
-        <v>1.05</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL11" t="n">
         <v>110</v>
@@ -3323,50 +3323,50 @@
         <v>5.3</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BR11" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BX11" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>6.8</v>
@@ -3415,19 +3415,19 @@
         <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
         <v>2</v>
@@ -3442,13 +3442,13 @@
         <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -3475,7 +3475,7 @@
         <v>110</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3505,16 +3505,16 @@
         <v>130</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
@@ -3523,22 +3523,22 @@
         <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
         <v>7.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,37 +3547,37 @@
         <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
         <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BL12" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BO12" t="n">
         <v>3.4</v>
@@ -3586,41 +3586,41 @@
         <v>13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
         <v>32</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BT12" t="n">
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BX12" t="n">
         <v>70</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>25</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3690,19 +3690,19 @@
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
         <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3813,7 +3813,7 @@
         <v>22</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
         <v>3.15</v>
@@ -3822,16 +3822,16 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="BL13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BO13" t="n">
         <v>3.95</v>
@@ -3840,13 +3840,13 @@
         <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR13" t="n">
         <v>29</v>
       </c>
       <c r="BS13" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="BT13" t="n">
         <v>8.6</v>
@@ -3858,23 +3858,23 @@
         <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BX13" t="n">
         <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BZ13" t="n">
         <v>23</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
@@ -3917,7 +3917,7 @@
         <v>5.3</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
         <v>4.5</v>
@@ -3944,7 +3944,7 @@
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
         <v>1.73</v>
@@ -3956,10 +3956,10 @@
         <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y14" t="n">
         <v>21</v>
@@ -4022,7 +4022,7 @@
         <v>32</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
@@ -4034,7 +4034,7 @@
         <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB14" t="n">
         <v>6</v>
@@ -4064,71 +4064,71 @@
         <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BI14" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BO14" t="n">
         <v>3.65</v>
       </c>
       <c r="BP14" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="BR14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -4201,13 +4201,13 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
         <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
         <v>2.38</v>
@@ -4222,7 +4222,7 @@
         <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
         <v>11.5</v>
@@ -4318,71 +4318,71 @@
         <v>6.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO15" t="n">
         <v>3.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="BR15" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV15" t="n">
         <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>23</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4419,13 +4419,13 @@
         <v>4.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K16" t="n">
         <v>4.6</v>
@@ -4437,7 +4437,7 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.16</v>
@@ -4449,10 +4449,10 @@
         <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T16" t="n">
         <v>1.53</v>
@@ -4461,13 +4461,13 @@
         <v>2.8</v>
       </c>
       <c r="V16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="W16" t="n">
         <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
         <v>15</v>
@@ -4551,13 +4551,13 @@
         <v>17</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BC16" t="n">
         <v>40</v>
@@ -4569,74 +4569,74 @@
         <v>46</v>
       </c>
       <c r="BF16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG16" t="n">
         <v>6.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BI16" t="n">
         <v>3.7</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL16" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="BP16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BU16" t="n">
         <v>3.9</v>
       </c>
       <c r="BV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>13.5</v>
       </c>
-      <c r="BW16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>15</v>
-      </c>
       <c r="CA16" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4691,25 +4691,25 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
         <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
         <v>2.58</v>
@@ -4724,7 +4724,7 @@
         <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
         <v>28</v>
@@ -4739,7 +4739,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>36</v>
@@ -4793,7 +4793,7 @@
         <v>8.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
         <v>34</v>
@@ -4829,68 +4829,830 @@
         <v>25</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="BL17" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BS17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU17" t="n">
         <v>5.4</v>
       </c>
       <c r="BV17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-17 21:14:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z18" t="n">
         <v>32</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="AA18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW18" t="n">
         <v>4.1</v>
       </c>
-      <c r="BX17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY17" t="n">
+      <c r="AX18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG18" t="n">
         <v>4.2</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="BH18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-17 21:14:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>390</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>280</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-17 21:14:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Universidad de Venezuela</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>320</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>470</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>510</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
         <v>21</v>
       </c>
-      <c r="CA17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-05-17 19:00:56</t>
+      <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -890,7 +890,7 @@
         <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
         <v>1.67</v>
@@ -899,7 +899,7 @@
         <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1132,13 +1132,13 @@
         <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
         <v>1.73</v>
@@ -1186,7 +1186,7 @@
         <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
         <v>23</v>
@@ -1201,19 +1201,19 @@
         <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
         <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO3" t="n">
         <v>34</v>
@@ -1258,7 +1258,7 @@
         <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
         <v>6.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1395,10 +1395,10 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -1407,10 +1407,10 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
         <v>1.55</v>
@@ -1512,10 +1512,10 @@
         <v>4.6</v>
       </c>
       <c r="BC4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD4" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
         <v>4.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H5" t="n">
         <v>6.6</v>
@@ -1634,7 +1634,7 @@
         <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1739,7 +1739,7 @@
         <v>5.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1873,52 +1873,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I6" t="n">
         <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>1.81</v>
@@ -1927,22 +1927,22 @@
         <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
         <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>12.5</v>
@@ -1951,7 +1951,7 @@
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
         <v>18</v>
@@ -1981,10 +1981,10 @@
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
         <v>10.5</v>
@@ -1996,7 +1996,7 @@
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>9.6</v>
@@ -2008,49 +2008,49 @@
         <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
         <v>12</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
@@ -2059,44 +2059,44 @@
         <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV6" t="n">
         <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.77</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2468,13 +2468,13 @@
         <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>48</v>
@@ -2498,7 +2498,7 @@
         <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2510,7 +2510,7 @@
         <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
         <v>4.5</v>
@@ -2519,28 +2519,28 @@
         <v>4.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
         <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF8" t="n">
         <v>5.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.95</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>1.39</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>1.15</v>
@@ -2674,7 +2674,7 @@
         <v>1.71</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
@@ -2683,7 +2683,7 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -2746,37 +2746,37 @@
         <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>4.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
         <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>3.85</v>
       </c>
       <c r="BA9" t="n">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="BB9" t="n">
         <v>4.3</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
@@ -2898,7 +2898,7 @@
         <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2928,7 +2928,7 @@
         <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
         <v>1.61</v>
@@ -2937,13 +2937,13 @@
         <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>15.5</v>
@@ -3006,10 +3006,10 @@
         <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
@@ -3018,7 +3018,7 @@
         <v>9.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
         <v>15</v>
@@ -3030,19 +3030,19 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.05</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
         <v>15</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
         <v>2.12</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
         <v>22</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.34</v>
@@ -3430,7 +3430,7 @@
         <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
@@ -3445,10 +3445,10 @@
         <v>1.97</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -3466,7 +3466,7 @@
         <v>7.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
         <v>28</v>
@@ -3505,40 +3505,40 @@
         <v>130</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS12" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ12" t="n">
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,16 +3547,16 @@
         <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="n">
         <v>3.5</v>
@@ -3580,7 +3580,7 @@
         <v>4.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP12" t="n">
         <v>13</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
         <v>2.18</v>
@@ -3660,13 +3660,13 @@
         <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3681,28 +3681,28 @@
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3717,10 +3717,10 @@
         <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
@@ -3729,7 +3729,7 @@
         <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -3738,7 +3738,7 @@
         <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
         <v>26</v>
@@ -3765,10 +3765,10 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT13" t="n">
         <v>10.5</v>
@@ -3780,7 +3780,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3792,19 +3792,19 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC13" t="n">
         <v>17.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
         <v>8.6</v>
@@ -3813,22 +3813,22 @@
         <v>22</v>
       </c>
       <c r="BH13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN13" t="n">
         <v>5.2</v>
@@ -3840,13 +3840,13 @@
         <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR13" t="n">
         <v>29</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT13" t="n">
         <v>8.6</v>
@@ -3858,13 +3858,13 @@
         <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX13" t="n">
         <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>23</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
         <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
         <v>5.3</v>
@@ -3923,7 +3923,7 @@
         <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3938,10 +3938,10 @@
         <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
         <v>2.9</v>
@@ -3959,7 +3959,7 @@
         <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
         <v>21</v>
@@ -4049,7 +4049,7 @@
         <v>7.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
         <v>15</v>
@@ -4058,7 +4058,7 @@
         <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>8</v>
@@ -4067,10 +4067,10 @@
         <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
         <v>4.7</v>
@@ -4100,19 +4100,19 @@
         <v>25</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4124,11 +4124,11 @@
         <v>19</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
         <v>5.5</v>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -4201,16 +4201,16 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
         <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -4225,13 +4225,13 @@
         <v>170</v>
       </c>
       <c r="AB15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC15" t="n">
-        <v>12</v>
-      </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>90</v>
@@ -4273,10 +4273,10 @@
         <v>17.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>8</v>
@@ -4288,7 +4288,7 @@
         <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX15" t="n">
         <v>9.199999999999999</v>
@@ -4300,7 +4300,7 @@
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
         <v>14.5</v>
@@ -4309,16 +4309,16 @@
         <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
         <v>6.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="n">
         <v>3.85</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I16" t="n">
         <v>1.79</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>4.4</v>
@@ -4449,7 +4449,7 @@
         <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S16" t="n">
         <v>2.24</v>
@@ -4461,7 +4461,7 @@
         <v>2.8</v>
       </c>
       <c r="V16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W16" t="n">
         <v>1.27</v>
@@ -4482,7 +4482,7 @@
         <v>27</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
         <v>10</v>
@@ -4515,13 +4515,13 @@
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
         <v>6.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ16" t="n">
         <v>14</v>
@@ -4569,10 +4569,10 @@
         <v>46</v>
       </c>
       <c r="BF16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
         <v>5</v>
@@ -4584,13 +4584,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
         <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
         <v>8.6</v>
@@ -4602,41 +4602,41 @@
         <v>32</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR16" t="n">
         <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU16" t="n">
         <v>3.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
         <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
         <v>1.27</v>
@@ -4963,10 +4963,10 @@
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="U18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
         <v>1.34</v>
@@ -4987,10 +4987,10 @@
         <v>95</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
         <v>19</v>
@@ -5035,10 +5035,10 @@
         <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -5050,7 +5050,7 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -5059,28 +5059,28 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
         <v>17</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="n">
         <v>3.1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H19" t="n">
         <v>15.5</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K19" t="n">
         <v>7.6</v>
@@ -5211,7 +5211,7 @@
         <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S19" t="n">
         <v>2.56</v>
@@ -5226,13 +5226,13 @@
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="Z19" t="n">
         <v>200</v>
@@ -5259,7 +5259,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AI19" t="n">
         <v>280</v>
@@ -5271,7 +5271,7 @@
         <v>15.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>310</v>
@@ -5313,7 +5313,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BA19" t="n">
         <v>9.199999999999999</v>
@@ -5394,11 +5394,11 @@
         <v>11</v>
       </c>
       <c r="CA19" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G20" t="n">
         <v>1.21</v>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
         <v>7.8</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>1.25</v>
@@ -5471,7 +5471,7 @@
         <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="U20" t="n">
         <v>1.5</v>
@@ -5489,7 +5489,7 @@
         <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -5516,7 +5516,7 @@
         <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="AJ20" t="n">
         <v>7.8</v>
@@ -5525,13 +5525,13 @@
         <v>16.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -5540,13 +5540,13 @@
         <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -5555,10 +5555,10 @@
         <v>16.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>6</v>
@@ -5567,10 +5567,10 @@
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB20" t="n">
         <v>6.8</v>
@@ -5579,64 +5579,64 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF20" t="n">
         <v>3.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH20" t="n">
         <v>4.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN20" t="n">
         <v>3.45</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BP20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BU20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,7 +890,7 @@
         <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.67</v>
@@ -899,10 +899,10 @@
         <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
@@ -917,7 +917,7 @@
         <v>48</v>
       </c>
       <c r="Z2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA2" t="n">
         <v>430</v>
@@ -926,7 +926,7 @@
         <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD2" t="n">
         <v>46</v>
@@ -953,7 +953,7 @@
         <v>16</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
         <v>150</v>
@@ -965,16 +965,16 @@
         <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -983,10 +983,10 @@
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB2" t="n">
         <v>8.4</v>
@@ -1010,34 +1010,34 @@
         <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
         <v>3.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2" t="n">
         <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO2" t="n">
         <v>3.25</v>
@@ -1052,35 +1052,35 @@
         <v>24</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
         <v>16</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
@@ -1141,13 +1141,13 @@
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -1177,16 +1177,16 @@
         <v>40</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
         <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
         <v>23</v>
@@ -1201,7 +1201,7 @@
         <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
         <v>44</v>
@@ -1213,10 +1213,10 @@
         <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP3" t="n">
         <v>9.6</v>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>16.5</v>
@@ -1249,25 +1249,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
         <v>21</v>
@@ -1282,16 +1282,16 @@
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO3" t="n">
         <v>4.9</v>
@@ -1306,19 +1306,19 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>5.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
         <v>1.88</v>
@@ -1407,10 +1407,10 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
         <v>1.55</v>
@@ -1452,7 +1452,7 @@
         <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
@@ -1461,7 +1461,7 @@
         <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G5" t="n">
         <v>1.51</v>
@@ -1628,13 +1628,13 @@
         <v>6.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J5" t="n">
         <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1643,19 +1643,19 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="n">
         <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S5" t="n">
         <v>2.18</v>
@@ -1664,13 +1664,13 @@
         <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X5" t="n">
         <v>38</v>
@@ -1784,19 +1784,19 @@
         <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>4.7</v>
@@ -1808,10 +1808,10 @@
         <v>9.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR5" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BS5" t="n">
         <v>6.6</v>
@@ -1820,29 +1820,29 @@
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>11.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H6" t="n">
         <v>2.1</v>
@@ -1885,46 +1885,46 @@
         <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.33</v>
       </c>
       <c r="X6" t="n">
         <v>15.5</v>
@@ -1942,7 +1942,7 @@
         <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>12.5</v>
@@ -1969,7 +1969,7 @@
         <v>50</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1984,16 +1984,16 @@
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
         <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
@@ -2008,49 +2008,49 @@
         <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>15</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE6" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6</v>
-      </c>
       <c r="BF6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BI6" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
@@ -2059,16 +2059,16 @@
         <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
         <v>5.1</v>
@@ -2080,23 +2080,23 @@
         <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -2130,55 +2130,55 @@
         <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
         <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
         <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -2226,131 +2226,131 @@
         <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV7" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="AW7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
         <v>3.15</v>
@@ -2390,16 +2390,16 @@
         <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2408,19 +2408,19 @@
         <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.61</v>
@@ -2447,7 +2447,7 @@
         <v>44</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
         <v>8.4</v>
@@ -2462,43 +2462,43 @@
         <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
         <v>48</v>
       </c>
       <c r="AM8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2507,58 +2507,58 @@
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX8" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AY8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
         <v>5.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN8" t="n">
         <v>7</v>
@@ -2567,22 +2567,22 @@
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR8" t="n">
         <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>22</v>
@@ -2591,10 +2591,10 @@
         <v>4.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.52</v>
       </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.71</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.96</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>2.88</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>85</v>
-      </c>
       <c r="AG9" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>240</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL9" t="n">
         <v>110</v>
       </c>
-      <c r="AL9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="BM9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CA9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>6.8</v>
       </c>
       <c r="G10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.51</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
         <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>44</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>5.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>3.95</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>3.35</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.6</v>
+        <v>3.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>15</v>
+        <v>2.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BN10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BP10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
         <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
         <v>22</v>
       </c>
-      <c r="Z11" t="n">
-        <v>40</v>
-      </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
         <v>80</v>
       </c>
       <c r="AN11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
       <c r="BK11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BL11" t="n">
         <v>110</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT11" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BX11" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BY11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ11" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
@@ -3415,28 +3415,28 @@
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
         <v>1.98</v>
@@ -3448,7 +3448,7 @@
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -3475,7 +3475,7 @@
         <v>110</v>
       </c>
       <c r="AF12" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3505,16 +3505,16 @@
         <v>130</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ12" t="n">
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
@@ -3523,22 +3523,22 @@
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>5.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,87 +3547,87 @@
         <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BP12" t="n">
         <v>13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BR12" t="n">
         <v>32</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BT12" t="n">
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BX12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>1.77</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
         <v>21</v>
       </c>
-      <c r="Y13" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="BB13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO13" t="n">
+      <c r="BK13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP13" t="n">
         <v>32</v>
       </c>
-      <c r="AP13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN13" t="n">
+      <c r="BQ13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT13" t="n">
         <v>5.2</v>
       </c>
-      <c r="BO13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV13" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="BW13" t="n">
         <v>5.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BZ13" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="H14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
         <v>4.8</v>
       </c>
-      <c r="I14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="BB14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD14" t="n">
         <v>4.5</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BE14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.8</v>
       </c>
-      <c r="AX14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8</v>
-      </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BN14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU14" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BV14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CA14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>20</v>
       </c>
       <c r="AK15" t="n">
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC15" t="n">
         <v>17.5</v>
       </c>
-      <c r="AR15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="BD15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>22</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BT15" t="n">
         <v>8.6</v>
       </c>
-      <c r="BN15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BU15" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BZ15" t="n">
         <v>23</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.5</v>
       </c>
-      <c r="G16" t="n">
+      <c r="L16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN16" t="n">
         <v>4.7</v>
       </c>
-      <c r="H16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X16" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="BO16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV16" t="n">
         <v>42</v>
       </c>
-      <c r="AG16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>75</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>8.6</v>
       </c>
-      <c r="BO16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BX16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ16" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
         <v>28</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -4772,10 +4772,10 @@
         <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ17" t="n">
         <v>17.5</v>
@@ -4808,7 +4808,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
@@ -4826,7 +4826,7 @@
         <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH17" t="n">
         <v>4.4</v>
@@ -4844,7 +4844,7 @@
         <v>85</v>
       </c>
       <c r="BM17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN17" t="n">
         <v>5.4</v>
@@ -4862,10 +4862,10 @@
         <v>24</v>
       </c>
       <c r="BS17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU17" t="n">
         <v>5.4</v>
@@ -4874,23 +4874,23 @@
         <v>26</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ17" t="n">
         <v>17.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="H18" t="n">
-        <v>3.55</v>
+        <v>15.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.95</v>
+        <v>17.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AJ18" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AL18" t="n">
         <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS18" t="n">
         <v>10</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT18" t="n">
+      <c r="AZ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY18" t="n">
+      <c r="BC18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG18" t="n">
         <v>10</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BH18" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK18" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="BP18" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS18" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU18" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>5.1</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA18" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -5166,184 +5166,184 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
-        <v>15.5</v>
+        <v>3.55</v>
       </c>
       <c r="I19" t="n">
-        <v>17.5</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.27</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.54</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>4.5</v>
+        <v>1.72</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>48</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>390</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>310</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
         <v>4.6</v>
       </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>9</v>
-      </c>
       <c r="AS19" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
       </c>
       <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
         <v>13.5</v>
       </c>
-      <c r="AV19" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AW19" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>15</v>
       </c>
       <c r="BK19" t="n">
         <v>6.2</v>
@@ -5352,53 +5352,53 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BP19" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
         <v>3.45</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BP20" t="n">
         <v>6</v>
@@ -5652,7 +5652,1023 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 23:28:34</t>
+          <t>2026-05-18 01:41:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>55</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-18 01:41:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-18 01:41:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>46</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-18 01:41:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X24" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-18 01:41:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="H2" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
@@ -887,40 +887,40 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -929,10 +929,10 @@
         <v>16.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -941,10 +941,10 @@
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
         <v>12.5</v>
@@ -953,43 +953,43 @@
         <v>16</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>4.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>3.85</v>
       </c>
       <c r="AY2" t="n">
         <v>8.6</v>
@@ -998,43 +998,43 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF2" t="n">
         <v>3.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>4</v>
@@ -1049,38 +1049,38 @@
         <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>11.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>2.66</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1144,7 +1144,7 @@
         <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H4" t="n">
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1386,43 +1386,43 @@
         <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
@@ -1434,7 +1434,7 @@
         <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
         <v>15</v>
@@ -1476,22 +1476,22 @@
         <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
@@ -1506,19 +1506,19 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G6" t="n">
         <v>3.95</v>
@@ -1903,19 +1903,19 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -2035,7 +2035,7 @@
         <v>14.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
         <v>3.15</v>
@@ -2044,13 +2044,13 @@
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
@@ -2062,41 +2062,41 @@
         <v>28</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
         <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2130,55 +2130,55 @@
         <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -2190,7 +2190,7 @@
         <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
@@ -2202,7 +2202,7 @@
         <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
         <v>15.5</v>
@@ -2214,7 +2214,7 @@
         <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
         <v>34</v>
@@ -2223,10 +2223,10 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
         <v>22</v>
@@ -2235,122 +2235,122 @@
         <v>40</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.2</v>
       </c>
       <c r="BA7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
         <v>3.15</v>
@@ -2390,16 +2390,16 @@
         <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2408,25 +2408,25 @@
         <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
         <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.58</v>
@@ -2543,22 +2543,22 @@
         <v>15.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL8" t="n">
         <v>120</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN8" t="n">
         <v>7</v>
@@ -2567,34 +2567,34 @@
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
         <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
         <v>22</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2668,37 +2668,37 @@
         <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB9" t="n">
         <v>12</v>
@@ -2707,13 +2707,13 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2722,85 +2722,85 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU9" t="n">
         <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
         <v>4.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
         <v>4.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
@@ -2818,13 +2818,13 @@
         <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="BP9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR9" t="n">
         <v>26</v>
@@ -2833,13 +2833,13 @@
         <v>4.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW9" t="n">
         <v>4.9</v>
@@ -2848,17 +2848,17 @@
         <v>46</v>
       </c>
       <c r="BY9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA9" t="n">
         <v>4.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2889,46 +2889,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H10" t="n">
         <v>1.39</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
         <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
         <v>1.68</v>
@@ -2940,13 +2940,13 @@
         <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
         <v>40</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>14</v>
@@ -2958,7 +2958,7 @@
         <v>44</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD10" t="n">
         <v>13</v>
@@ -2967,7 +2967,7 @@
         <v>17</v>
       </c>
       <c r="AF10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG10" t="n">
         <v>950</v>
@@ -2979,7 +2979,7 @@
         <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AK10" t="n">
         <v>110</v>
@@ -2994,67 +2994,67 @@
         <v>95</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.95</v>
+        <v>23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3066,25 +3066,25 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>12</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>4.6</v>
@@ -3093,26 +3093,26 @@
         <v>3.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BX10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY10" t="n">
         <v>6.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3146,22 @@
         <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
         <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -3176,25 +3176,25 @@
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
         <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
         <v>20</v>
@@ -3203,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
         <v>46</v>
@@ -3224,10 +3224,10 @@
         <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>42</v>
@@ -3242,16 +3242,16 @@
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
         <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.2</v>
@@ -3266,37 +3266,37 @@
         <v>4.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY11" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
         <v>4.6</v>
@@ -3308,7 +3308,7 @@
         <v>4.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
@@ -3320,16 +3320,16 @@
         <v>110</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN11" t="n">
         <v>6.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.4</v>
@@ -3347,7 +3347,7 @@
         <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW11" t="n">
         <v>4.4</v>
@@ -3359,14 +3359,14 @@
         <v>4.7</v>
       </c>
       <c r="BZ11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA11" t="n">
         <v>4.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -3397,49 +3397,49 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
         <v>1.97</v>
@@ -3448,7 +3448,7 @@
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -3460,22 +3460,22 @@
         <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3505,122 +3505,122 @@
         <v>130</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB12" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BC12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE12" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO12" t="n">
         <v>3.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS12" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BZ12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
         <v>1.75</v>
       </c>
       <c r="I13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -3696,22 +3696,22 @@
         <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X13" t="n">
         <v>30</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
         <v>20</v>
@@ -3732,7 +3732,7 @@
         <v>42</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH13" t="n">
         <v>15</v>
@@ -3744,31 +3744,31 @@
         <v>95</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13" t="n">
         <v>55</v>
       </c>
       <c r="AN13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ13" t="n">
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT13" t="n">
         <v>25</v>
@@ -3783,7 +3783,7 @@
         <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY13" t="n">
         <v>17.5</v>
@@ -3795,7 +3795,7 @@
         <v>21</v>
       </c>
       <c r="BB13" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BC13" t="n">
         <v>40</v>
@@ -3804,19 +3804,19 @@
         <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF13" t="n">
         <v>28</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
         <v>5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.199999999999999</v>
@@ -3834,7 +3834,7 @@
         <v>8.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BP13" t="n">
         <v>32</v>
@@ -3852,13 +3852,13 @@
         <v>5.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
         <v>11.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX13" t="n">
         <v>20</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3923,13 +3923,13 @@
         <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.26</v>
@@ -3938,28 +3938,28 @@
         <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>2.34</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
         <v>25</v>
@@ -3974,7 +3974,7 @@
         <v>10</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
         <v>26</v>
@@ -4019,10 +4019,10 @@
         <v>17.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8</v>
@@ -4034,7 +4034,7 @@
         <v>18</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
         <v>9.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB14" t="n">
         <v>14.5</v>
@@ -4055,16 +4055,16 @@
         <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
         <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="n">
         <v>3.85</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4094,22 +4094,22 @@
         <v>11.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR14" t="n">
         <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT14" t="n">
         <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
         <v>8</v>
@@ -4118,7 +4118,7 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ14" t="n">
         <v>23</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
         <v>3.6</v>
@@ -4183,19 +4183,19 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
         <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
         <v>2.76</v>
@@ -4210,19 +4210,19 @@
         <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
         <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -4231,10 +4231,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
         <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
         <v>26</v>
@@ -4255,19 +4255,19 @@
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
         <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
@@ -4276,22 +4276,22 @@
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
         <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.6</v>
@@ -4300,19 +4300,19 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>17.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>8.6</v>
@@ -4321,7 +4321,7 @@
         <v>22</v>
       </c>
       <c r="BH15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI15" t="n">
         <v>3.1</v>
@@ -4330,34 +4330,34 @@
         <v>11</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP15" t="n">
         <v>17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR15" t="n">
         <v>29</v>
       </c>
       <c r="BS15" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU15" t="n">
         <v>5.4</v>
@@ -4366,23 +4366,23 @@
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX15" t="n">
         <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>23</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -4425,34 +4425,34 @@
         <v>5.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>1.73</v>
@@ -4467,7 +4467,7 @@
         <v>2.16</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y16" t="n">
         <v>21</v>
@@ -4479,16 +4479,16 @@
         <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="n">
         <v>12.5</v>
@@ -4497,10 +4497,10 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
         <v>19.5</v>
@@ -4515,13 +4515,13 @@
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
@@ -4536,13 +4536,13 @@
         <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>16.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -4557,13 +4557,13 @@
         <v>7.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BE16" t="n">
         <v>8.199999999999999</v>
@@ -4572,25 +4572,25 @@
         <v>8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
         <v>4.7</v>
@@ -4599,44 +4599,44 @@
         <v>3.65</v>
       </c>
       <c r="BP16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>42</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA16" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
         <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
@@ -4718,19 +4718,19 @@
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X17" t="n">
         <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -4742,7 +4742,7 @@
         <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
         <v>14.5</v>
@@ -4754,13 +4754,13 @@
         <v>14.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
         <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL17" t="n">
         <v>28</v>
@@ -4772,10 +4772,10 @@
         <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>17.5</v>
@@ -4808,7 +4808,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
@@ -4823,13 +4823,13 @@
         <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG17" t="n">
         <v>26</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI17" t="n">
         <v>3.3</v>
@@ -4838,13 +4838,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL17" t="n">
         <v>85</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN17" t="n">
         <v>5.4</v>
@@ -4856,41 +4856,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR17" t="n">
         <v>24</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
         <v>7.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV17" t="n">
         <v>26</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX17" t="n">
         <v>32</v>
       </c>
       <c r="BY17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
         <v>17.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>15.5</v>
       </c>
       <c r="I18" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="J18" t="n">
         <v>6.4</v>
@@ -4939,37 +4939,37 @@
         <v>7.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
         <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
         <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
         <v>4.5</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AI18" t="n">
         <v>260</v>
@@ -5029,10 +5029,10 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AR18" t="n">
         <v>9.6</v>
@@ -5044,7 +5044,7 @@
         <v>7.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV18" t="n">
         <v>8.6</v>
@@ -5062,7 +5062,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB18" t="n">
         <v>7.6</v>
@@ -5071,13 +5071,13 @@
         <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
         <v>15</v>
       </c>
       <c r="BK18" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,13 +5104,13 @@
         <v>3.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BP18" t="n">
         <v>7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR18" t="n">
         <v>27</v>
@@ -5122,7 +5122,7 @@
         <v>18.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
         <v>2.4</v>
@@ -5199,13 +5199,13 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
         <v>2.3</v>
@@ -5217,10 +5217,10 @@
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
         <v>1.34</v>
@@ -5238,19 +5238,19 @@
         <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB19" t="n">
         <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
         <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
         <v>16.5</v>
@@ -5262,7 +5262,7 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
         <v>38</v>
@@ -5280,7 +5280,7 @@
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
         <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5304,7 +5304,7 @@
         <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -5313,34 +5313,34 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC19" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
         <v>17</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="n">
         <v>3.05</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN19" t="n">
         <v>5</v>
@@ -5361,7 +5361,7 @@
         <v>3.85</v>
       </c>
       <c r="BP19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ19" t="n">
         <v>8.4</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
@@ -5379,7 +5379,7 @@
         <v>5.1</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW19" t="n">
         <v>10.5</v>
@@ -5388,17 +5388,17 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -5432,22 +5432,22 @@
         <v>1.17</v>
       </c>
       <c r="G20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="H20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="K20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
@@ -5471,7 +5471,7 @@
         <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="U20" t="n">
         <v>1.5</v>
@@ -5480,25 +5480,25 @@
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="Z20" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
         <v>950</v>
@@ -5516,10 +5516,10 @@
         <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>16.5</v>
@@ -5528,10 +5528,10 @@
         <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -5540,25 +5540,25 @@
         <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>6</v>
@@ -5567,28 +5567,28 @@
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
         <v>6.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
         <v>3.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="n">
         <v>4.5</v>
@@ -5597,7 +5597,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="BK20" t="n">
         <v>8</v>
@@ -5627,7 +5627,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
         <v>9.199999999999999</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -5704,13 +5704,13 @@
         <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P21" t="n">
         <v>1.55</v>
@@ -5725,7 +5725,7 @@
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
         <v>1.77</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -5937,55 +5937,55 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I22" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
         <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="W22" t="n">
         <v>1.2</v>
@@ -5997,13 +5997,13 @@
         <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AB22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC22" t="n">
         <v>10.5</v>
@@ -6012,16 +6012,16 @@
         <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>38</v>
@@ -6036,31 +6036,31 @@
         <v>90</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR22" t="n">
         <v>8.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV22" t="n">
         <v>9</v>
@@ -6069,40 +6069,40 @@
         <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AY22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
         <v>26</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="n">
         <v>4.4</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ22" t="n">
         <v>12</v>
@@ -6111,25 +6111,25 @@
         <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BM22" t="n">
         <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BO22" t="n">
         <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BQ22" t="n">
         <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BS22" t="n">
         <v>1.01</v>
@@ -6138,16 +6138,16 @@
         <v>4.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW22" t="n">
         <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="n">
         <v>2.14</v>
@@ -6200,7 +6200,7 @@
         <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
         <v>3.1</v>
@@ -6227,7 +6227,7 @@
         <v>2.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
         <v>4.8</v>
@@ -6236,7 +6236,7 @@
         <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
         <v>1.23</v>
@@ -6266,7 +6266,7 @@
         <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF23" t="n">
         <v>12</v>
@@ -6278,7 +6278,7 @@
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -6296,7 +6296,7 @@
         <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP23" t="n">
         <v>8.199999999999999</v>
@@ -6308,7 +6308,7 @@
         <v>7.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -6344,13 +6344,13 @@
         <v>8</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>18</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23" t="n">
         <v>3.15</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>1.42</v>
       </c>
       <c r="H24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I24" t="n">
         <v>12</v>
@@ -6460,7 +6460,7 @@
         <v>5.2</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6478,13 +6478,13 @@
         <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="R24" t="n">
         <v>1.49</v>
       </c>
       <c r="S24" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T24" t="n">
         <v>2.08</v>
@@ -6508,7 +6508,7 @@
         <v>100</v>
       </c>
       <c r="AA24" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AB24" t="n">
         <v>10.5</v>
@@ -6520,7 +6520,7 @@
         <v>40</v>
       </c>
       <c r="AE24" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF24" t="n">
         <v>9.800000000000001</v>
@@ -6595,7 +6595,7 @@
         <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>12.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
@@ -890,7 +890,7 @@
         <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
         <v>1.69</v>
@@ -902,13 +902,13 @@
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
         <v>2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -1129,7 +1129,7 @@
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1138,13 +1138,13 @@
         <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
@@ -1159,10 +1159,10 @@
         <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1207,13 +1207,13 @@
         <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
         <v>30</v>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
         <v>16.5</v>
@@ -1252,19 +1252,19 @@
         <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
         <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>7.8</v>
@@ -1273,40 +1273,40 @@
         <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>6.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>5.6</v>
@@ -1318,7 +1318,7 @@
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1327,14 +1327,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.8</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.7</v>
-      </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1389,7 +1389,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
@@ -1398,7 +1398,7 @@
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
@@ -1407,19 +1407,19 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
@@ -1428,28 +1428,28 @@
         <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
         <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
@@ -1458,7 +1458,7 @@
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
         <v>50</v>
@@ -1467,37 +1467,37 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1506,25 +1506,25 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BG4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
         <v>3.6</v>
@@ -1536,40 +1536,40 @@
         <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
         <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
         <v>6.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW4" t="n">
         <v>6.8</v>
@@ -1581,14 +1581,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I5" t="n">
         <v>6.6</v>
       </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1643,34 +1643,34 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="X5" t="n">
         <v>38</v>
@@ -1682,64 +1682,64 @@
         <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL5" t="n">
         <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
@@ -1748,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1757,92 +1757,92 @@
         <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC5" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="n">
         <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ5" t="n">
         <v>4.9</v>
       </c>
       <c r="BR5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS5" t="n">
         <v>6.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA5" t="n">
         <v>5.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>3.95</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1897,28 +1897,28 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.8</v>
@@ -1930,7 +1930,7 @@
         <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
         <v>16</v>
@@ -1942,10 +1942,10 @@
         <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1969,7 +1969,7 @@
         <v>50</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1981,10 +1981,10 @@
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
         <v>12</v>
@@ -1993,13 +1993,13 @@
         <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>19</v>
@@ -2014,43 +2014,43 @@
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
@@ -2062,13 +2062,13 @@
         <v>28</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
         <v>5.3</v>
@@ -2077,33 +2077,33 @@
         <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>FC Ararat Yerevan</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO8" t="n">
         <v>2.72</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X8" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH8" t="n">
+      <c r="BP8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
         <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="BV8" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BX8" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BY8" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,244 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>2.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.59</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA9" t="n">
         <v>42</v>
       </c>
-      <c r="AA9" t="n">
-        <v>120</v>
-      </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY9" t="n">
         <v>4.4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG9" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
         <v>3.7</v>
       </c>
       <c r="BL9" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.72</v>
+        <v>4.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BY9" t="n">
         <v>4.9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>9.4</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.49</v>
+        <v>5.3</v>
       </c>
       <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.5</v>
       </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>6.2</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X10" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="BE10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP10" t="n">
         <v>13</v>
       </c>
-      <c r="AE10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="BQ10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BR10" t="n">
         <v>26</v>
       </c>
-      <c r="AI10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BS10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="CA10" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>5</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>9.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>1.39</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>1.49</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.3</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="BC11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD11" t="n">
         <v>4.2</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BE11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="BF11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="BL11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BX11" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.73</v>
+        <v>3.05</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>2.36</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="n">
         <v>22</v>
       </c>
-      <c r="Z12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>19.5</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA12" t="n">
         <v>5.4</v>
       </c>
-      <c r="AR12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB12" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM12" t="n">
-        <v>14</v>
+        <v>5.3</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BT12" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BZ12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.7</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>1.71</v>
       </c>
       <c r="H13" t="n">
-        <v>1.75</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.76</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1.26</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>14</v>
       </c>
-      <c r="AA13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="BN13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR13" t="n">
         <v>27</v>
       </c>
-      <c r="AC13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BS13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>21</v>
       </c>
-      <c r="BB13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>75</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>13</v>
-      </c>
       <c r="CA13" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="X14" t="n">
         <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AA14" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>20</v>
       </c>
       <c r="AK14" t="n">
         <v>21</v>
       </c>
       <c r="AL14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX14" t="n">
         <v>40</v>
       </c>
-      <c r="AM14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY14" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>23</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.95</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
         <v>4.5</v>
       </c>
       <c r="O15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.23</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="n">
         <v>21</v>
       </c>
-      <c r="Y15" t="n">
-        <v>970</v>
-      </c>
       <c r="Z15" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
       </c>
       <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>16.5</v>
       </c>
-      <c r="AI15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AR15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD15" t="n">
         <v>26</v>
       </c>
-      <c r="AK15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="BE15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP15" t="n">
         <v>12</v>
       </c>
-      <c r="AO15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>17</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BW15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="CA15" t="n">
         <v>6.6</v>
       </c>
-      <c r="BX15" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>6</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -4404,187 +4404,187 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB16" t="n">
         <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK16" t="n">
         <v>21</v>
       </c>
-      <c r="AE16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO16" t="n">
         <v>90</v>
       </c>
-      <c r="AN16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>75</v>
-      </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="AS16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AV16" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
-        <v>26</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4593,31 +4593,31 @@
         <v>9</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BR16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS16" t="n">
         <v>7</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
         <v>8</v>
@@ -4626,17 +4626,17 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>1.73</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>1.74</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>2.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="Y17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG17" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AH17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>13</v>
       </c>
-      <c r="AC17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE17" t="n">
+      <c r="AS17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>80</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD17" t="n">
         <v>38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>26</v>
       </c>
       <c r="BE17" t="n">
         <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BG17" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BJ17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT17" t="n">
         <v>5.2</v>
       </c>
-      <c r="BL17" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BU17" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV17" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX17" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,244 +4907,244 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>15.5</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="J18" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.6</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.54</v>
-      </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="U18" t="n">
-        <v>1.61</v>
+        <v>2.58</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="X18" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>370</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AM18" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP18" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW18" t="n">
         <v>36</v>
       </c>
-      <c r="AR18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS18" t="n">
+      <c r="AX18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY18" t="n">
         <v>10</v>
       </c>
-      <c r="AT18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW18" t="n">
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BN18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BR18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BS18" t="n">
         <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -5166,184 +5166,184 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="H19" t="n">
-        <v>3.55</v>
+        <v>15.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>19.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="X19" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="AA19" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>9</v>
       </c>
-      <c r="AD19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>38</v>
-      </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS19" t="n">
         <v>10</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AT19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="AZ19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG19" t="n">
         <v>10</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB19" t="n">
+      <c r="BH19" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BI19" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BK19" t="n">
         <v>6.2</v>
@@ -5352,53 +5352,53 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="BP19" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>11</v>
       </c>
-      <c r="BT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA19" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -5420,239 +5420,239 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.17</v>
+        <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>1.23</v>
+        <v>2.36</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>3.55</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU20" t="n">
         <v>5.1</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>290</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>420</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY20" t="n">
+      <c r="BV20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>12</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>950</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ20" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -5669,244 +5669,244 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="G21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.4</v>
       </c>
-      <c r="H21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q21" t="n">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.73</v>
+        <v>5.4</v>
       </c>
       <c r="X21" t="n">
-        <v>9.4</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="AA21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AK21" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="AL21" t="n">
         <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>210</v>
+        <v>450</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>3.95</v>
       </c>
       <c r="AO21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AY21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD21" t="n">
         <v>10</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE21" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL21" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="BP21" t="n">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX21" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -5928,202 +5928,202 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS22" t="n">
         <v>5.9</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
         <v>10</v>
       </c>
-      <c r="Z22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AZ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC22" t="n">
         <v>22</v>
       </c>
-      <c r="AC22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD22" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BF22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="BJ22" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BK22" t="n">
         <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="BM22" t="n">
         <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="BQ22" t="n">
         <v>1.01</v>
@@ -6135,32 +6135,32 @@
         <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BW22" t="n">
         <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BY22" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="CA22" t="n">
         <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -6177,244 +6177,244 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.94</v>
+        <v>5.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>1.72</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="W23" t="n">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>150</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="AF23" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="AK23" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AM23" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="AO23" t="n">
-        <v>140</v>
+        <v>10.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
         <v>7.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AU23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX23" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG23" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH23" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="BJ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK23" t="n">
         <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="BM23" t="n">
         <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="BQ23" t="n">
         <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BS23" t="n">
         <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="BV23" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX23" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="BY23" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="CA23" t="n">
         <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -6431,244 +6431,498 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="G24" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="H24" t="n">
-        <v>9.4</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH24" t="n">
         <v>25</v>
       </c>
-      <c r="Y24" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>460</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AI24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>280</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AR24" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY24" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BE24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK24" t="n">
         <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM24" t="n">
         <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ24" t="n">
         <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS24" t="n">
         <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW24" t="n">
         <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY24" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA24" t="n">
         <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>450</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
@@ -881,206 +881,206 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AA2" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
         <v>16</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="AP2" t="n">
         <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG2" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.7</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>9.6</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CA2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="n">
         <v>2.76</v>
@@ -1126,7 +1126,7 @@
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1135,76 +1135,76 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
         <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1213,70 +1213,70 @@
         <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY3" t="n">
         <v>12</v>
       </c>
-      <c r="AS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB3" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC3" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG3" t="n">
         <v>9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>21</v>
       </c>
       <c r="BH3" t="n">
         <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1297,7 +1297,7 @@
         <v>4.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.4</v>
@@ -1309,10 +1309,10 @@
         <v>8.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1327,14 +1327,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
         <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
         <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -1389,7 +1389,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
@@ -1401,7 +1401,7 @@
         <v>1.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.35</v>
@@ -1410,52 +1410,52 @@
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>48</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
       </c>
       <c r="AK4" t="n">
         <v>32</v>
@@ -1464,13 +1464,13 @@
         <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
@@ -1479,116 +1479,116 @@
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="n">
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>6.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>34</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>27</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
         <v>1.58</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1643,19 +1643,19 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q5" t="n">
         <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S5" t="n">
         <v>2.28</v>
@@ -1664,22 +1664,22 @@
         <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
         <v>2.72</v>
       </c>
       <c r="X5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1688,10 +1688,10 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>80</v>
@@ -1703,43 +1703,43 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>390</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
         <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
@@ -1748,19 +1748,19 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1769,22 +1769,22 @@
         <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BH5" t="n">
         <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.800000000000001</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1885,13 +1885,13 @@
         <v>2.26</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1906,94 +1906,94 @@
         <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
         <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W6" t="n">
         <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
@@ -2002,108 +2002,108 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>15</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS6" t="n">
         <v>10</v>
       </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BT6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
         <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Slovakian Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Noah</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Ararat Yerevan</t>
+          <t>KFC Komarno</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2292,72 +2292,72 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>FC Ararat Yerevan</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.55</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.07</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.88</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>1.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG9" t="n">
         <v>14</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
         <v>32</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
       </c>
       <c r="AL9" t="n">
         <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX9" t="n">
         <v>11</v>
       </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="AY9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF9" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO9" t="n">
         <v>4</v>
       </c>
-      <c r="BI9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BP9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BR9" t="n">
         <v>38</v>
       </c>
       <c r="BS9" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BX9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>2.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA10" t="n">
         <v>42</v>
       </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
       <c r="AB10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP10" t="n">
         <v>12</v>
       </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AQ10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT10" t="n">
         <v>11</v>
       </c>
-      <c r="AH10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AU10" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AY10" t="n">
         <v>4.5</v>
       </c>
       <c r="AZ10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC10" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BD10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG10" t="n">
         <v>15.5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH10" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
         <v>3.7</v>
       </c>
       <c r="BL10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.72</v>
+        <v>4.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BR10" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BT10" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BY10" t="n">
         <v>4.9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>9.4</v>
+        <v>1.84</v>
       </c>
       <c r="H11" t="n">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.49</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV11" t="n">
         <v>16</v>
       </c>
-      <c r="Z11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP11" t="n">
         <v>13</v>
       </c>
-      <c r="AE11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="BQ11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BR11" t="n">
         <v>26</v>
       </c>
-      <c r="AI11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BS11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>19</v>
+      </c>
+      <c r="CA11" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>5</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>6.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05</v>
+        <v>9.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2.52</v>
+        <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>1.49</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>2.88</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AM12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="AO12" t="n">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="AP12" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV12" t="n">
+      <c r="BF12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BR12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="BV12" t="n">
-        <v>23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="G13" t="n">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>2.92</v>
       </c>
       <c r="J13" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
-        <v>2.38</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP13" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AZ13" t="n">
         <v>13</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="BA13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF13" t="n">
         <v>16.5</v>
       </c>
-      <c r="AR13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BG13" t="n">
         <v>16.5</v>
       </c>
-      <c r="BD13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM13" t="n">
-        <v>14</v>
+        <v>5.3</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BZ13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="I14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J14" t="n">
         <v>3.95</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN14" t="n">
         <v>4.3</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="BO14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>21</v>
       </c>
-      <c r="Y14" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>23</v>
-      </c>
       <c r="CA14" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR15" t="n">
         <v>21</v>
       </c>
-      <c r="AE15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AS15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF15" t="n">
         <v>10</v>
       </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="n">
         <v>4</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>10</v>
       </c>
-      <c r="BK15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
         <v>8.4</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>19</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
         <v>4.5</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
         <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="n">
         <v>60</v>
       </c>
-      <c r="AA16" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>85</v>
-      </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
         <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN16" t="n">
         <v>9.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG16" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BU16" t="n">
         <v>4.8</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.8</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>4.9</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>1.73</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.74</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
         <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.78</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.54</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>2.34</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="X17" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="Z17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB17" t="n">
         <v>14</v>
       </c>
-      <c r="AA17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP17" t="n">
         <v>11</v>
       </c>
-      <c r="AD17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="BQ17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR17" t="n">
         <v>25</v>
       </c>
-      <c r="AU17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY17" t="n">
+      <c r="BS17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>17.5</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>80</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>75</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>13</v>
-      </c>
       <c r="CA17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>4.8</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="H18" t="n">
-        <v>3.85</v>
+        <v>1.74</v>
       </c>
       <c r="I18" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="U18" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>2.34</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="X18" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA18" t="n">
         <v>19</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG18" t="n">
         <v>19</v>
       </c>
-      <c r="Z18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AH18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
         <v>13</v>
       </c>
-      <c r="AC18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AS18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX18" t="n">
         <v>40</v>
       </c>
-      <c r="AF18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV18" t="n">
+      <c r="AY18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="BC18" t="n">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="BD18" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BE18" t="n">
         <v>50</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BG18" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>75</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BO18" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BR18" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BS18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BY18" t="n">
         <v>7.6</v>
       </c>
-      <c r="BT18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ18" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5161,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>15.5</v>
+        <v>3.85</v>
       </c>
       <c r="I19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X19" t="n">
         <v>19.5</v>
       </c>
-      <c r="J19" t="n">
+      <c r="Y19" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU19" t="n">
         <v>6.4</v>
       </c>
-      <c r="K19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>190</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>370</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD19" t="n">
+      <c r="BV19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW19" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>10</v>
-      </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -5420,239 +5420,239 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.18</v>
+        <v>1.23</v>
       </c>
       <c r="G20" t="n">
-        <v>2.36</v>
+        <v>1.28</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.74</v>
+        <v>4.6</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="AA20" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>280</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>9</v>
       </c>
-      <c r="AD20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>38</v>
-      </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AL20" t="n">
         <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="AN20" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT20" t="n">
+      <c r="AZ20" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>17</v>
-      </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH20" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BI20" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="BP20" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>11</v>
       </c>
-      <c r="BT20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA20" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.17</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU21" t="n">
         <v>5.1</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>290</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>420</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR21" t="n">
+      <c r="BV21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA21" t="n">
         <v>11</v>
       </c>
-      <c r="AS21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>950</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -5923,244 +5923,244 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="G22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21</v>
+      </c>
+      <c r="I22" t="n">
+        <v>27</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.4</v>
       </c>
-      <c r="H22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="Q22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>310</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>460</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>490</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF22" t="n">
         <v>3.55</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="BG22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA22" t="n">
+      <c r="BZ22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CA22" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>250</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>60</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -6182,239 +6182,239 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="G23" t="n">
-        <v>6.8</v>
+        <v>2.42</v>
       </c>
       <c r="H23" t="n">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>250</v>
+      </c>
+      <c r="BM23" t="n">
         <v>5</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X23" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="BN23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV23" t="n">
         <v>48</v>
       </c>
-      <c r="AG23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>240</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>140</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>55</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR23" t="n">
+      <c r="BW23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ23" t="n">
         <v>60</v>
       </c>
-      <c r="BS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>22</v>
-      </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -6431,244 +6431,244 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.93</v>
+        <v>5.1</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>5.9</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>1.66</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>1.74</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="V24" t="n">
-        <v>1.23</v>
+        <v>2.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM24" t="n">
         <v>150</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AN24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR24" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AS24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU24" t="n">
         <v>8</v>
       </c>
-      <c r="AD24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AV24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>170</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ24" t="n">
+      <c r="BO24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV24" t="n">
         <v>13</v>
       </c>
-      <c r="BK24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>240</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>55</v>
-      </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BX24" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ24" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -6685,244 +6685,498 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="G25" t="n">
-        <v>1.41</v>
+        <v>2.12</v>
       </c>
       <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX25" t="n">
         <v>9.4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>450</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>7.4</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>46</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:24:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>450</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR26" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB25" t="n">
+      <c r="AS26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB26" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD25" t="n">
+      <c r="BC26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH26" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-05-18 06:08:13</t>
+      <c r="BI26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>200</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>120</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H2" t="n">
         <v>12</v>
@@ -908,7 +908,7 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -917,10 +917,10 @@
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA2" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -950,7 +950,7 @@
         <v>12</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -965,7 +965,7 @@
         <v>260</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ2" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
         <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -986,7 +986,7 @@
         <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
         <v>6.8</v>
@@ -995,10 +995,10 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
@@ -1007,10 +1007,10 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
         <v>3.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G3" t="n">
         <v>3.25</v>
@@ -1120,13 +1120,13 @@
         <v>2.54</v>
       </c>
       <c r="I3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1135,7 +1135,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.39</v>
@@ -1144,34 +1144,34 @@
         <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
         <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
         <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>42</v>
@@ -1213,7 +1213,7 @@
         <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
         <v>32</v>
@@ -1228,7 +1228,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1240,10 +1240,10 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1252,25 +1252,25 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>9</v>
       </c>
       <c r="BH3" t="n">
         <v>3.25</v>
@@ -1282,13 +1282,13 @@
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN3" t="n">
         <v>6.4</v>
@@ -1297,44 +1297,44 @@
         <v>4.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>5.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -1389,13 +1389,13 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
         <v>1.95</v>
@@ -1407,16 +1407,16 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>15</v>
@@ -1425,7 +1425,7 @@
         <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>46</v>
@@ -1434,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
@@ -1443,7 +1443,7 @@
         <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
@@ -1458,16 +1458,16 @@
         <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
         <v>26</v>
@@ -1482,7 +1482,7 @@
         <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1494,7 +1494,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,19 +1506,19 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.55</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="H5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
@@ -1643,7 +1643,7 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
@@ -1655,22 +1655,22 @@
         <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1679,7 +1679,7 @@
         <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1706,7 +1706,7 @@
         <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>390</v>
+        <v>570</v>
       </c>
       <c r="AJ5" t="n">
         <v>16</v>
@@ -1721,16 +1721,16 @@
         <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO5" t="n">
         <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
@@ -1769,10 +1769,10 @@
         <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
         <v>5.3</v>
@@ -1784,7 +1784,7 @@
         <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.800000000000001</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.31</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.34</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1933,142 +1933,142 @@
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AB6" t="n">
         <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL6" t="n">
         <v>55</v>
       </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
         <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP6" t="n">
         <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
         <v>5.2</v>
@@ -2077,26 +2077,26 @@
         <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
         <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
         <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>500</v>
@@ -2148,16 +2148,16 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.24</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,28 +2372,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Noah</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Ararat Yerevan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="G8" t="n">
         <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
         <v>500</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="R8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>MB Rouissat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>1.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.97</v>
+        <v>1.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>FC Ararat Yerevan</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>2.46</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.85</v>
+        <v>1.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,102 +3129,102 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3233,147 +3233,147 @@
         <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR11" t="n">
         <v>20</v>
       </c>
-      <c r="AL11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BD11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN11" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>110</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BO11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BP11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR11" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BX11" t="n">
         <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>1.07</v>
       </c>
       <c r="G12" t="n">
-        <v>9.6</v>
+        <v>990</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>1.49</v>
+        <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>6.4</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.02</v>
       </c>
-      <c r="N12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.88</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,90 +3637,90 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="G13" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB13" t="n">
         <v>15</v>
       </c>
-      <c r="Z13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>16</v>
-      </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
         <v>14</v>
@@ -3729,159 +3729,159 @@
         <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN13" t="n">
         <v>32</v>
       </c>
-      <c r="AL13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>23</v>
-      </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
         <v>11</v>
       </c>
-      <c r="AR13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF13" t="n">
         <v>20</v>
       </c>
-      <c r="AX13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>4.7</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BR13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV13" t="n">
         <v>22</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>23</v>
-      </c>
       <c r="BW13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>1.34</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>1.43</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>3.3</v>
       </c>
       <c r="W14" t="n">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="Y14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA14" t="n">
         <v>19</v>
       </c>
-      <c r="Z14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>16.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>14</v>
+        <v>3.75</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BY14" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.94</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.33</v>
@@ -4183,213 +4183,213 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="X15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>24</v>
       </c>
-      <c r="Y15" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA15" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,114 +4399,114 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="X16" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>34</v>
@@ -4515,135 +4515,135 @@
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
         <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV16" t="n">
         <v>44</v>
       </c>
-      <c r="AX16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>42</v>
-      </c>
       <c r="BW16" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
         <v>6.2</v>
       </c>
       <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
         <v>4.1</v>
       </c>
-      <c r="K17" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
         <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA17" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>85</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL17" t="n">
         <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE17" t="n">
         <v>16</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BZ17" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>1.74</v>
+        <v>3.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
         <v>4.6</v>
       </c>
-      <c r="K18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.8</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.5</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.78</v>
-      </c>
       <c r="S18" t="n">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>2.34</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="X18" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>14</v>
       </c>
-      <c r="AA18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="BA18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF18" t="n">
         <v>10</v>
       </c>
-      <c r="AE18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW18" t="n">
+      <c r="BG18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP18" t="n">
         <v>14</v>
       </c>
-      <c r="AX18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>85</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>75</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>32</v>
-      </c>
       <c r="BQ18" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BX18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BZ18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Oud-Heverlee Leuven</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
       </c>
       <c r="Y19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
         <v>19</v>
       </c>
-      <c r="Z19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>14</v>
-      </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO19" t="n">
         <v>60</v>
       </c>
-      <c r="AN19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>32</v>
-      </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
       </c>
       <c r="AV19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>15</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
         <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>50</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>10</v>
       </c>
-      <c r="BG19" t="n">
-        <v>28</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BK19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS19" t="n">
         <v>7.4</v>
       </c>
-      <c r="BL19" t="n">
-        <v>75</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>8</v>
-      </c>
       <c r="BT19" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV19" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BW19" t="n">
         <v>8.4</v>
       </c>
       <c r="BX19" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L20" t="n">
         <v>1.28</v>
       </c>
-      <c r="H20" t="n">
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X20" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP20" t="n">
         <v>16</v>
       </c>
-      <c r="I20" t="n">
+      <c r="AQ20" t="n">
         <v>19</v>
       </c>
-      <c r="J20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="AR20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK20" t="n">
         <v>5.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X20" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>280</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN20" t="n">
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN20" t="n">
         <v>4.5</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK20" t="n">
+      <c r="BO20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP20" t="n">
         <v>11</v>
       </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>7</v>
-      </c>
       <c r="BQ20" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BR20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BS20" t="n">
         <v>7.2</v>
       </c>
       <c r="BT20" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA20" t="n">
         <v>6.4</v>
       </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>5.2</v>
-      </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.18</v>
+        <v>4.8</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>1.72</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>2.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="S21" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z21" t="n">
         <v>14</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH21" t="n">
         <v>15</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AI21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>85</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BP21" t="n">
         <v>32</v>
       </c>
-      <c r="AA21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="BQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX21" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY21" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>1.22</v>
+        <v>990</v>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>990</v>
       </c>
       <c r="J22" t="n">
-        <v>7.6</v>
+        <v>1.06</v>
       </c>
       <c r="K22" t="n">
-        <v>9.6</v>
+        <v>500</v>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
         <v>1.04</v>
       </c>
-      <c r="N22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>310</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>490</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BJ22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,244 +6177,244 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.42</v>
       </c>
-      <c r="H23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.52</v>
-      </c>
       <c r="Q23" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>5.3</v>
+        <v>2.64</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA23" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX23" t="n">
         <v>14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.3</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.1</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>26</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.3</v>
+        <v>28</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="BJ23" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL23" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="BM23" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP23" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR23" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV23" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="BW23" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX23" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="BY23" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ23" t="n">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -6431,244 +6431,244 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N24" t="n">
         <v>5.1</v>
       </c>
-      <c r="G24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.05</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.34</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>390</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>280</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
         <v>10</v>
       </c>
-      <c r="AA24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO24" t="n">
+      <c r="BN24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>11</v>
       </c>
-      <c r="AP24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>170</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>65</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>70</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>13</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>24</v>
-      </c>
       <c r="CA24" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -6685,244 +6685,244 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="G25" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AK25" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AN25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>6.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD25" t="n">
-        <v>44</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ25" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>240</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BN25" t="n">
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU25" t="n">
         <v>5.1</v>
       </c>
-      <c r="BO25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>6</v>
-      </c>
       <c r="BV25" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="BZ25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="CA25" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -6939,244 +6939,1260 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="G26" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="H26" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="K26" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.7</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.85</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="AA26" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AD26" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>150</v>
+        <v>460</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>490</v>
       </c>
       <c r="AN26" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AO26" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS26" t="n">
         <v>4.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA26" t="n">
         <v>4.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
         <v>4.7</v>
       </c>
       <c r="BF26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:42:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
         <v>4.2</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>250</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY27" t="n">
         <v>4.7</v>
       </c>
-      <c r="BH26" t="n">
+      <c r="BZ27" t="n">
+        <v>60</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:42:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X28" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>170</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:42:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>46</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:42:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>440</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS30" t="n">
         <v>4.8</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="AT30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI30" t="n">
         <v>3.2</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BJ30" t="n">
         <v>14.5</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BK30" t="n">
         <v>3.65</v>
       </c>
-      <c r="BL26" t="n">
+      <c r="BL30" t="n">
         <v>200</v>
       </c>
-      <c r="BM26" t="n">
+      <c r="BM30" t="n">
         <v>4.7</v>
       </c>
-      <c r="BN26" t="n">
+      <c r="BN30" t="n">
         <v>4.4</v>
       </c>
-      <c r="BO26" t="n">
+      <c r="BO30" t="n">
         <v>3</v>
       </c>
-      <c r="BP26" t="n">
+      <c r="BP30" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BQ26" t="n">
+      <c r="BQ30" t="n">
         <v>5.8</v>
       </c>
-      <c r="BR26" t="n">
+      <c r="BR30" t="n">
         <v>29</v>
       </c>
-      <c r="BS26" t="n">
+      <c r="BS30" t="n">
         <v>4.1</v>
       </c>
-      <c r="BT26" t="n">
+      <c r="BT30" t="n">
         <v>16.5</v>
       </c>
-      <c r="BU26" t="n">
+      <c r="BU30" t="n">
         <v>3.75</v>
       </c>
-      <c r="BV26" t="n">
+      <c r="BV30" t="n">
         <v>120</v>
       </c>
-      <c r="BW26" t="n">
+      <c r="BW30" t="n">
         <v>4.6</v>
       </c>
-      <c r="BX26" t="n">
+      <c r="BX30" t="n">
         <v>110</v>
       </c>
-      <c r="BY26" t="n">
+      <c r="BY30" t="n">
         <v>4.6</v>
       </c>
-      <c r="BZ26" t="n">
+      <c r="BZ30" t="n">
         <v>15.5</v>
       </c>
-      <c r="CA26" t="n">
+      <c r="CA30" t="n">
         <v>3.7</v>
       </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-05-18 08:24:12</t>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -872,7 +872,7 @@
         <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
@@ -887,7 +887,7 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
         <v>1.51</v>
@@ -896,13 +896,13 @@
         <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>2.54</v>
       </c>
       <c r="I3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>3.5</v>
@@ -1141,7 +1141,7 @@
         <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -1156,16 +1156,16 @@
         <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1228,7 +1228,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1240,7 +1240,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1252,7 +1252,7 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1267,37 +1267,37 @@
         <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN3" t="n">
         <v>6.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.2</v>
@@ -1306,19 +1306,19 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>5.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>36</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
         <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I4" t="n">
         <v>2.96</v>
@@ -1380,7 +1380,7 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1398,7 +1398,7 @@
         <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
@@ -1410,7 +1410,7 @@
         <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
         <v>1.51</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
@@ -1679,7 +1679,7 @@
         <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1697,7 +1697,7 @@
         <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
         <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="AJ5" t="n">
         <v>16</v>
@@ -1727,10 +1727,10 @@
         <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I6" t="n">
         <v>2.08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1897,16 +1897,16 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1915,16 +1915,16 @@
         <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1933,7 +1933,7 @@
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>24</v>
@@ -1942,16 +1942,16 @@
         <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AG6" t="n">
         <v>18</v>
@@ -1978,13 +1978,13 @@
         <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR6" t="n">
         <v>12</v>
@@ -2005,7 +2005,7 @@
         <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -2020,7 +2020,7 @@
         <v>34</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD6" t="n">
         <v>28</v>
@@ -2032,7 +2032,7 @@
         <v>25</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="n">
         <v>3.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>990</v>
@@ -2148,22 +2148,22 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q7" t="n">
         <v>1.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
         <v>1.23</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>1.64</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.46</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.21</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>1.21</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2432,7 +2432,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2635,112 +2635,112 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.08</v>
       </c>
-      <c r="G9" t="n">
-        <v>990</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>990</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K9" t="n">
-        <v>500</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2770,7 +2770,7 @@
         <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ9" t="n">
         <v>1.01</v>
@@ -2797,68 +2797,68 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
         <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM9" t="n">
         <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO9" t="n">
         <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
         <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU9" t="n">
         <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
         <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA9" t="n">
         <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>1.03</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>1.52</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>990</v>
@@ -2910,25 +2910,25 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="S10" t="n">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G11" t="n">
         <v>2.48</v>
@@ -3152,16 +3152,16 @@
         <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
         <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
         <v>990</v>
       </c>
       <c r="H12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
         <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
         <v>500</v>
@@ -3418,7 +3418,7 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
         <v>1.25</v>
@@ -3430,13 +3430,13 @@
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="R12" t="n">
         <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
         <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
         <v>2.04</v>
@@ -3699,10 +3699,10 @@
         <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X13" t="n">
         <v>18.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="J14" t="n">
         <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
@@ -3935,37 +3935,37 @@
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AA14" t="n">
         <v>13.5</v>
@@ -3983,7 +3983,7 @@
         <v>14.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AG14" t="n">
         <v>38</v>
@@ -3992,13 +3992,13 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AK14" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AL14" t="n">
         <v>95</v>
@@ -4007,25 +4007,25 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AO14" t="n">
         <v>4.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
         <v>12</v>
@@ -4034,101 +4034,101 @@
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5</v>
       </c>
       <c r="BA14" t="n">
         <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BI14" t="n">
         <v>3.85</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BN14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT14" t="n">
         <v>4.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV14" t="n">
         <v>8.6</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BX14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>10.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.45</v>
@@ -4207,10 +4207,10 @@
         <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -4413,58 +4413,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
         <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R16" t="n">
         <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
         <v>25</v>
@@ -4545,7 +4545,7 @@
         <v>6.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>8.800000000000001</v>
@@ -4557,7 +4557,7 @@
         <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
         <v>14.5</v>
@@ -4575,28 +4575,28 @@
         <v>6.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL16" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM16" t="n">
         <v>5.4</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP16" t="n">
         <v>12.5</v>
@@ -4611,19 +4611,19 @@
         <v>4.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW16" t="n">
         <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.9</v>
@@ -4685,7 +4685,7 @@
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4697,7 +4697,7 @@
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -4709,7 +4709,7 @@
         <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U17" t="n">
         <v>1.97</v>
@@ -4724,37 +4724,37 @@
         <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
         <v>46</v>
       </c>
       <c r="AA17" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
         <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="n">
         <v>17</v>
@@ -4766,7 +4766,7 @@
         <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
         <v>11</v>
@@ -4775,64 +4775,64 @@
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>17.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
         <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB17" t="n">
         <v>15</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>15.5</v>
       </c>
       <c r="BC17" t="n">
         <v>16.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BE17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="n">
         <v>3.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4850,7 +4850,7 @@
         <v>4.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP17" t="n">
         <v>11.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
         <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.33</v>
@@ -4945,34 +4945,34 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
         <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
         <v>24</v>
@@ -4990,7 +4990,7 @@
         <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
         <v>19</v>
@@ -5074,7 +5074,7 @@
         <v>5.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
@@ -5137,14 +5137,14 @@
         <v>10</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="CA18" t="n">
         <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
         <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -5202,34 +5202,34 @@
         <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
         <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
         <v>2.22</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
         <v>20</v>
@@ -5238,7 +5238,7 @@
         <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
@@ -5268,10 +5268,10 @@
         <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
         <v>90</v>
@@ -5289,10 +5289,10 @@
         <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5316,7 +5316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB19" t="n">
         <v>16.5</v>
@@ -5328,25 +5328,25 @@
         <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,10 +5355,10 @@
         <v>9.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP19" t="n">
         <v>12</v>
@@ -5367,38 +5367,38 @@
         <v>5.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY19" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX19" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BZ19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA19" t="n">
         <v>6.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H20" t="n">
         <v>5.9</v>
@@ -5441,10 +5441,10 @@
         <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.28</v>
@@ -5459,16 +5459,16 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
         <v>1.78</v>
@@ -5480,7 +5480,7 @@
         <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
         <v>23</v>
@@ -5498,7 +5498,7 @@
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
         <v>26</v>
@@ -5507,7 +5507,7 @@
         <v>85</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -5519,19 +5519,19 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK20" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>20</v>
       </c>
       <c r="AL20" t="n">
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO20" t="n">
         <v>90</v>
@@ -5543,10 +5543,10 @@
         <v>19</v>
       </c>
       <c r="AR20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS20" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.8</v>
       </c>
       <c r="AT20" t="n">
         <v>9</v>
@@ -5558,7 +5558,7 @@
         <v>18.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -5570,37 +5570,37 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
         <v>14</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5618,13 +5618,13 @@
         <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT20" t="n">
         <v>9.800000000000001</v>
@@ -5636,7 +5636,7 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
@@ -5645,14 +5645,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -5689,10 +5689,10 @@
         <v>4.9</v>
       </c>
       <c r="H21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="J21" t="n">
         <v>4.6</v>
@@ -5731,10 +5731,10 @@
         <v>2.8</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>32</v>
@@ -5746,10 +5746,10 @@
         <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
@@ -5764,7 +5764,7 @@
         <v>44</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH21" t="n">
         <v>15</v>
@@ -5800,7 +5800,7 @@
         <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT21" t="n">
         <v>26</v>
@@ -5827,7 +5827,7 @@
         <v>21</v>
       </c>
       <c r="BB21" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BC21" t="n">
         <v>40</v>
@@ -5842,71 +5842,71 @@
         <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL21" t="n">
         <v>75</v>
       </c>
       <c r="BM21" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BN21" t="n">
         <v>9</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ21" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BT21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV21" t="n">
         <v>11</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX21" t="n">
         <v>19.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BZ21" t="n">
         <v>12.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -5937,46 +5937,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>990</v>
+        <v>3.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.06</v>
+        <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>990</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1.06</v>
+        <v>2.16</v>
       </c>
       <c r="K22" t="n">
-        <v>500</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O22" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -5985,118 +5985,118 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA22" t="n">
         <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE22" t="n">
         <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -6215,22 +6215,22 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
         <v>1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S23" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
         <v>1.6</v>
@@ -6245,7 +6245,7 @@
         <v>1.9</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y23" t="n">
         <v>18.5</v>
@@ -6269,13 +6269,13 @@
         <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI23" t="n">
         <v>40</v>
@@ -6305,7 +6305,7 @@
         <v>18</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>60</v>
@@ -6329,7 +6329,7 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>36</v>
@@ -6377,7 +6377,7 @@
         <v>4.7</v>
       </c>
       <c r="BP23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ23" t="n">
         <v>6.6</v>
@@ -6386,7 +6386,7 @@
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23" t="n">
         <v>7.6</v>
@@ -6404,7 +6404,7 @@
         <v>34</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ23" t="n">
         <v>17.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -6451,19 +6451,19 @@
         <v>1.28</v>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I24" t="n">
         <v>18.5</v>
       </c>
       <c r="J24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
@@ -6478,13 +6478,13 @@
         <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R24" t="n">
         <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
         <v>2.32</v>
@@ -6496,7 +6496,7 @@
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="X24" t="n">
         <v>28</v>
@@ -6511,10 +6511,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD24" t="n">
         <v>950</v>
@@ -6532,7 +6532,7 @@
         <v>44</v>
       </c>
       <c r="AI24" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AJ24" t="n">
         <v>9</v>
@@ -6547,7 +6547,7 @@
         <v>300</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -6559,22 +6559,22 @@
         <v>38</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW24" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>6.2</v>
@@ -6583,28 +6583,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC24" t="n">
         <v>12.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="n">
         <v>4.4</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G25" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.65</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.55</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -6729,7 +6729,7 @@
         <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q25" t="n">
         <v>2.3</v>
@@ -6738,10 +6738,10 @@
         <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U25" t="n">
         <v>1.96</v>
@@ -6750,13 +6750,13 @@
         <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
         <v>32</v>
@@ -6813,10 +6813,10 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -6828,7 +6828,7 @@
         <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -6837,13 +6837,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
         <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>4.2</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -6858,7 +6858,7 @@
         <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH25" t="n">
         <v>3.05</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.18</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I26" t="n">
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -6977,13 +6977,13 @@
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
         <v>1.6</v>
@@ -6992,19 +6992,19 @@
         <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
         <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X26" t="n">
         <v>30</v>
@@ -7013,7 +7013,7 @@
         <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
@@ -7040,7 +7040,7 @@
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="AJ26" t="n">
         <v>9.4</v>
@@ -7076,10 +7076,10 @@
         <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW26" t="n">
         <v>4.8</v>
@@ -7088,7 +7088,7 @@
         <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
         <v>4.4</v>
@@ -7106,7 +7106,7 @@
         <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF26" t="n">
         <v>3.55</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -7207,25 +7207,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
         <v>3.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
         <v>1.12</v>
@@ -7237,7 +7237,7 @@
         <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q27" t="n">
         <v>2.56</v>
@@ -7249,7 +7249,7 @@
         <v>5.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
         <v>1.76</v>
@@ -7258,7 +7258,7 @@
         <v>1.32</v>
       </c>
       <c r="W27" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
@@ -7315,7 +7315,7 @@
         <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ27" t="n">
         <v>9</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -7464,16 +7464,16 @@
         <v>5.4</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="I28" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
         <v>4.5</v>
@@ -7494,7 +7494,7 @@
         <v>1.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R28" t="n">
         <v>1.35</v>
@@ -7503,16 +7503,16 @@
         <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U28" t="n">
         <v>1.82</v>
       </c>
       <c r="V28" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -7521,16 +7521,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB28" t="n">
         <v>22</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>11.5</v>
@@ -7551,7 +7551,7 @@
         <v>42</v>
       </c>
       <c r="AJ28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK28" t="n">
         <v>90</v>
@@ -7617,7 +7617,7 @@
         <v>7.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG28" t="n">
         <v>9</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
@@ -7760,7 +7760,7 @@
         <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
         <v>1.24</v>
@@ -7853,13 +7853,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA29" t="n">
         <v>8.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC29" t="n">
         <v>19.5</v>
@@ -7925,7 +7925,7 @@
         <v>5.5</v>
       </c>
       <c r="BX29" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BY29" t="n">
         <v>5.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -7972,79 +7972,79 @@
         <v>1.36</v>
       </c>
       <c r="G30" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
         <v>11.5</v>
       </c>
       <c r="J30" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K30" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
         <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R30" t="n">
         <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z30" t="n">
         <v>110</v>
       </c>
       <c r="AA30" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE30" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
@@ -8053,7 +8053,7 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="n">
         <v>150</v>
@@ -8068,34 +8068,34 @@
         <v>48</v>
       </c>
       <c r="AM30" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN30" t="n">
         <v>6.6</v>
       </c>
       <c r="AO30" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AP30" t="n">
-        <v>17.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AR30" t="n">
         <v>4.7</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT30" t="n">
         <v>8.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW30" t="n">
         <v>4.8</v>
@@ -8104,13 +8104,13 @@
         <v>7.4</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB30" t="n">
         <v>9.6</v>
@@ -8119,16 +8119,16 @@
         <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
         <v>4.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH30" t="n">
         <v>4.8</v>
@@ -8143,10 +8143,10 @@
         <v>3.65</v>
       </c>
       <c r="BL30" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN30" t="n">
         <v>4.4</v>
@@ -8164,35 +8164,35 @@
         <v>29</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT30" t="n">
         <v>16.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV30" t="n">
         <v>120</v>
       </c>
       <c r="BW30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX30" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA30" t="n">
         <v>3.7</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G2" t="n">
         <v>1.31</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
         <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -884,31 +884,31 @@
         <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -917,10 +917,10 @@
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA2" t="n">
-        <v>530</v>
+        <v>450</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -929,10 +929,10 @@
         <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE2" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AF2" t="n">
         <v>10.5</v>
@@ -941,10 +941,10 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
         <v>12</v>
@@ -956,25 +956,25 @@
         <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -983,10 +983,10 @@
         <v>13.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
         <v>6.8</v>
@@ -995,10 +995,10 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
@@ -1007,22 +1007,22 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BI2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
@@ -1034,19 +1034,19 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1055,32 +1055,32 @@
         <v>9</v>
       </c>
       <c r="BT2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.98</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I3" t="n">
         <v>2.74</v>
@@ -1126,40 +1126,40 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
         <v>1.46</v>
@@ -1177,10 +1177,10 @@
         <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1228,7 +1228,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>9.6</v>
@@ -1243,7 +1243,7 @@
         <v>8.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1267,7 +1267,7 @@
         <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
         <v>9.199999999999999</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.68</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.76</v>
-      </c>
       <c r="H4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1389,16 +1389,16 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
@@ -1410,25 +1410,25 @@
         <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
         <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
@@ -1443,10 +1443,10 @@
         <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>16.5</v>
@@ -1455,10 +1455,10 @@
         <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
         <v>42</v>
@@ -1467,19 +1467,19 @@
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
         <v>24</v>
@@ -1488,7 +1488,7 @@
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
@@ -1509,13 +1509,13 @@
         <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
         <v>36</v>
@@ -1542,53 +1542,53 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO4" t="n">
         <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW4" t="n">
         <v>7.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>27</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G5" t="n">
         <v>1.55</v>
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1667,7 +1667,7 @@
         <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
         <v>2.8</v>
@@ -1679,7 +1679,7 @@
         <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>330</v>
+        <v>470</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1688,10 +1688,10 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>80</v>
@@ -1706,7 +1706,7 @@
         <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
         <v>16</v>
@@ -1730,16 +1730,16 @@
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
         <v>44</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
@@ -1754,13 +1754,13 @@
         <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1778,7 +1778,7 @@
         <v>5.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
@@ -1903,10 +1903,10 @@
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1915,16 +1915,16 @@
         <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1933,7 +1933,7 @@
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
         <v>24</v>
@@ -1951,13 +1951,13 @@
         <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG6" t="n">
         <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
         <v>40</v>
@@ -1999,13 +1999,13 @@
         <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -2020,7 +2020,7 @@
         <v>34</v>
       </c>
       <c r="BC6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
         <v>28</v>
@@ -2032,7 +2032,7 @@
         <v>25</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -2127,112 +2127,112 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>990</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2289,68 +2289,68 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
         <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM7" t="n">
         <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
         <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7" t="n">
         <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
         <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
         <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
         <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2447,37 +2447,37 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2543,13 +2543,13 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BK8" t="n">
         <v>1.04</v>
@@ -2561,25 +2561,25 @@
         <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS8" t="n">
         <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU8" t="n">
         <v>1.04</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
@@ -2677,10 +2677,10 @@
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
@@ -2701,13 +2701,13 @@
         <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>85</v>
@@ -2728,73 +2728,73 @@
         <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
         <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO9" t="n">
         <v>110</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.55</v>
@@ -2806,59 +2806,59 @@
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL9" t="n">
         <v>180</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN9" t="n">
         <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BP9" t="n">
         <v>16</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR9" t="n">
         <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT9" t="n">
         <v>9.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV9" t="n">
         <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX9" t="n">
         <v>65</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.52</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
         <v>990</v>
@@ -2916,19 +2916,19 @@
         <v>2.94</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P10" t="n">
         <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -3149,28 +3149,28 @@
         <v>2.48</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P11" t="n">
         <v>1.88</v>
@@ -3185,7 +3185,7 @@
         <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
         <v>2.12</v>
@@ -3194,7 +3194,7 @@
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
@@ -3305,7 +3305,7 @@
         <v>4.1</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BI11" t="n">
         <v>2.68</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3332,13 +3332,13 @@
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
         <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT11" t="n">
         <v>7.8</v>
@@ -3347,26 +3347,26 @@
         <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -3397,112 +3397,112 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="G12" t="n">
-        <v>990</v>
+        <v>1.63</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>1.49</v>
       </c>
       <c r="I12" t="n">
-        <v>990</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>2.76</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.11</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
         <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J13" t="n">
         <v>3.45</v>
@@ -3684,7 +3684,7 @@
         <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
@@ -3699,10 +3699,10 @@
         <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
         <v>18.5</v>
@@ -3753,7 +3753,7 @@
         <v>95</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
         <v>24</v>
@@ -3804,7 +3804,7 @@
         <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
@@ -3816,7 +3816,7 @@
         <v>4</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
@@ -3852,7 +3852,7 @@
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>22</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -3905,52 +3905,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="I14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
         <v>3.4</v>
@@ -3974,10 +3974,10 @@
         <v>46</v>
       </c>
       <c r="AC14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
         <v>14.5</v>
@@ -3989,16 +3989,16 @@
         <v>38</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AK14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL14" t="n">
         <v>95</v>
@@ -4007,82 +4007,82 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA14" t="n">
         <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI14" t="n">
         <v>3.85</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BN14" t="n">
         <v>13</v>
@@ -4091,44 +4091,44 @@
         <v>4.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ14" t="n">
         <v>6.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BX14" t="n">
         <v>21</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
         <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
@@ -4458,13 +4458,13 @@
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X16" t="n">
         <v>25</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.4</v>
@@ -4691,19 +4691,19 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
         <v>3.65</v>
@@ -4712,185 +4712,185 @@
         <v>1.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="X17" t="n">
         <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU17" t="n">
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>12</v>
       </c>
       <c r="BE17" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO17" t="n">
         <v>3.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BT17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -4927,19 +4927,19 @@
         <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -5074,7 +5074,7 @@
         <v>5.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.29</v>
@@ -5208,28 +5208,28 @@
         <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
         <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
         <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
         <v>20</v>
@@ -5238,13 +5238,13 @@
         <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
         <v>20</v>
@@ -5280,19 +5280,19 @@
         <v>9.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5301,7 +5301,7 @@
         <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW19" t="n">
         <v>44</v>
@@ -5316,7 +5316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
         <v>16.5</v>
@@ -5328,13 +5328,13 @@
         <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
         <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G20" t="n">
         <v>1.66</v>
       </c>
       <c r="H20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
         <v>6.6</v>
@@ -5447,7 +5447,7 @@
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5459,22 +5459,22 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
         <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
         <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
         <v>1.18</v>
@@ -5537,7 +5537,7 @@
         <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
         <v>19</v>
@@ -5546,10 +5546,10 @@
         <v>4.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
@@ -5570,10 +5570,10 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
         <v>14</v>
@@ -5585,7 +5585,7 @@
         <v>4.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG20" t="n">
         <v>4.6</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
@@ -5627,22 +5627,22 @@
         <v>7</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>17</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -5689,16 +5689,16 @@
         <v>4.9</v>
       </c>
       <c r="H21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.73</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.74</v>
       </c>
       <c r="J21" t="n">
         <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.26</v>
@@ -5719,7 +5719,7 @@
         <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
         <v>2.22</v>
@@ -5731,25 +5731,25 @@
         <v>2.8</v>
       </c>
       <c r="V21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="W21" t="n">
         <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y21" t="n">
         <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" t="n">
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
@@ -5764,7 +5764,7 @@
         <v>44</v>
       </c>
       <c r="AG21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH21" t="n">
         <v>15</v>
@@ -5797,7 +5797,7 @@
         <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS21" t="n">
         <v>18.5</v>
@@ -5818,7 +5818,7 @@
         <v>40</v>
       </c>
       <c r="AY21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
         <v>14.5</v>
@@ -5827,10 +5827,10 @@
         <v>21</v>
       </c>
       <c r="BB21" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BC21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD21" t="n">
         <v>38</v>
@@ -5845,7 +5845,7 @@
         <v>6.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI21" t="n">
         <v>3.75</v>
@@ -5854,13 +5854,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL21" t="n">
         <v>75</v>
       </c>
       <c r="BM21" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN21" t="n">
         <v>9</v>
@@ -5869,34 +5869,34 @@
         <v>6.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT21" t="n">
         <v>5.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BV21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX21" t="n">
         <v>19.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ21" t="n">
         <v>12.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="H22" t="n">
         <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J22" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="K22" t="n">
         <v>4.7</v>
@@ -5961,13 +5961,13 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P22" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
         <v>1.5</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X22" t="n">
         <v>29</v>
@@ -6000,7 +6000,7 @@
         <v>34</v>
       </c>
       <c r="AA22" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
         <v>21</v>
@@ -6009,46 +6009,46 @@
         <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
         <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH22" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AI22" t="n">
-        <v>280</v>
+        <v>180</v>
       </c>
       <c r="AJ22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AL22" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AM22" t="n">
-        <v>690</v>
+        <v>440</v>
       </c>
       <c r="AN22" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="AO22" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR22" t="n">
         <v>13</v>
@@ -6057,7 +6057,7 @@
         <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU22" t="n">
         <v>5.8</v>
@@ -6069,10 +6069,10 @@
         <v>1.05</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>11.5</v>
@@ -6081,7 +6081,7 @@
         <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
         <v>14.5</v>
@@ -6093,7 +6093,7 @@
         <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG22" t="n">
         <v>9.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.08</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.85</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.32</v>
@@ -6218,40 +6218,40 @@
         <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
         <v>1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
         <v>18.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
         <v>70</v>
@@ -6263,22 +6263,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
         <v>25</v>
@@ -6293,7 +6293,7 @@
         <v>60</v>
       </c>
       <c r="AN23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>32</v>
@@ -6305,7 +6305,7 @@
         <v>18</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>60</v>
@@ -6314,16 +6314,16 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -6335,10 +6335,10 @@
         <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
         <v>26</v>
@@ -6350,7 +6350,7 @@
         <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH23" t="n">
         <v>4.2</v>
@@ -6365,7 +6365,7 @@
         <v>7.4</v>
       </c>
       <c r="BL23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BM23" t="n">
         <v>10.5</v>
@@ -6380,7 +6380,7 @@
         <v>14</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="G24" t="n">
         <v>1.28</v>
@@ -6454,13 +6454,13 @@
         <v>15.5</v>
       </c>
       <c r="I24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.26</v>
@@ -6469,7 +6469,7 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
@@ -6478,25 +6478,25 @@
         <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R24" t="n">
         <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T24" t="n">
         <v>2.32</v>
       </c>
       <c r="U24" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="X24" t="n">
         <v>28</v>
@@ -6547,7 +6547,7 @@
         <v>300</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -6559,10 +6559,10 @@
         <v>38</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
@@ -6571,10 +6571,10 @@
         <v>13</v>
       </c>
       <c r="AV24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW24" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
         <v>6.2</v>
@@ -6583,10 +6583,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB24" t="n">
         <v>7.4</v>
@@ -6595,16 +6595,16 @@
         <v>12.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF24" t="n">
         <v>3.85</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH24" t="n">
         <v>4.4</v>
@@ -6616,13 +6616,13 @@
         <v>15</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN24" t="n">
         <v>3.7</v>
@@ -6631,7 +6631,7 @@
         <v>3.15</v>
       </c>
       <c r="BP24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BQ24" t="n">
         <v>5.7</v>
@@ -6640,35 +6640,35 @@
         <v>27</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT24" t="n">
         <v>18.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
         <v>10</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BZ24" t="n">
         <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>2.22</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
         <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -6747,10 +6747,10 @@
         <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
@@ -6762,7 +6762,7 @@
         <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB25" t="n">
         <v>8.4</v>
@@ -6771,7 +6771,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>65</v>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD25" t="n">
         <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF25" t="n">
         <v>17</v>
@@ -6870,7 +6870,7 @@
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6882,7 +6882,7 @@
         <v>5</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP25" t="n">
         <v>18</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>1.21</v>
       </c>
       <c r="H26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I26" t="n">
         <v>27</v>
@@ -6968,7 +6968,7 @@
         <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -7136,13 +7136,13 @@
         <v>3.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BP26" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -7210,34 +7210,34 @@
         <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H27" t="n">
         <v>3.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
         <v>3.1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="M27" t="n">
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O27" t="n">
         <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q27" t="n">
         <v>2.56</v>
@@ -7249,16 +7249,16 @@
         <v>5.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
         <v>1.32</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
@@ -7282,7 +7282,7 @@
         <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="n">
         <v>15.5</v>
@@ -7294,7 +7294,7 @@
         <v>32</v>
       </c>
       <c r="AI27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
         <v>40</v>
@@ -7303,7 +7303,7 @@
         <v>40</v>
       </c>
       <c r="AL27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM27" t="n">
         <v>230</v>
@@ -7324,13 +7324,13 @@
         <v>4</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
         <v>14</v>
@@ -7345,10 +7345,10 @@
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB27" t="n">
         <v>4.1</v>
@@ -7360,31 +7360,31 @@
         <v>4.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF27" t="n">
         <v>4.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ27" t="n">
         <v>13.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL27" t="n">
         <v>250</v>
       </c>
       <c r="BM27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN27" t="n">
         <v>5.8</v>
@@ -7393,10 +7393,10 @@
         <v>3.8</v>
       </c>
       <c r="BP27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR27" t="n">
         <v>55</v>
@@ -7411,10 +7411,10 @@
         <v>5.2</v>
       </c>
       <c r="BV27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX27" t="n">
         <v>75</v>
@@ -7426,11 +7426,11 @@
         <v>60</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H28" t="n">
         <v>1.67</v>
       </c>
       <c r="I28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J28" t="n">
         <v>4.2</v>
@@ -7485,25 +7485,25 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
         <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
         <v>1.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
         <v>1.82</v>
@@ -7521,7 +7521,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA28" t="n">
         <v>17</v>
@@ -7530,22 +7530,22 @@
         <v>22</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD28" t="n">
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF28" t="n">
         <v>46</v>
       </c>
       <c r="AG28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
         <v>42</v>
@@ -7566,13 +7566,13 @@
         <v>110</v>
       </c>
       <c r="AO28" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>8</v>
@@ -7581,19 +7581,19 @@
         <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY28" t="n">
         <v>19.5</v>
@@ -7605,58 +7605,58 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BH28" t="n">
         <v>4.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ28" t="n">
         <v>12.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BN28" t="n">
         <v>11.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP28" t="n">
         <v>65</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR28" t="n">
         <v>70</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT28" t="n">
         <v>4.9</v>
@@ -7665,26 +7665,26 @@
         <v>3.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW28" t="n">
         <v>8</v>
       </c>
       <c r="BX28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BZ28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G29" t="n">
         <v>2.12</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>3.25</v>
@@ -7733,7 +7733,7 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
@@ -7742,7 +7742,7 @@
         <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P29" t="n">
         <v>1.57</v>
@@ -7760,7 +7760,7 @@
         <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="V29" t="n">
         <v>1.24</v>
@@ -7784,7 +7784,7 @@
         <v>7</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
         <v>21</v>
@@ -7829,10 +7829,10 @@
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29" t="n">
         <v>5.9</v>
@@ -7844,7 +7844,7 @@
         <v>16.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -7856,10 +7856,10 @@
         <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>19.5</v>
@@ -7868,13 +7868,13 @@
         <v>44</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF29" t="n">
         <v>17.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH29" t="n">
         <v>3.15</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -7969,58 +7969,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="I30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S30" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T30" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V30" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -8044,19 +8044,19 @@
         <v>40</v>
       </c>
       <c r="AE30" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>32</v>
       </c>
       <c r="AI30" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ30" t="n">
         <v>13</v>
@@ -8065,7 +8065,7 @@
         <v>18</v>
       </c>
       <c r="AL30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM30" t="n">
         <v>180</v>
@@ -8083,22 +8083,22 @@
         <v>5</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
         <v>8.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV30" t="n">
         <v>4.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX30" t="n">
         <v>7.4</v>
@@ -8110,7 +8110,7 @@
         <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
         <v>9.6</v>
@@ -8122,13 +8122,13 @@
         <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF30" t="n">
         <v>4.9</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH30" t="n">
         <v>4.8</v>
@@ -8140,7 +8140,7 @@
         <v>14.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL30" t="n">
         <v>190</v>
@@ -8170,7 +8170,7 @@
         <v>16.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="BV30" t="n">
         <v>120</v>
@@ -8188,11 +8188,11 @@
         <v>15</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -908,7 +908,7 @@
         <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -965,7 +965,7 @@
         <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.4</v>
@@ -983,7 +983,7 @@
         <v>13.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW2" t="n">
         <v>5.7</v>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA2" t="n">
         <v>5.7</v>
@@ -1022,7 +1022,7 @@
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I3" t="n">
         <v>2.74</v>
@@ -1129,34 +1129,34 @@
         <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.57</v>
@@ -1168,7 +1168,7 @@
         <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
@@ -1180,7 +1180,7 @@
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1189,7 +1189,7 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -1222,16 +1222,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.6</v>
@@ -1240,7 +1240,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1249,34 +1249,34 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1297,10 +1297,10 @@
         <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1315,16 +1315,16 @@
         <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
         <v>7</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>36</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
         <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1389,7 +1389,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
@@ -1398,7 +1398,7 @@
         <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
@@ -1419,7 +1419,7 @@
         <v>1.59</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
         <v>12.5</v>
@@ -1482,7 +1482,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1506,13 +1506,13 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
         <v>23</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -1634,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1649,37 +1649,37 @@
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
         <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
         <v>2.8</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y5" t="n">
         <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>470</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1688,64 +1688,64 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>44</v>
       </c>
       <c r="AT5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU5" t="n">
         <v>11</v>
       </c>
-      <c r="AU5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>32</v>
@@ -1754,16 +1754,16 @@
         <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
         <v>12.5</v>
@@ -1775,10 +1775,10 @@
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH5" t="n">
         <v>5</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
         <v>4.8</v>
@@ -1805,7 +1805,7 @@
         <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ5" t="n">
         <v>4.9</v>
@@ -1826,7 +1826,7 @@
         <v>44</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>42</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G6" t="n">
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="n">
         <v>2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1903,13 +1903,13 @@
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
         <v>3.1</v>
@@ -1918,22 +1918,22 @@
         <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W6" t="n">
         <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>24</v>
@@ -1948,16 +1948,16 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
         <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>40</v>
@@ -1978,10 +1978,10 @@
         <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>9.4</v>
@@ -1993,10 +1993,10 @@
         <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>9.4</v>
@@ -2005,22 +2005,22 @@
         <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
         <v>34</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD6" t="n">
         <v>28</v>
@@ -2038,7 +2038,7 @@
         <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
@@ -2056,7 +2056,7 @@
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>27</v>
@@ -2074,7 +2074,7 @@
         <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
         <v>15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>3.05</v>
@@ -2139,7 +2139,7 @@
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
@@ -2160,7 +2160,7 @@
         <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.35</v>
@@ -2235,58 +2235,58 @@
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
         <v>25</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>65</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
         <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
         <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2459,7 +2459,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>950</v>
@@ -2483,70 +2483,70 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
         <v>950</v>
@@ -2561,19 +2561,19 @@
         <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BS8" t="n">
         <v>1.04</v>
@@ -2597,14 +2597,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA8" t="n">
         <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2668,13 +2668,13 @@
         <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
         <v>1.91</v>
@@ -2689,7 +2689,7 @@
         <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
         <v>17.5</v>
@@ -2701,7 +2701,7 @@
         <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>9.4</v>
@@ -2743,58 +2743,58 @@
         <v>110</v>
       </c>
       <c r="AP9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY9" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="AZ9" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4</v>
-      </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G10" t="n">
         <v>1.52</v>
@@ -2919,7 +2919,7 @@
         <v>1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.94</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
         <v>1.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.32</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
         <v>3.2</v>
@@ -3161,7 +3161,7 @@
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -3215,16 +3215,16 @@
         <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3245,7 +3245,7 @@
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
         <v>48</v>
@@ -3260,7 +3260,7 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -3272,7 +3272,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,28 +3284,28 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4</v>
       </c>
       <c r="BC11" t="n">
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
         <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BI11" t="n">
         <v>2.68</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3332,13 +3332,13 @@
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="BR11" t="n">
         <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT11" t="n">
         <v>7.8</v>
@@ -3350,23 +3350,23 @@
         <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3397,64 +3397,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H12" t="n">
-        <v>1.49</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z12" t="n">
         <v>85</v>
@@ -3463,7 +3463,7 @@
         <v>400</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
         <v>11</v>
@@ -3484,7 +3484,7 @@
         <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AJ12" t="n">
         <v>16.5</v>
@@ -3502,7 +3502,7 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AP12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="J13" t="n">
         <v>3.45</v>
@@ -3669,43 +3669,43 @@
         <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
         <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
         <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -3717,10 +3717,10 @@
         <v>38</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
         <v>14</v>
@@ -3729,13 +3729,13 @@
         <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
         <v>44</v>
@@ -3744,31 +3744,31 @@
         <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
         <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
         <v>11</v>
@@ -3777,52 +3777,52 @@
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL13" t="n">
         <v>120</v>
@@ -3834,25 +3834,25 @@
         <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV13" t="n">
         <v>22</v>
@@ -3861,10 +3861,10 @@
         <v>4.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
         <v>2.74</v>
@@ -3941,13 +3941,13 @@
         <v>1.43</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
         <v>2.12</v>
@@ -3962,7 +3962,7 @@
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
         <v>11.5</v>
@@ -3977,7 +3977,7 @@
         <v>15.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>14.5</v>
@@ -3989,7 +3989,7 @@
         <v>38</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
         <v>32</v>
@@ -4010,10 +4010,10 @@
         <v>120</v>
       </c>
       <c r="AO14" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -4025,7 +4025,7 @@
         <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -4037,37 +4037,37 @@
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
         <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
         <v>3.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI14" t="n">
         <v>3.85</v>
@@ -4076,31 +4076,31 @@
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN14" t="n">
         <v>13</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT14" t="n">
         <v>4.7</v>
@@ -4118,17 +4118,17 @@
         <v>21</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ14" t="n">
         <v>11</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
         <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>14</v>
@@ -4258,7 +4258,7 @@
         <v>42</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
         <v>23</v>
@@ -4276,7 +4276,7 @@
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -4300,19 +4300,19 @@
         <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC15" t="n">
         <v>21</v>
       </c>
       <c r="BD15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE15" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.63</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H16" t="n">
         <v>5.1</v>
@@ -4458,16 +4458,16 @@
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
         <v>2.34</v>
       </c>
       <c r="X16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
         <v>25</v>
@@ -4479,10 +4479,10 @@
         <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
         <v>21</v>
@@ -4491,7 +4491,7 @@
         <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -4503,7 +4503,7 @@
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="n">
         <v>17</v>
@@ -4527,22 +4527,22 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -4554,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="BB16" t="n">
         <v>13</v>
@@ -4563,16 +4563,16 @@
         <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
         <v>4.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
         <v>5.2</v>
@@ -4694,37 +4694,37 @@
         <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
         <v>40</v>
@@ -4739,7 +4739,7 @@
         <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
         <v>75</v>
@@ -4748,28 +4748,28 @@
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
         <v>130</v>
       </c>
       <c r="AN17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO17" t="n">
         <v>90</v>
@@ -4778,58 +4778,58 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BF17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI17" t="n">
         <v>3</v>
@@ -4838,59 +4838,59 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO17" t="n">
         <v>3.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY17" t="n">
         <v>14</v>
       </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BZ17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4927,10 +4927,10 @@
         <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
         <v>3.7</v>
@@ -4954,16 +4954,16 @@
         <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
         <v>2.32</v>
@@ -4975,7 +4975,7 @@
         <v>1.87</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4987,7 +4987,7 @@
         <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>9</v>
@@ -4999,10 +4999,10 @@
         <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
@@ -5020,7 +5020,7 @@
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
         <v>13.5</v>
@@ -5050,10 +5050,10 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY18" t="n">
         <v>9.6</v>
@@ -5071,37 +5071,37 @@
         <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>9</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO18" t="n">
         <v>3.95</v>
@@ -5110,13 +5110,13 @@
         <v>14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
         <v>7.2</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="G19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
         <v>4.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.29</v>
@@ -5214,16 +5214,16 @@
         <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
         <v>2.14</v>
@@ -5232,10 +5232,10 @@
         <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
         <v>110</v>
@@ -5244,13 +5244,13 @@
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
         <v>12.5</v>
@@ -5259,10 +5259,10 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
         <v>20</v>
@@ -5280,7 +5280,7 @@
         <v>9.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -5289,10 +5289,10 @@
         <v>15.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5304,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -5325,10 +5325,10 @@
         <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>7.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J20" t="n">
         <v>4.2</v>
@@ -5447,7 +5447,7 @@
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5459,136 +5459,136 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
         <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T20" t="n">
         <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V20" t="n">
         <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA20" t="n">
         <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV20" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
@@ -5627,22 +5627,22 @@
         <v>7</v>
       </c>
       <c r="BT20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>17</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5689,40 +5689,40 @@
         <v>4.9</v>
       </c>
       <c r="H21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.72</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.73</v>
       </c>
       <c r="J21" t="n">
         <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T21" t="n">
         <v>1.54</v>
@@ -5731,13 +5731,13 @@
         <v>2.8</v>
       </c>
       <c r="V21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W21" t="n">
         <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y21" t="n">
         <v>14.5</v>
@@ -5746,13 +5746,13 @@
         <v>14.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD21" t="n">
         <v>10</v>
@@ -5764,10 +5764,10 @@
         <v>44</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
@@ -5779,7 +5779,7 @@
         <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
         <v>55</v>
@@ -5788,25 +5788,25 @@
         <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV21" t="n">
         <v>9.800000000000001</v>
@@ -5842,71 +5842,71 @@
         <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BN21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BP21" t="n">
         <v>32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BT21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV21" t="n">
         <v>10.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5937,166 +5937,166 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="G22" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="I22" t="n">
         <v>3.55</v>
       </c>
       <c r="J22" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.5</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X22" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AB22" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AI22" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN22" t="n">
         <v>75</v>
       </c>
-      <c r="AK22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>440</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>110</v>
-      </c>
       <c r="AO22" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AR22" t="n">
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.05</v>
+        <v>5.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.06</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="H23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>3.85</v>
@@ -6209,7 +6209,7 @@
         <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
@@ -6218,10 +6218,10 @@
         <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
         <v>1.7</v>
@@ -6233,22 +6233,22 @@
         <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U23" t="n">
         <v>2.52</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z23" t="n">
         <v>30</v>
@@ -6263,7 +6263,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
@@ -6311,10 +6311,10 @@
         <v>60</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV23" t="n">
         <v>15.5</v>
@@ -6347,7 +6347,7 @@
         <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23" t="n">
         <v>29</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>1.23</v>
       </c>
       <c r="G24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="H24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
         <v>19</v>
@@ -6475,13 +6475,13 @@
         <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q24" t="n">
         <v>1.61</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
         <v>2.54</v>
@@ -6496,7 +6496,7 @@
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X24" t="n">
         <v>28</v>
@@ -6529,7 +6529,7 @@
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
         <v>270</v>
@@ -6553,7 +6553,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
         <v>38</v>
@@ -6568,7 +6568,7 @@
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV24" t="n">
         <v>9.199999999999999</v>
@@ -6583,7 +6583,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BA24" t="n">
         <v>8.6</v>
@@ -6595,7 +6595,7 @@
         <v>12.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BE24" t="n">
         <v>8.6</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6705,16 +6705,16 @@
         <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -6747,19 +6747,19 @@
         <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA25" t="n">
         <v>90</v>
@@ -6771,10 +6771,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
         <v>16.5</v>
@@ -6786,7 +6786,7 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
         <v>38</v>
@@ -6813,22 +6813,22 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -6840,25 +6840,25 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
         <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH25" t="n">
         <v>3.05</v>
@@ -6870,7 +6870,7 @@
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6882,7 +6882,7 @@
         <v>5</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP25" t="n">
         <v>18</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -6977,16 +6977,16 @@
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R26" t="n">
         <v>1.56</v>
@@ -7055,7 +7055,7 @@
         <v>490</v>
       </c>
       <c r="AN26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -7064,13 +7064,13 @@
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT26" t="n">
         <v>7.8</v>
@@ -7079,10 +7079,10 @@
         <v>13</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
         <v>6</v>
@@ -7091,10 +7091,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB26" t="n">
         <v>6.8</v>
@@ -7103,16 +7103,16 @@
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF26" t="n">
         <v>3.55</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH26" t="n">
         <v>4.4</v>
@@ -7124,7 +7124,7 @@
         <v>17</v>
       </c>
       <c r="BK26" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7136,7 +7136,7 @@
         <v>3.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BP26" t="n">
         <v>6.2</v>
@@ -7172,11 +7172,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G27" t="n">
         <v>2.38</v>
@@ -7216,13 +7216,13 @@
         <v>3.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
         <v>1.47</v>
@@ -7378,7 +7378,7 @@
         <v>13.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL27" t="n">
         <v>250</v>
@@ -7390,7 +7390,7 @@
         <v>5.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP27" t="n">
         <v>24</v>
@@ -7408,7 +7408,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV27" t="n">
         <v>46</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="I28" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="J28" t="n">
         <v>4.2</v>
@@ -7479,40 +7479,40 @@
         <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V28" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -7521,7 +7521,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA28" t="n">
         <v>17</v>
@@ -7548,10 +7548,10 @@
         <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK28" t="n">
         <v>90</v>
@@ -7563,16 +7563,16 @@
         <v>150</v>
       </c>
       <c r="AN28" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AP28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
         <v>8</v>
@@ -7587,13 +7587,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY28" t="n">
         <v>19.5</v>
@@ -7602,25 +7602,25 @@
         <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC28" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="n">
         <v>4.2</v>
@@ -7629,37 +7629,37 @@
         <v>2.92</v>
       </c>
       <c r="BJ28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK28" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BL28" t="n">
         <v>160</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BN28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP28" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR28" t="n">
         <v>65</v>
       </c>
-      <c r="BQ28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>70</v>
-      </c>
       <c r="BS28" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT28" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BU28" t="n">
         <v>3.5</v>
@@ -7674,17 +7674,17 @@
         <v>30</v>
       </c>
       <c r="BY28" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BZ28" t="n">
         <v>22</v>
       </c>
       <c r="CA28" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G29" t="n">
         <v>2.12</v>
       </c>
       <c r="H29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>5.1</v>
@@ -7745,10 +7745,10 @@
         <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
         <v>1.2</v>
@@ -7760,7 +7760,7 @@
         <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
         <v>1.24</v>
@@ -7790,7 +7790,7 @@
         <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="n">
         <v>11.5</v>
@@ -7811,7 +7811,7 @@
         <v>28</v>
       </c>
       <c r="AL29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
         <v>230</v>
@@ -7850,19 +7850,19 @@
         <v>9.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA29" t="n">
         <v>8.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>44</v>
@@ -7898,13 +7898,13 @@
         <v>5.1</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP29" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR29" t="n">
         <v>44</v>
@@ -7916,13 +7916,13 @@
         <v>9</v>
       </c>
       <c r="BU29" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="BV29" t="n">
         <v>55</v>
       </c>
       <c r="BW29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX29" t="n">
         <v>80</v>
@@ -7934,11 +7934,11 @@
         <v>46</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G30" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H30" t="n">
         <v>10.5</v>
@@ -7984,7 +7984,7 @@
         <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L30" t="n">
         <v>1.27</v>
@@ -7999,16 +7999,16 @@
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R30" t="n">
         <v>1.52</v>
       </c>
       <c r="S30" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
         <v>2.04</v>
@@ -8092,7 +8092,7 @@
         <v>8.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
         <v>4.5</v>
@@ -8140,7 +8140,7 @@
         <v>14.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="BL30" t="n">
         <v>190</v>
@@ -8152,13 +8152,13 @@
         <v>4.4</v>
       </c>
       <c r="BO30" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BP30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ30" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="BR30" t="n">
         <v>29</v>
@@ -8170,7 +8170,7 @@
         <v>16.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="BV30" t="n">
         <v>120</v>
@@ -8188,11 +8188,11 @@
         <v>15</v>
       </c>
       <c r="CA30" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -881,13 +881,13 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q2" t="n">
         <v>1.46</v>
@@ -908,7 +908,7 @@
         <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -929,13 +929,13 @@
         <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>190</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -944,7 +944,7 @@
         <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>140</v>
+        <v>460</v>
       </c>
       <c r="AJ2" t="n">
         <v>12</v>
@@ -953,10 +953,10 @@
         <v>15.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="AN2" t="n">
         <v>4.4</v>
@@ -965,16 +965,16 @@
         <v>200</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -983,22 +983,22 @@
         <v>13.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
@@ -1007,16 +1007,16 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1135,16 +1135,16 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
@@ -1153,28 +1153,28 @@
         <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
         <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
         <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
@@ -1186,7 +1186,7 @@
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -1198,37 +1198,37 @@
         <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1237,10 +1237,10 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1249,22 +1249,22 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
         <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF3" t="n">
         <v>29</v>
@@ -1276,37 +1276,37 @@
         <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>6.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>5.7</v>
@@ -1315,26 +1315,26 @@
         <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>8</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G4" t="n">
         <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
@@ -1389,37 +1389,37 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
         <v>1.91</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
         <v>12.5</v>
@@ -1434,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
@@ -1449,28 +1449,28 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
@@ -1482,7 +1482,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1494,31 +1494,31 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
         <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1643,34 +1643,34 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.17</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
         <v>29</v>
@@ -1679,7 +1679,7 @@
         <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
         <v>170</v>
@@ -1688,10 +1688,10 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>75</v>
@@ -1700,7 +1700,7 @@
         <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
         <v>19</v>
@@ -1709,46 +1709,46 @@
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
         <v>14</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>870</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AS5" t="n">
         <v>44</v>
       </c>
       <c r="AT5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU5" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>11</v>
       </c>
       <c r="AV5" t="n">
         <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1760,7 +1760,7 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
         <v>13.5</v>
@@ -1769,22 +1769,22 @@
         <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BH5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.800000000000001</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>4.8</v>
@@ -1805,44 +1805,44 @@
         <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU5" t="n">
         <v>5.1</v>
       </c>
       <c r="BV5" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX5" t="n">
         <v>44</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>42</v>
       </c>
       <c r="BY5" t="n">
         <v>8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1897,10 +1897,10 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
         <v>2.14</v>
@@ -1912,16 +1912,16 @@
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W6" t="n">
         <v>1.32</v>
@@ -1933,7 +1933,7 @@
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
         <v>24</v>
@@ -1948,7 +1948,7 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
@@ -1960,7 +1960,7 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
@@ -1975,10 +1975,10 @@
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
@@ -1993,7 +1993,7 @@
         <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -2005,37 +2005,37 @@
         <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BC6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG6" t="n">
         <v>11.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
         <v>3.4</v>
@@ -2044,13 +2044,13 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
@@ -2062,13 +2062,13 @@
         <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>5.2</v>
@@ -2080,23 +2080,23 @@
         <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
         <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
@@ -2181,112 +2181,112 @@
         <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
         <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AS7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AV7" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>25</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2381,49 +2381,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G8" t="n">
         <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="I8" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
         <v>1.6</v>
@@ -2447,10 +2447,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC8" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2459,7 +2459,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
         <v>950</v>
@@ -2471,76 +2471,76 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
@@ -2552,13 +2552,13 @@
         <v>950</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BN8" t="n">
         <v>3.95</v>
@@ -2570,41 +2570,41 @@
         <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BR8" t="n">
         <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BT8" t="n">
         <v>950</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BZ8" t="n">
         <v>20</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2635,166 +2635,166 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD9" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
         <v>150</v>
       </c>
-      <c r="AB9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
         <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
         <v>3.55</v>
@@ -2806,59 +2806,59 @@
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
         <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BZ9" t="n">
         <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>500</v>
@@ -2913,7 +2913,7 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
         <v>1.1</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3048,7 +3048,7 @@
         <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -3170,10 +3170,10 @@
         <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
         <v>1.98</v>
@@ -3191,13 +3191,13 @@
         <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
         <v>1.68</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
@@ -3212,7 +3212,7 @@
         <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>16.5</v>
@@ -3239,10 +3239,10 @@
         <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
         <v>24</v>
@@ -3260,7 +3260,7 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -3272,7 +3272,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,28 +3284,28 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>42</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
         <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI11" t="n">
         <v>2.68</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3332,13 +3332,13 @@
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR11" t="n">
         <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT11" t="n">
         <v>7.8</v>
@@ -3350,23 +3350,23 @@
         <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
         <v>1.66</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.5</v>
@@ -3418,13 +3418,13 @@
         <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="P12" t="n">
         <v>1.6</v>
@@ -3433,16 +3433,16 @@
         <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
@@ -3451,49 +3451,49 @@
         <v>2.5</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="AA12" t="n">
         <v>400</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
         <v>260</v>
@@ -3505,58 +3505,58 @@
         <v>380</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -3675,7 +3675,7 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
@@ -3684,151 +3684,151 @@
         <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
         <v>18</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG13" t="n">
         <v>14</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
         <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL13" t="n">
         <v>120</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN13" t="n">
         <v>7</v>
@@ -3846,16 +3846,16 @@
         <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW13" t="n">
         <v>4.5</v>
@@ -3864,7 +3864,7 @@
         <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="G14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K14" t="n">
         <v>6.8</v>
@@ -3935,7 +3935,7 @@
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
         <v>1.43</v>
@@ -3944,22 +3944,22 @@
         <v>1.71</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="W14" t="n">
         <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3983,37 +3983,37 @@
         <v>14.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AG14" t="n">
         <v>38</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AI14" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>290</v>
       </c>
       <c r="AK14" t="n">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AL14" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -4025,7 +4025,7 @@
         <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -4037,10 +4037,10 @@
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>18</v>
@@ -4049,19 +4049,19 @@
         <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
         <v>3.8</v>
@@ -4073,62 +4073,62 @@
         <v>3.85</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BN14" t="n">
         <v>13</v>
       </c>
       <c r="BO14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT14" t="n">
         <v>4.6</v>
       </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BU14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BX14" t="n">
         <v>21</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA14" t="n">
         <v>4.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>2.92</v>
       </c>
       <c r="H15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I15" t="n">
         <v>2.8</v>
@@ -4177,7 +4177,7 @@
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -4192,7 +4192,7 @@
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -4201,10 +4201,10 @@
         <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
         <v>1.56</v>
@@ -4213,58 +4213,58 @@
         <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
         <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
         <v>14</v>
       </c>
-      <c r="AE15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
         <v>15.5</v>
@@ -4276,7 +4276,7 @@
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -4300,19 +4300,19 @@
         <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
         <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G16" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
         <v>5.9</v>
@@ -4428,10 +4428,10 @@
         <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
@@ -4458,13 +4458,13 @@
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
         <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="X16" t="n">
         <v>23</v>
@@ -4476,7 +4476,7 @@
         <v>46</v>
       </c>
       <c r="AA16" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>11.5</v>
@@ -4485,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
@@ -4509,7 +4509,7 @@
         <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM16" t="n">
         <v>90</v>
@@ -4530,7 +4530,7 @@
         <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
@@ -4542,7 +4542,7 @@
         <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -4560,19 +4560,19 @@
         <v>13</v>
       </c>
       <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD16" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE16" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="n">
         <v>4.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H17" t="n">
         <v>5.2</v>
@@ -4679,7 +4679,7 @@
         <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
@@ -4691,34 +4691,34 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
         <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -4730,13 +4730,13 @@
         <v>40</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
         <v>20</v>
@@ -4748,31 +4748,31 @@
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK17" t="n">
         <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -4781,22 +4781,22 @@
         <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU17" t="n">
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -4808,7 +4808,7 @@
         <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BB17" t="n">
         <v>17</v>
@@ -4817,16 +4817,16 @@
         <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
         <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH17" t="n">
         <v>3.3</v>
@@ -4838,59 +4838,59 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN17" t="n">
         <v>4.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BP17" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT17" t="n">
         <v>8.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
         <v>14</v>
       </c>
       <c r="BZ17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA17" t="n">
         <v>10.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
         <v>2.14</v>
@@ -4930,16 +4930,16 @@
         <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4948,13 +4948,13 @@
         <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
         <v>1.47</v>
@@ -4966,16 +4966,16 @@
         <v>1.65</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -5020,7 +5020,7 @@
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>13.5</v>
@@ -5050,13 +5050,13 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>14</v>
@@ -5071,40 +5071,40 @@
         <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ18" t="n">
         <v>9</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN18" t="n">
         <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
         <v>14</v>
@@ -5140,11 +5140,11 @@
         <v>19</v>
       </c>
       <c r="CA18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -5193,160 +5193,160 @@
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W19" t="n">
         <v>2.22</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.14</v>
-      </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
         <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
         <v>110</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
         <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC19" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>15</v>
-      </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>10</v>
       </c>
-      <c r="BF19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5361,19 +5361,19 @@
         <v>3.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU19" t="n">
         <v>4.7</v>
@@ -5385,20 +5385,20 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY19" t="n">
         <v>8.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.28</v>
@@ -5459,16 +5459,16 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T20" t="n">
         <v>1.79</v>
@@ -5480,10 +5480,10 @@
         <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
         <v>24</v>
@@ -5495,7 +5495,7 @@
         <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
@@ -5507,13 +5507,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG20" t="n">
         <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
         <v>75</v>
@@ -5522,7 +5522,7 @@
         <v>16.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>34</v>
@@ -5537,19 +5537,19 @@
         <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR20" t="n">
         <v>20</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AS20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT20" t="n">
         <v>9</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AU20" t="n">
         <v>9</v>
@@ -5558,7 +5558,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -5567,28 +5567,28 @@
         <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BB20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BF20" t="n">
         <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
@@ -5630,29 +5630,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BZ20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA20" t="n">
         <v>6.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5719,10 +5719,10 @@
         <v>1.47</v>
       </c>
       <c r="R21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T21" t="n">
         <v>1.54</v>
@@ -5737,10 +5737,10 @@
         <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
         <v>14.5</v>
@@ -5752,7 +5752,7 @@
         <v>29</v>
       </c>
       <c r="AC21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>10</v>
@@ -5767,13 +5767,13 @@
         <v>19.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="n">
         <v>46</v>
@@ -5782,19 +5782,19 @@
         <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN21" t="n">
         <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
         <v>13.5</v>
@@ -5806,7 +5806,7 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV21" t="n">
         <v>9.800000000000001</v>
@@ -5818,10 +5818,10 @@
         <v>40</v>
       </c>
       <c r="AY21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
@@ -5836,25 +5836,25 @@
         <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH21" t="n">
         <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BL21" t="n">
         <v>70</v>
@@ -5866,7 +5866,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BP21" t="n">
         <v>32</v>
@@ -5878,7 +5878,7 @@
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BT21" t="n">
         <v>5</v>
@@ -5893,20 +5893,20 @@
         <v>9.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BZ21" t="n">
         <v>12</v>
       </c>
       <c r="CA21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5937,166 +5937,166 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>2.98</v>
       </c>
       <c r="G22" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="H22" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="L22" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB22" t="n">
         <v>8</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AC22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE22" t="n">
         <v>11</v>
       </c>
-      <c r="Z22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF22" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6191,31 +6191,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="H23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.9</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -6233,43 +6233,43 @@
         <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U23" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
@@ -6278,37 +6278,37 @@
         <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>27</v>
       </c>
       <c r="AM23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP23" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS23" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AT23" t="n">
         <v>11.5</v>
@@ -6317,13 +6317,13 @@
         <v>8.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -6332,89 +6332,89 @@
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD23" t="n">
         <v>26</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL23" t="n">
         <v>85</v>
       </c>
       <c r="BM23" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT23" t="n">
         <v>7.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BW23" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX23" t="n">
         <v>34</v>
       </c>
       <c r="BY23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ23" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J24" t="n">
         <v>6.6</v>
       </c>
       <c r="K24" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.26</v>
@@ -6469,28 +6469,28 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="T24" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
@@ -6499,10 +6499,10 @@
         <v>4.7</v>
       </c>
       <c r="X24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Z24" t="n">
         <v>200</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="AE24" t="n">
         <v>390</v>
@@ -6529,7 +6529,7 @@
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>950</v>
+        <v>170</v>
       </c>
       <c r="AI24" t="n">
         <v>270</v>
@@ -6538,43 +6538,43 @@
         <v>9</v>
       </c>
       <c r="AK24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM24" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX24" t="n">
         <v>6.2</v>
@@ -6583,46 +6583,46 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BG24" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH24" t="n">
         <v>4.4</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
         <v>15</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
         <v>3.7</v>
@@ -6637,38 +6637,38 @@
         <v>5.7</v>
       </c>
       <c r="BR24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT24" t="n">
         <v>18.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>11</v>
-      </c>
       <c r="CA24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6702,28 +6702,28 @@
         <v>2.22</v>
       </c>
       <c r="G25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.45</v>
       </c>
-      <c r="K25" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
         <v>1.41</v>
@@ -6744,13 +6744,13 @@
         <v>1.92</v>
       </c>
       <c r="U25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
@@ -6762,19 +6762,19 @@
         <v>30</v>
       </c>
       <c r="AA25" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
         <v>18.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF25" t="n">
         <v>16.5</v>
@@ -6786,7 +6786,7 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>490</v>
       </c>
       <c r="AJ25" t="n">
         <v>38</v>
@@ -6798,13 +6798,13 @@
         <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -6816,19 +6816,19 @@
         <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -6840,31 +6840,31 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF25" t="n">
         <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ25" t="n">
         <v>10.5</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN25" t="n">
         <v>5</v>
@@ -6888,13 +6888,13 @@
         <v>18</v>
       </c>
       <c r="BQ25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT25" t="n">
         <v>6.8</v>
@@ -6903,7 +6903,7 @@
         <v>5.1</v>
       </c>
       <c r="BV25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
         <v>10.5</v>
@@ -6912,17 +6912,17 @@
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>1.21</v>
       </c>
       <c r="H26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I26" t="n">
         <v>27</v>
@@ -6968,7 +6968,7 @@
         <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -6983,10 +6983,10 @@
         <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
         <v>1.56</v>
@@ -6995,10 +6995,10 @@
         <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V26" t="n">
         <v>1.04</v>
@@ -7019,31 +7019,31 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC26" t="n">
         <v>23</v>
       </c>
       <c r="AD26" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AJ26" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AK26" t="n">
         <v>19.5</v>
@@ -7052,7 +7052,7 @@
         <v>85</v>
       </c>
       <c r="AM26" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AN26" t="n">
         <v>4.5</v>
@@ -7064,13 +7064,13 @@
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT26" t="n">
         <v>7.8</v>
@@ -7079,10 +7079,10 @@
         <v>13</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX26" t="n">
         <v>6</v>
@@ -7091,52 +7091,52 @@
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH26" t="n">
         <v>4.4</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BJ26" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN26" t="n">
         <v>3.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BP26" t="n">
         <v>6.2</v>
@@ -7154,29 +7154,29 @@
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
         <v>15</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>14.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA26" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7210,10 +7210,10 @@
         <v>2.22</v>
       </c>
       <c r="G27" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
         <v>4.1</v>
@@ -7222,13 +7222,13 @@
         <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
         <v>2.62</v>
@@ -7240,7 +7240,7 @@
         <v>1.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
         <v>1.19</v>
@@ -7255,16 +7255,16 @@
         <v>1.64</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
         <v>32</v>
@@ -7279,10 +7279,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
         <v>15.5</v>
@@ -7300,7 +7300,7 @@
         <v>40</v>
       </c>
       <c r="AK27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL27" t="n">
         <v>70</v>
@@ -7321,10 +7321,10 @@
         <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
@@ -7336,7 +7336,7 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX27" t="n">
         <v>11</v>
@@ -7348,37 +7348,37 @@
         <v>18.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB27" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB27" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH27" t="n">
         <v>3.15</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ27" t="n">
         <v>13.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="BL27" t="n">
         <v>250</v>
@@ -7390,7 +7390,7 @@
         <v>5.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP27" t="n">
         <v>24</v>
@@ -7408,7 +7408,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV27" t="n">
         <v>46</v>
@@ -7417,7 +7417,7 @@
         <v>4.5</v>
       </c>
       <c r="BX27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY27" t="n">
         <v>4.7</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7467,49 +7467,49 @@
         <v>6.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U28" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W28" t="n">
         <v>1.19</v>
@@ -7518,16 +7518,16 @@
         <v>16</v>
       </c>
       <c r="Y28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z28" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>9</v>
       </c>
       <c r="AA28" t="n">
         <v>17</v>
       </c>
       <c r="AB28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="n">
         <v>9.4</v>
@@ -7536,7 +7536,7 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF28" t="n">
         <v>46</v>
@@ -7548,7 +7548,7 @@
         <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
         <v>170</v>
@@ -7566,13 +7566,13 @@
         <v>120</v>
       </c>
       <c r="AO28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR28" t="n">
         <v>8</v>
@@ -7581,19 +7581,19 @@
         <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28" t="n">
         <v>19.5</v>
@@ -7605,25 +7605,25 @@
         <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI28" t="n">
         <v>2.92</v>
@@ -7632,31 +7632,31 @@
         <v>12</v>
       </c>
       <c r="BK28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BL28" t="n">
         <v>160</v>
       </c>
       <c r="BM28" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BN28" t="n">
         <v>10.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP28" t="n">
         <v>60</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS28" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BT28" t="n">
         <v>4.5</v>
@@ -7674,17 +7674,17 @@
         <v>30</v>
       </c>
       <c r="BY28" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BZ28" t="n">
         <v>22</v>
       </c>
       <c r="CA28" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7739,16 +7739,16 @@
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O29" t="n">
         <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R29" t="n">
         <v>1.2</v>
@@ -7757,7 +7757,7 @@
         <v>4.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U29" t="n">
         <v>1.73</v>
@@ -7877,7 +7877,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI29" t="n">
         <v>2.36</v>
@@ -7886,59 +7886,59 @@
         <v>13</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL29" t="n">
         <v>240</v>
       </c>
       <c r="BM29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN29" t="n">
         <v>5.1</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP29" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BR29" t="n">
         <v>44</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT29" t="n">
         <v>9</v>
       </c>
       <c r="BU29" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV29" t="n">
         <v>55</v>
       </c>
       <c r="BW29" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX29" t="n">
         <v>80</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ29" t="n">
         <v>46</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7975,16 +7975,16 @@
         <v>1.39</v>
       </c>
       <c r="H30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
         <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="K30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.27</v>
@@ -8014,13 +8014,13 @@
         <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -8092,7 +8092,7 @@
         <v>8.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV30" t="n">
         <v>4.5</v>
@@ -8152,7 +8152,7 @@
         <v>4.4</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BP30" t="n">
         <v>9.199999999999999</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
         <v>1.31</v>
@@ -872,10 +872,10 @@
         <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -884,13 +884,13 @@
         <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
         <v>2.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R2" t="n">
         <v>1.77</v>
@@ -908,7 +908,7 @@
         <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -935,7 +935,7 @@
         <v>190</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -959,7 +959,7 @@
         <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AO2" t="n">
         <v>200</v>
@@ -971,10 +971,10 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -986,22 +986,22 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -1010,10 +1010,10 @@
         <v>16.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
@@ -1022,7 +1022,7 @@
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>4</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>13</v>
       </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA2" t="n">
         <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
         <v>2.72</v>
@@ -1129,7 +1129,7 @@
         <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1138,31 +1138,31 @@
         <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
         <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
         <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1171,7 +1171,7 @@
         <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
@@ -1216,19 +1216,19 @@
         <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1249,13 +1249,13 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
         <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BC3" t="n">
         <v>9.6</v>
@@ -1264,7 +1264,7 @@
         <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BF3" t="n">
         <v>29</v>
@@ -1312,7 +1312,7 @@
         <v>5.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -1383,7 +1383,7 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1398,10 +1398,10 @@
         <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
@@ -1434,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
@@ -1452,7 +1452,7 @@
         <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
         <v>40</v>
@@ -1470,7 +1470,7 @@
         <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
@@ -1482,7 +1482,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1494,7 +1494,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,16 +1506,16 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
         <v>50</v>
@@ -1527,68 +1527,68 @@
         <v>21</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO4" t="n">
         <v>5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
         <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY4" t="n">
         <v>36</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>27</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
         <v>5.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S5" t="n">
         <v>2.22</v>
@@ -1667,22 +1667,22 @@
         <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X5" t="n">
         <v>29</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
         <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
         <v>13</v>
@@ -1691,25 +1691,25 @@
         <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
         <v>14</v>
@@ -1724,13 +1724,13 @@
         <v>5.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>27</v>
       </c>
       <c r="AQ5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR5" t="n">
         <v>50</v>
@@ -1739,16 +1739,16 @@
         <v>44</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1757,13 +1757,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
         <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>12.5</v>
@@ -1772,10 +1772,10 @@
         <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
         <v>38</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>3.95</v>
@@ -1903,10 +1903,10 @@
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1915,7 +1915,7 @@
         <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
         <v>2.28</v>
@@ -1930,10 +1930,10 @@
         <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>24</v>
@@ -1951,7 +1951,7 @@
         <v>19.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AG6" t="n">
         <v>18</v>
@@ -1978,7 +1978,7 @@
         <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
@@ -2005,7 +2005,7 @@
         <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -2014,13 +2014,13 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD6" t="n">
         <v>30</v>
@@ -2029,7 +2029,7 @@
         <v>48</v>
       </c>
       <c r="BF6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BG6" t="n">
         <v>11.5</v>
@@ -2038,13 +2038,13 @@
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2062,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
@@ -2074,16 +2074,16 @@
         <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV6" t="n">
         <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY6" t="n">
         <v>9.4</v>
@@ -2092,11 +2092,11 @@
         <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
         <v>23</v>
@@ -2202,7 +2202,7 @@
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
         <v>23</v>
@@ -2235,13 +2235,13 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
         <v>6.2</v>
@@ -2259,13 +2259,13 @@
         <v>5.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY7" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA7" t="n">
         <v>6.2</v>
@@ -2283,10 +2283,10 @@
         <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.35</v>
       </c>
       <c r="G8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="n">
         <v>9.4</v>
@@ -2393,7 +2393,7 @@
         <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>6.4</v>
@@ -2405,7 +2405,7 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
@@ -2423,16 +2423,16 @@
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2519,7 +2519,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
@@ -2531,10 +2531,10 @@
         <v>3.35</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="BF8" t="n">
         <v>4.4</v>
@@ -2549,7 +2549,7 @@
         <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BK8" t="n">
         <v>4.4</v>
@@ -2567,7 +2567,7 @@
         <v>2.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="BQ8" t="n">
         <v>3.75</v>
@@ -2579,7 +2579,7 @@
         <v>1.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
         <v>4.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
         <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB9" t="n">
         <v>9.6</v>
@@ -2707,25 +2707,25 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
         <v>150</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK9" t="n">
         <v>27</v>
@@ -2737,37 +2737,37 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP9" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
         <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2776,25 +2776,25 @@
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB9" t="n">
         <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.55</v>
@@ -2806,59 +2806,59 @@
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BL9" t="n">
         <v>170</v>
       </c>
       <c r="BM9" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BR9" t="n">
         <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BT9" t="n">
         <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="BV9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BZ9" t="n">
         <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2991,64 +2991,64 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
         <v>3.2</v>
@@ -3155,7 +3155,7 @@
         <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -3185,16 +3185,16 @@
         <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
         <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AE12" t="n">
         <v>480</v>
@@ -3511,7 +3511,7 @@
         <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS12" t="n">
         <v>7.8</v>
@@ -3523,7 +3523,7 @@
         <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW12" t="n">
         <v>7.6</v>
@@ -3544,7 +3544,7 @@
         <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD12" t="n">
         <v>7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
         <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -3675,13 +3675,13 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
@@ -3693,13 +3693,13 @@
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
         <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
@@ -3723,13 +3723,13 @@
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
         <v>29</v>
       </c>
       <c r="AF13" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
         <v>14</v>
@@ -3741,10 +3741,10 @@
         <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -3795,22 +3795,22 @@
         <v>18</v>
       </c>
       <c r="BB13" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="BC13" t="n">
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
         <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -4189,10 +4189,10 @@
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -4213,7 +4213,7 @@
         <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
         <v>15</v>
@@ -4255,7 +4255,7 @@
         <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
@@ -4303,7 +4303,7 @@
         <v>18</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC15" t="n">
         <v>21</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4431,34 +4431,34 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.64</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
         <v>1.2</v>
@@ -4473,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
@@ -4485,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
@@ -4494,25 +4494,25 @@
         <v>12</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN16" t="n">
         <v>8.199999999999999</v>
@@ -4530,7 +4530,7 @@
         <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
@@ -4548,7 +4548,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
@@ -4566,13 +4566,13 @@
         <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="n">
         <v>4.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="n">
         <v>1.83</v>
@@ -4685,46 +4685,46 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
         <v>2.2</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
         <v>40</v>
@@ -4733,10 +4733,10 @@
         <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>20</v>
@@ -4751,19 +4751,19 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
         <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK17" t="n">
         <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
         <v>120</v>
@@ -4772,7 +4772,7 @@
         <v>12</v>
       </c>
       <c r="AO17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -4784,34 +4784,34 @@
         <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU17" t="n">
         <v>8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>16.5</v>
+        <v>60</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
         <v>16.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC17" t="n">
         <v>17.5</v>
@@ -4820,13 +4820,13 @@
         <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH17" t="n">
         <v>3.3</v>
@@ -4838,13 +4838,13 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BN17" t="n">
         <v>4.4</v>
@@ -4856,41 +4856,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT17" t="n">
         <v>8.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BZ17" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="CA17" t="n">
         <v>10.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
         <v>2.14</v>
@@ -4930,7 +4930,7 @@
         <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.7</v>
@@ -4945,7 +4945,7 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
@@ -4954,25 +4954,25 @@
         <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
         <v>24</v>
@@ -4990,7 +4990,7 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>19</v>
@@ -5029,7 +5029,7 @@
         <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
         <v>15</v>
@@ -5074,43 +5074,43 @@
         <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="n">
         <v>3.9</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>9</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN18" t="n">
         <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP18" t="n">
         <v>14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
@@ -5140,11 +5140,11 @@
         <v>19</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
         <v>4.7</v>
@@ -5193,52 +5193,52 @@
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
         <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T19" t="n">
         <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
         <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA19" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
         <v>10.5</v>
@@ -5262,7 +5262,7 @@
         <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
         <v>20</v>
@@ -5271,16 +5271,16 @@
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
         <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -5295,7 +5295,7 @@
         <v>13.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
@@ -5304,7 +5304,7 @@
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5316,25 +5316,25 @@
         <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BB19" t="n">
         <v>17</v>
       </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
         <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BH19" t="n">
         <v>3.9</v>
@@ -5346,59 +5346,59 @@
         <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP19" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT19" t="n">
         <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>40</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19" t="n">
         <v>46</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G20" t="n">
         <v>1.65</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I20" t="n">
         <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
         <v>4.5</v>
@@ -5453,13 +5453,13 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
         <v>1.73</v>
@@ -5468,22 +5468,22 @@
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
         <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
         <v>24</v>
@@ -5492,10 +5492,10 @@
         <v>50</v>
       </c>
       <c r="AA20" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
@@ -5510,7 +5510,7 @@
         <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
@@ -5525,10 +5525,10 @@
         <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AN20" t="n">
         <v>8.199999999999999</v>
@@ -5537,7 +5537,7 @@
         <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
         <v>21</v>
@@ -5546,22 +5546,22 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
         <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY20" t="n">
         <v>9</v>
@@ -5570,7 +5570,7 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BB20" t="n">
         <v>14</v>
@@ -5582,13 +5582,13 @@
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BF20" t="n">
         <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5606,13 +5606,13 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP20" t="n">
         <v>11</v>
@@ -5630,29 +5630,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA20" t="n">
         <v>6.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>1.71</v>
@@ -5707,16 +5707,16 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
         <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R21" t="n">
         <v>1.84</v>
@@ -5743,7 +5743,7 @@
         <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
         <v>19</v>
@@ -5779,7 +5779,7 @@
         <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
         <v>50</v>
@@ -5794,13 +5794,13 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -5836,7 +5836,7 @@
         <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF21" t="n">
         <v>32</v>
@@ -5857,7 +5857,7 @@
         <v>8</v>
       </c>
       <c r="BL21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BM21" t="n">
         <v>12</v>
@@ -5872,7 +5872,7 @@
         <v>32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L22" t="n">
         <v>1.56</v>
@@ -5961,7 +5961,7 @@
         <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
         <v>1.68</v>
@@ -5976,46 +5976,46 @@
         <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
         <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
         <v>6.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
         <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
         <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
         <v>17</v>
@@ -6030,34 +6030,34 @@
         <v>70</v>
       </c>
       <c r="AK22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL22" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AM22" t="n">
         <v>330</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO22" t="n">
         <v>95</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>6.4</v>
@@ -6066,7 +6066,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>16</v>
@@ -6075,10 +6075,10 @@
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB22" t="n">
         <v>48</v>
@@ -6087,13 +6087,13 @@
         <v>16</v>
       </c>
       <c r="BD22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF22" t="n">
         <v>11</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>10</v>
       </c>
       <c r="BG22" t="n">
         <v>18</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6203,19 +6203,19 @@
         <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -6227,13 +6227,13 @@
         <v>1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U23" t="n">
         <v>2.48</v>
@@ -6245,13 +6245,13 @@
         <v>2.04</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
         <v>80</v>
@@ -6263,10 +6263,10 @@
         <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
         <v>14</v>
@@ -6284,7 +6284,7 @@
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL23" t="n">
         <v>27</v>
@@ -6299,7 +6299,7 @@
         <v>36</v>
       </c>
       <c r="AP23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ23" t="n">
         <v>18.5</v>
@@ -6308,13 +6308,13 @@
         <v>30</v>
       </c>
       <c r="AS23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT23" t="n">
         <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>16.5</v>
@@ -6329,16 +6329,16 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
         <v>26</v>
@@ -6347,7 +6347,7 @@
         <v>55</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG23" t="n">
         <v>32</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G24" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="H24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="J24" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.26</v>
@@ -6469,142 +6469,142 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="T24" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="X24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="n">
+        <v>290</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD24" t="n">
         <v>55</v>
       </c>
-      <c r="Z24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>150</v>
-      </c>
       <c r="AE24" t="n">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="AF24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>330</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT24" t="n">
         <v>7.6</v>
       </c>
-      <c r="AG24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>170</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>270</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR24" t="n">
+      <c r="AU24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY24" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AZ24" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA24" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AT24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB24" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH24" t="n">
         <v>4.4</v>
@@ -6613,7 +6613,7 @@
         <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK24" t="n">
         <v>6.6</v>
@@ -6622,7 +6622,7 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN24" t="n">
         <v>3.7</v>
@@ -6640,10 +6640,10 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT24" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU24" t="n">
         <v>7.2</v>
@@ -6652,7 +6652,7 @@
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
@@ -6661,14 +6661,14 @@
         <v>11</v>
       </c>
       <c r="BZ24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
         <v>3.85</v>
@@ -6717,46 +6717,46 @@
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="P25" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T25" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U25" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
         <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z25" t="n">
         <v>30</v>
@@ -6765,19 +6765,19 @@
         <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD25" t="n">
         <v>18.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AF25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
         <v>13.5</v>
@@ -6786,7 +6786,7 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
         <v>38</v>
@@ -6807,94 +6807,94 @@
         <v>500</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
         <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
         <v>6.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB25" t="n">
         <v>14.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BF25" t="n">
         <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ25" t="n">
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN25" t="n">
         <v>5</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT25" t="n">
         <v>6.8</v>
@@ -6903,26 +6903,26 @@
         <v>5.1</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
         <v>11.5</v>
       </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6953,58 +6953,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
         <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P26" t="n">
         <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R26" t="n">
         <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="U26" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="X26" t="n">
         <v>30</v>
@@ -7013,19 +7013,19 @@
         <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
         <v>23</v>
       </c>
       <c r="AD26" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
@@ -7040,10 +7040,10 @@
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="AJ26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AK26" t="n">
         <v>19.5</v>
@@ -7052,10 +7052,10 @@
         <v>85</v>
       </c>
       <c r="AM26" t="n">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="AN26" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -7064,58 +7064,58 @@
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.2</v>
+        <v>42</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX26" t="n">
         <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI26" t="n">
         <v>3.95</v>
@@ -7124,59 +7124,59 @@
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN26" t="n">
         <v>3.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="BP26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="H27" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="n">
         <v>4.1</v>
@@ -7222,49 +7222,49 @@
         <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.47</v>
       </c>
-      <c r="M27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
         <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
         <v>32</v>
@@ -7273,7 +7273,7 @@
         <v>110</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC27" t="n">
         <v>8.800000000000001</v>
@@ -7282,7 +7282,7 @@
         <v>19.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
         <v>15.5</v>
@@ -7315,19 +7315,19 @@
         <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
@@ -7336,7 +7336,7 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX27" t="n">
         <v>11</v>
@@ -7348,43 +7348,43 @@
         <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BJ27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BL27" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="BM27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN27" t="n">
         <v>5.8</v>
@@ -7393,16 +7393,16 @@
         <v>3.8</v>
       </c>
       <c r="BP27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR27" t="n">
         <v>55</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT27" t="n">
         <v>8.199999999999999</v>
@@ -7411,26 +7411,26 @@
         <v>5.2</v>
       </c>
       <c r="BV27" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ27" t="n">
         <v>60</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="J28" t="n">
         <v>4.2</v>
@@ -7503,16 +7503,16 @@
         <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U28" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="W28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -7521,7 +7521,7 @@
         <v>8.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
         <v>17</v>
@@ -7557,7 +7557,7 @@
         <v>90</v>
       </c>
       <c r="AL28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM28" t="n">
         <v>150</v>
@@ -7572,7 +7572,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR28" t="n">
         <v>8</v>
@@ -7587,7 +7587,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -7608,16 +7608,16 @@
         <v>10</v>
       </c>
       <c r="BC28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE28" t="n">
         <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG28" t="n">
         <v>9</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="G29" t="n">
         <v>2.12</v>
@@ -7724,55 +7724,55 @@
         <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="P29" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
         <v>1.89</v>
       </c>
       <c r="X29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
         <v>36</v>
@@ -7781,7 +7781,7 @@
         <v>150</v>
       </c>
       <c r="AB29" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC29" t="n">
         <v>8.199999999999999</v>
@@ -7790,61 +7790,61 @@
         <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF29" t="n">
         <v>11.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI29" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM29" t="n">
         <v>230</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO29" t="n">
         <v>150</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -7853,70 +7853,70 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD29" t="n">
         <v>44</v>
       </c>
       <c r="BE29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BL29" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="BM29" t="n">
         <v>6</v>
       </c>
       <c r="BN29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BP29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ29" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BR29" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT29" t="n">
         <v>9</v>
       </c>
       <c r="BU29" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="BV29" t="n">
         <v>55</v>
@@ -7928,17 +7928,17 @@
         <v>80</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ29" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA29" t="n">
         <v>5.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7972,16 +7972,16 @@
         <v>1.36</v>
       </c>
       <c r="G30" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K30" t="n">
         <v>5.8</v>
@@ -7999,28 +7999,28 @@
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
         <v>1.65</v>
       </c>
       <c r="R30" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
         <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V30" t="n">
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -8089,7 +8089,7 @@
         <v>5</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU30" t="n">
         <v>10.5</v>
@@ -8140,16 +8140,16 @@
         <v>14.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL30" t="n">
         <v>190</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO30" t="n">
         <v>3</v>
@@ -8158,41 +8158,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR30" t="n">
         <v>29</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT30" t="n">
         <v>16.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BV30" t="n">
         <v>120</v>
       </c>
       <c r="BW30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX30" t="n">
         <v>100</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ30" t="n">
         <v>15</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H2" t="n">
         <v>11.5</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
         <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -884,13 +884,13 @@
         <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
         <v>2.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.77</v>
@@ -902,13 +902,13 @@
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -962,7 +962,7 @@
         <v>3.95</v>
       </c>
       <c r="AO2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -971,10 +971,10 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -986,7 +986,7 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
@@ -1001,7 +1001,7 @@
         <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -1010,7 +1010,7 @@
         <v>16.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>3.05</v>
@@ -1022,7 +1022,7 @@
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1111,49 +1111,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
         <v>2.02</v>
@@ -1162,40 +1162,40 @@
         <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.6</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1213,100 +1213,100 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>10</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="BK3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>6.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
         <v>26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>5.7</v>
@@ -1315,26 +1315,26 @@
         <v>4.7</v>
       </c>
       <c r="BV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
         <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
@@ -1407,13 +1407,13 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
         <v>1.58</v>
@@ -1482,7 +1482,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1494,7 +1494,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,7 +1506,7 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1554,13 +1554,13 @@
         <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
         <v>6</v>
@@ -1572,7 +1572,7 @@
         <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
         <v>40</v>
@@ -1581,14 +1581,14 @@
         <v>36</v>
       </c>
       <c r="BZ4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA4" t="n">
         <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.49</v>
       </c>
       <c r="G5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K5" t="n">
         <v>5.4</v>
@@ -1658,31 +1658,31 @@
         <v>1.76</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
         <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB5" t="n">
         <v>13</v>
@@ -1700,7 +1700,7 @@
         <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH5" t="n">
         <v>19</v>
@@ -1712,19 +1712,19 @@
         <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL5" t="n">
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
         <v>27</v>
@@ -1733,10 +1733,10 @@
         <v>30</v>
       </c>
       <c r="AR5" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AS5" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1745,22 +1745,22 @@
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
@@ -1778,71 +1778,71 @@
         <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR5" t="n">
         <v>19.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>44</v>
       </c>
       <c r="BY5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1873,178 +1873,178 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AM6" t="n">
         <v>80</v>
       </c>
-      <c r="AK6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>90</v>
-      </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,40 +2053,40 @@
         <v>12.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
         <v>10</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>21</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2163,10 +2163,10 @@
         <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.69</v>
@@ -2184,7 +2184,7 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>23</v>
@@ -2229,10 +2229,10 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>5.3</v>
@@ -2253,13 +2253,13 @@
         <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW7" t="n">
         <v>5.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
         <v>7.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="H8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2441,7 +2441,7 @@
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2483,7 +2483,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2492,7 +2492,7 @@
         <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
         <v>4.2</v>
@@ -2501,7 +2501,7 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2513,13 +2513,13 @@
         <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY8" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
@@ -2528,46 +2528,46 @@
         <v>5.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BD8" t="n">
         <v>2.36</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.12</v>
+        <v>5.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BP8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>3.75</v>
@@ -2576,35 +2576,35 @@
         <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="BT8" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2635,31 +2635,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G9" t="n">
         <v>2.34</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
         <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
@@ -2668,22 +2668,22 @@
         <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
         <v>1.74</v>
@@ -2692,10 +2692,10 @@
         <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
         <v>290</v>
@@ -2704,10 +2704,10 @@
         <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>150</v>
@@ -2716,7 +2716,7 @@
         <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
@@ -2725,10 +2725,10 @@
         <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
         <v>50</v>
@@ -2737,19 +2737,19 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="AP9" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
         <v>8.800000000000001</v>
@@ -2758,16 +2758,16 @@
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="AX9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB9" t="n">
         <v>10.5</v>
@@ -2788,19 +2788,19 @@
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
         <v>12</v>
@@ -2815,31 +2815,31 @@
         <v>5.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS9" t="n">
         <v>5</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
         <v>3.45</v>
       </c>
       <c r="BV9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW9" t="n">
         <v>5.1</v>
@@ -2851,14 +2851,14 @@
         <v>5.3</v>
       </c>
       <c r="BZ9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA9" t="n">
         <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.34</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
         <v>3.2</v>
@@ -3173,28 +3173,28 @@
         <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
         <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
         <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
@@ -3305,7 +3305,7 @@
         <v>4.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI11" t="n">
         <v>2.68</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3332,13 +3332,13 @@
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR11" t="n">
         <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT11" t="n">
         <v>7.8</v>
@@ -3350,23 +3350,23 @@
         <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
         <v>480</v>
@@ -3511,7 +3511,7 @@
         <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
         <v>7.8</v>
@@ -3523,7 +3523,7 @@
         <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW12" t="n">
         <v>7.6</v>
@@ -3544,7 +3544,7 @@
         <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3651,100 +3651,100 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>17.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -3756,28 +3756,28 @@
         <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
         <v>13</v>
@@ -3789,31 +3789,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
         <v>3</v>
@@ -3822,49 +3822,49 @@
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL13" t="n">
         <v>120</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN13" t="n">
         <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV13" t="n">
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX13" t="n">
         <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q14" t="n">
         <v>1.43</v>
@@ -4037,7 +4037,7 @@
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY14" t="n">
         <v>14.5</v>
@@ -4052,7 +4052,7 @@
         <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
         <v>28</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.33</v>
@@ -4207,10 +4207,10 @@
         <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
         <v>19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>1.65</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
         <v>5.9</v>
@@ -4431,7 +4431,7 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
@@ -4512,7 +4512,7 @@
         <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>8.199999999999999</v>
@@ -4542,7 +4542,7 @@
         <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -4554,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>44</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
         <v>13</v>
@@ -4566,7 +4566,7 @@
         <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
         <v>5.2</v>
@@ -4679,7 +4679,7 @@
         <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
@@ -4688,43 +4688,43 @@
         <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
         <v>40</v>
@@ -4736,10 +4736,10 @@
         <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
         <v>75</v>
@@ -4751,52 +4751,52 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
         <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="AO17" t="n">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
         <v>7.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4805,28 +4805,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD17" t="n">
         <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="n">
         <v>3.3</v>
@@ -4844,53 +4844,53 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP17" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT17" t="n">
         <v>8.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW17" t="n">
         <v>12</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>29</v>
       </c>
       <c r="CA17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>3.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
         <v>3.9</v>
@@ -4969,13 +4969,13 @@
         <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
         <v>1.87</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4987,7 +4987,7 @@
         <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
@@ -4999,10 +4999,10 @@
         <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
@@ -5014,7 +5014,7 @@
         <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>38</v>
@@ -5038,13 +5038,13 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
         <v>13.5</v>
@@ -5068,19 +5068,19 @@
         <v>21</v>
       </c>
       <c r="BC18" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD18" t="n">
         <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BH18" t="n">
         <v>3.9</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5181,22 +5181,22 @@
         <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
         <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>4.4</v>
@@ -5205,37 +5205,37 @@
         <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
         <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y19" t="n">
         <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
         <v>120</v>
@@ -5268,7 +5268,7 @@
         <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
         <v>32</v>
@@ -5277,7 +5277,7 @@
         <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO19" t="n">
         <v>60</v>
@@ -5328,31 +5328,31 @@
         <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="n">
         <v>3.9</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
         <v>4.7</v>
@@ -5364,41 +5364,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR19" t="n">
         <v>25</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G20" t="n">
         <v>1.65</v>
@@ -5531,7 +5531,7 @@
         <v>390</v>
       </c>
       <c r="AN20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>85</v>
@@ -5546,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT20" t="n">
         <v>9</v>
@@ -5558,7 +5558,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5582,13 +5582,13 @@
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF20" t="n">
         <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5612,7 +5612,7 @@
         <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP20" t="n">
         <v>11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5707,10 +5707,10 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -5719,16 +5719,16 @@
         <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="S21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U21" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="V21" t="n">
         <v>2.38</v>
@@ -5737,19 +5737,19 @@
         <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
         <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
@@ -5767,16 +5767,16 @@
         <v>19.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ21" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL21" t="n">
         <v>44</v>
@@ -5785,10 +5785,10 @@
         <v>50</v>
       </c>
       <c r="AN21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AP21" t="n">
         <v>28</v>
@@ -5821,13 +5821,13 @@
         <v>18.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
       </c>
       <c r="BB21" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BC21" t="n">
         <v>42</v>
@@ -5836,19 +5836,19 @@
         <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF21" t="n">
         <v>32</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH21" t="n">
         <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ21" t="n">
         <v>9</v>
@@ -5857,10 +5857,10 @@
         <v>8</v>
       </c>
       <c r="BL21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN21" t="n">
         <v>8.800000000000001</v>
@@ -5872,16 +5872,16 @@
         <v>32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU21" t="n">
         <v>4.6</v>
@@ -5896,17 +5896,17 @@
         <v>19.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ21" t="n">
         <v>12</v>
       </c>
       <c r="CA21" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>3.05</v>
       </c>
       <c r="G22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H22" t="n">
         <v>2.82</v>
@@ -5961,7 +5961,7 @@
         <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
         <v>1.68</v>
@@ -5976,19 +5976,19 @@
         <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T22" t="n">
         <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
         <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X22" t="n">
         <v>6.6</v>
@@ -6021,7 +6021,7 @@
         <v>17</v>
       </c>
       <c r="AH22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI22" t="n">
         <v>120</v>
@@ -6051,7 +6051,7 @@
         <v>6.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS22" t="n">
         <v>46</v>
@@ -6066,7 +6066,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>16</v>
@@ -6075,7 +6075,7 @@
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
         <v>10.5</v>
@@ -6087,13 +6087,13 @@
         <v>16</v>
       </c>
       <c r="BD22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
         <v>18</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
@@ -6227,7 +6227,7 @@
         <v>1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
         <v>2.66</v>
@@ -6245,7 +6245,7 @@
         <v>2.04</v>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
@@ -6299,10 +6299,10 @@
         <v>36</v>
       </c>
       <c r="AP23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>19</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>18.5</v>
       </c>
       <c r="AR23" t="n">
         <v>30</v>
@@ -6329,7 +6329,7 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>40</v>
@@ -6341,7 +6341,7 @@
         <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE23" t="n">
         <v>55</v>
@@ -6368,7 +6368,7 @@
         <v>85</v>
       </c>
       <c r="BM23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN23" t="n">
         <v>5.1</v>
@@ -6380,13 +6380,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
         <v>7.6</v>
@@ -6398,7 +6398,7 @@
         <v>29</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX23" t="n">
         <v>34</v>
@@ -6407,14 +6407,14 @@
         <v>10</v>
       </c>
       <c r="BZ23" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6448,22 +6448,22 @@
         <v>1.27</v>
       </c>
       <c r="G24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
@@ -6475,7 +6475,7 @@
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q24" t="n">
         <v>1.66</v>
@@ -6487,124 +6487,124 @@
         <v>2.66</v>
       </c>
       <c r="T24" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>290</v>
+        <v>44</v>
       </c>
       <c r="Z24" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
         <v>55</v>
       </c>
       <c r="AE24" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI24" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AJ24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="AM24" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AP24" t="n">
         <v>19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
         <v>6.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>29</v>
       </c>
       <c r="BA24" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH24" t="n">
         <v>4.4</v>
@@ -6613,16 +6613,16 @@
         <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
         <v>3.7</v>
@@ -6631,7 +6631,7 @@
         <v>3.15</v>
       </c>
       <c r="BP24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BQ24" t="n">
         <v>5.7</v>
@@ -6640,35 +6640,35 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6702,13 +6702,13 @@
         <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H25" t="n">
         <v>3.65</v>
       </c>
       <c r="I25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>3.35</v>
@@ -6723,7 +6723,7 @@
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>1.47</v>
@@ -6735,7 +6735,7 @@
         <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
         <v>4.8</v>
@@ -6744,13 +6744,13 @@
         <v>2.02</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X25" t="n">
         <v>10.5</v>
@@ -6768,7 +6768,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>18.5</v>
@@ -6777,7 +6777,7 @@
         <v>290</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG25" t="n">
         <v>13.5</v>
@@ -6807,19 +6807,19 @@
         <v>500</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR25" t="n">
         <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU25" t="n">
         <v>6.8</v>
@@ -6828,7 +6828,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -6837,10 +6837,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB25" t="n">
         <v>14.5</v>
@@ -6849,16 +6849,16 @@
         <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>17</v>
+        <v>5.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH25" t="n">
         <v>3</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.17</v>
       </c>
       <c r="G26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>1.29</v>
@@ -6977,7 +6977,7 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.21</v>
@@ -6992,19 +6992,19 @@
         <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T26" t="n">
         <v>2.72</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="X26" t="n">
         <v>30</v>
@@ -7022,7 +7022,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD26" t="n">
         <v>950</v>
@@ -7040,22 +7040,22 @@
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AJ26" t="n">
         <v>8.6</v>
       </c>
       <c r="AK26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>85</v>
       </c>
       <c r="AM26" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -7067,10 +7067,10 @@
         <v>42</v>
       </c>
       <c r="AR26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -7079,22 +7079,22 @@
         <v>14</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
         <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
         <v>6.8</v>
@@ -7103,19 +7103,19 @@
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
         <v>3.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI26" t="n">
         <v>3.95</v>
@@ -7124,19 +7124,19 @@
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN26" t="n">
         <v>3.45</v>
       </c>
       <c r="BO26" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BP26" t="n">
         <v>6</v>
@@ -7148,35 +7148,35 @@
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>3.2</v>
@@ -7237,22 +7237,22 @@
         <v>1.6</v>
       </c>
       <c r="P27" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V27" t="n">
         <v>1.33</v>
@@ -7276,19 +7276,19 @@
         <v>7.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>19.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
         <v>15.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
         <v>32</v>
@@ -7315,19 +7315,19 @@
         <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
@@ -7336,37 +7336,37 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX27" t="n">
         <v>11</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH27" t="n">
         <v>3.05</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G28" t="n">
         <v>6.6</v>
@@ -7470,52 +7470,52 @@
         <v>1.63</v>
       </c>
       <c r="I28" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="J28" t="n">
         <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
         <v>8.6</v>
@@ -7548,31 +7548,31 @@
         <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AJ28" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AK28" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AL28" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AM28" t="n">
         <v>150</v>
       </c>
       <c r="AN28" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AO28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
         <v>8</v>
@@ -7581,22 +7581,22 @@
         <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AZ28" t="n">
         <v>19</v>
@@ -7611,7 +7611,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE28" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
         <v>9</v>
       </c>
       <c r="BH28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI28" t="n">
         <v>2.92</v>
@@ -7635,7 +7635,7 @@
         <v>4.2</v>
       </c>
       <c r="BL28" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="BM28" t="n">
         <v>6.2</v>
@@ -7647,16 +7647,16 @@
         <v>4</v>
       </c>
       <c r="BP28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR28" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BS28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT28" t="n">
         <v>4.5</v>
@@ -7677,14 +7677,14 @@
         <v>5.3</v>
       </c>
       <c r="BZ28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CA28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>1.99</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H29" t="n">
         <v>4.4</v>
@@ -7727,10 +7727,10 @@
         <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L29" t="n">
         <v>1.54</v>
@@ -7745,16 +7745,16 @@
         <v>1.56</v>
       </c>
       <c r="P29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T29" t="n">
         <v>2.24</v>
@@ -7766,7 +7766,7 @@
         <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
         <v>10</v>
@@ -7835,7 +7835,7 @@
         <v>8.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
@@ -7859,10 +7859,10 @@
         <v>8.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>44</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7972,13 +7972,13 @@
         <v>1.36</v>
       </c>
       <c r="G30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H30" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="I30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
         <v>5.3</v>
@@ -8002,10 +8002,10 @@
         <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S30" t="n">
         <v>2.7</v>
@@ -8020,7 +8020,7 @@
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -8080,7 +8080,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AR30" t="n">
         <v>4.8</v>
@@ -8089,7 +8089,7 @@
         <v>5</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU30" t="n">
         <v>10.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G2" t="n">
         <v>1.32</v>
@@ -866,16 +866,16 @@
         <v>11.5</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -884,25 +884,25 @@
         <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
@@ -917,10 +917,10 @@
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AA2" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -929,10 +929,10 @@
         <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>180</v>
       </c>
       <c r="AE2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF2" t="n">
         <v>9.800000000000001</v>
@@ -941,7 +941,7 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="n">
         <v>460</v>
@@ -962,7 +962,7 @@
         <v>3.95</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -974,22 +974,22 @@
         <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
         <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
         <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -1013,49 +1013,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU2" t="n">
         <v>7.4</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -1111,100 +1111,100 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.58</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1213,128 +1213,128 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.38</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.04</v>
+        <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.18</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.18</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.06</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.06</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.04</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.06</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.93</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.82</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>6.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="n">
         <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
@@ -1383,7 +1383,7 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1392,46 +1392,46 @@
         <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
@@ -1443,13 +1443,13 @@
         <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1458,34 +1458,34 @@
         <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
@@ -1506,7 +1506,7 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1521,10 +1521,10 @@
         <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.45</v>
@@ -1542,25 +1542,25 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
         <v>6</v>
@@ -1572,10 +1572,10 @@
         <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY4" t="n">
         <v>36</v>
@@ -1584,11 +1584,11 @@
         <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.26</v>
@@ -1643,7 +1643,7 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
@@ -1655,25 +1655,25 @@
         <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S5" t="n">
         <v>2.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
         <v>38</v>
@@ -1682,7 +1682,7 @@
         <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB5" t="n">
         <v>13</v>
@@ -1694,13 +1694,13 @@
         <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>19</v>
@@ -1718,7 +1718,7 @@
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
         <v>5.1</v>
@@ -1733,7 +1733,7 @@
         <v>30</v>
       </c>
       <c r="AR5" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AS5" t="n">
         <v>85</v>
@@ -1745,7 +1745,7 @@
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>34</v>
@@ -1754,16 +1754,16 @@
         <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
         <v>12.5</v>
@@ -1790,13 +1790,13 @@
         <v>9.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
@@ -1808,16 +1808,16 @@
         <v>9</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR5" t="n">
         <v>19.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU5" t="n">
         <v>6.2</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>11</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
         <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
         <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AO6" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>15</v>
       </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
         <v>55</v>
       </c>
       <c r="BC6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS6" t="n">
         <v>12.5</v>
       </c>
-      <c r="BN6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>10</v>
-      </c>
       <c r="BT6" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -2127,88 +2127,88 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
         <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
         <v>25</v>
@@ -2217,16 +2217,16 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>600</v>
@@ -2235,58 +2235,58 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="n">
         <v>4</v>
@@ -2307,37 +2307,37 @@
         <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
         <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
         <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY7" t="n">
         <v>1.04</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -2381,97 +2381,97 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
         <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH8" t="n">
         <v>500</v>
       </c>
-      <c r="AG8" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>950</v>
-      </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
         <v>500</v>
@@ -2480,131 +2480,131 @@
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>7</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="BA8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>7</v>
       </c>
-      <c r="AV8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT8" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -2635,46 +2635,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.6</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
         <v>1.84</v>
@@ -2683,52 +2683,52 @@
         <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>290</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AJ9" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>50</v>
@@ -2737,128 +2737,128 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AO9" t="n">
         <v>480</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW9" t="n">
         <v>38</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE9" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
       <c r="BF9" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO9" t="n">
         <v>4.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BV9" t="n">
         <v>42</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="G10" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2955,49 +2955,49 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>2.46</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>4.2</v>
@@ -3009,10 +3009,10 @@
         <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.07</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.07</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
         <v>4.2</v>
@@ -3021,98 +3021,98 @@
         <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.07</v>
+        <v>5.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="BA10" t="n">
         <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.07</v>
+        <v>8.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.07</v>
+        <v>2.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK10" t="n">
         <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM10" t="n">
         <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS10" t="n">
         <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU10" t="n">
         <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW10" t="n">
         <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY10" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -3161,58 +3161,58 @@
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
         <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
         <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>16.5</v>
@@ -3227,13 +3227,13 @@
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
         <v>32</v>
@@ -3245,7 +3245,7 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
         <v>48</v>
@@ -3260,7 +3260,7 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -3272,7 +3272,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,43 +3284,43 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>27</v>
       </c>
       <c r="BH11" t="n">
         <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3329,44 +3329,44 @@
         <v>4</v>
       </c>
       <c r="BP11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
         <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I12" t="n">
         <v>9.4</v>
@@ -3415,61 +3415,61 @@
         <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
         <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
         <v>220</v>
       </c>
       <c r="AA12" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE12" t="n">
         <v>480</v>
@@ -3478,149 +3478,149 @@
         <v>8.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>450</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AM12" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AV12" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
         <v>6.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK12" t="n">
         <v>1.04</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM12" t="n">
         <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS12" t="n">
         <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU12" t="n">
         <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW12" t="n">
         <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY12" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA12" t="n">
         <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -3651,97 +3651,97 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
         <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AB13" t="n">
         <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>500</v>
@@ -3753,103 +3753,103 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
         <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV13" t="n">
+      <c r="AZ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BL13" t="n">
         <v>120</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BN13" t="n">
         <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP13" t="n">
         <v>26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
         <v>4.4</v>
@@ -3858,13 +3858,13 @@
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
         <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -3905,55 +3905,55 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="S14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T14" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="W14" t="n">
         <v>1.1</v>
@@ -3962,19 +3962,19 @@
         <v>85</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
         <v>11.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AC14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD14" t="n">
         <v>11</v>
@@ -3986,7 +3986,7 @@
         <v>540</v>
       </c>
       <c r="AG14" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AH14" t="n">
         <v>40</v>
@@ -3995,13 +3995,13 @@
         <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="AK14" t="n">
         <v>480</v>
       </c>
       <c r="AL14" t="n">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AM14" t="n">
         <v>320</v>
@@ -4010,7 +4010,7 @@
         <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AP14" t="n">
         <v>17</v>
@@ -4022,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>16</v>
@@ -4037,7 +4037,7 @@
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>14.5</v>
@@ -4049,10 +4049,10 @@
         <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD14" t="n">
         <v>28</v>
@@ -4064,43 +4064,43 @@
         <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT14" t="n">
         <v>4.6</v>
@@ -4109,26 +4109,26 @@
         <v>3.35</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BW14" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BX14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA14" t="n">
         <v>4.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
@@ -4177,127 +4177,127 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
         <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
         <v>2.8</v>
       </c>
       <c r="T15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.62</v>
       </c>
-      <c r="U15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.55</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
         <v>95</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX15" t="n">
         <v>20</v>
       </c>
-      <c r="AP15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>18</v>
@@ -4306,55 +4306,55 @@
         <v>7.8</v>
       </c>
       <c r="BC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF15" t="n">
         <v>21</v>
       </c>
-      <c r="BD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK15" t="n">
         <v>3.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM15" t="n">
         <v>5.3</v>
       </c>
       <c r="BN15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP15" t="n">
         <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT15" t="n">
         <v>6.8</v>
@@ -4363,26 +4363,26 @@
         <v>4.7</v>
       </c>
       <c r="BV15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BW15" t="n">
         <v>4.4</v>
       </c>
       <c r="BX15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA15" t="n">
         <v>4.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
         <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>4.2</v>
@@ -4431,34 +4431,34 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
         <v>1.2</v>
@@ -4473,22 +4473,22 @@
         <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
         <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AF16" t="n">
         <v>12</v>
@@ -4497,10 +4497,10 @@
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ16" t="n">
         <v>17.5</v>
@@ -4509,16 +4509,16 @@
         <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP16" t="n">
         <v>19</v>
@@ -4527,10 +4527,10 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
@@ -4542,7 +4542,7 @@
         <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -4554,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
         <v>13</v>
@@ -4566,13 +4566,13 @@
         <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="n">
         <v>4.6</v>
@@ -4584,59 +4584,59 @@
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL16" t="n">
         <v>120</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BR16" t="n">
         <v>26</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA16" t="n">
         <v>4.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.75</v>
       </c>
-      <c r="K17" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
@@ -4694,25 +4694,25 @@
         <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
         <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>1.22</v>
@@ -4724,173 +4724,173 @@
         <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>85</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>300</v>
+        <v>85</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>7.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>14.5</v>
       </c>
-      <c r="BN17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW17" t="n">
+      <c r="BZ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA17" t="n">
         <v>12</v>
       </c>
-      <c r="BX17" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>29</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>10</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -4921,43 +4921,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.65</v>
       </c>
       <c r="K18" t="n">
         <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -4969,10 +4969,10 @@
         <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -4987,25 +4987,25 @@
         <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE18" t="n">
         <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
         <v>55</v>
@@ -5014,31 +5014,31 @@
         <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO18" t="n">
         <v>38</v>
       </c>
-      <c r="AM18" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>40</v>
-      </c>
       <c r="AP18" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR18" t="n">
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT18" t="n">
         <v>10</v>
@@ -5050,7 +5050,7 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -5062,7 +5062,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
@@ -5074,22 +5074,22 @@
         <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK18" t="n">
         <v>5.9</v>
@@ -5098,28 +5098,28 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU18" t="n">
         <v>5.4</v>
@@ -5137,14 +5137,14 @@
         <v>11.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -5175,178 +5175,178 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="S19" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="X19" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AH19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>19</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>17.5</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,50 +5355,50 @@
         <v>11</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BO19" t="n">
         <v>4</v>
       </c>
       <c r="BP19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ19" t="n">
         <v>6.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BS19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU19" t="n">
         <v>5</v>
       </c>
       <c r="BV19" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX19" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
         <v>4.3</v>
@@ -5447,43 +5447,43 @@
         <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
         <v>2.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
         <v>24</v>
@@ -5495,7 +5495,7 @@
         <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
@@ -5510,7 +5510,7 @@
         <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
@@ -5528,13 +5528,13 @@
         <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
@@ -5546,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
         <v>9</v>
@@ -5558,7 +5558,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5570,7 +5570,7 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>14</v>
@@ -5582,31 +5582,31 @@
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BF20" t="n">
         <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20" t="n">
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
@@ -5618,13 +5618,13 @@
         <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR20" t="n">
         <v>24</v>
       </c>
       <c r="BS20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT20" t="n">
         <v>9.800000000000001</v>
@@ -5636,23 +5636,23 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
         <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H21" t="n">
         <v>1.71</v>
@@ -5701,16 +5701,16 @@
         <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -5719,37 +5719,37 @@
         <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V21" t="n">
         <v>2.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB21" t="n">
         <v>29</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>28</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
@@ -5761,7 +5761,7 @@
         <v>14.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG21" t="n">
         <v>19.5</v>
@@ -5785,22 +5785,22 @@
         <v>50</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -5815,7 +5815,7 @@
         <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY21" t="n">
         <v>18.5</v>
@@ -5836,13 +5836,13 @@
         <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF21" t="n">
         <v>32</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH21" t="n">
         <v>4.9</v>
@@ -5851,13 +5851,13 @@
         <v>4.4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21" t="n">
         <v>8</v>
       </c>
       <c r="BL21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM21" t="n">
         <v>13</v>
@@ -5881,7 +5881,7 @@
         <v>11</v>
       </c>
       <c r="BT21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU21" t="n">
         <v>4.6</v>
@@ -5893,10 +5893,10 @@
         <v>9.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
         <v>12</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -5937,157 +5937,157 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="G22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K22" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="N22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.16</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB22" t="n">
         <v>8.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG22" t="n">
         <v>16</v>
       </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>17</v>
-      </c>
       <c r="AH22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK22" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="AM22" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>110</v>
       </c>
       <c r="AO22" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU22" t="n">
         <v>6.4</v>
       </c>
       <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA22" t="n">
         <v>11</v>
       </c>
-      <c r="AX22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC22" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB22" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>16</v>
-      </c>
       <c r="BD22" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE22" t="n">
         <v>12</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H23" t="n">
         <v>4.2</v>
@@ -6206,103 +6206,103 @@
         <v>3.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
         <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
         <v>17</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP23" t="n">
         <v>17.5</v>
       </c>
-      <c r="AL23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AR23" t="n">
         <v>30</v>
@@ -6311,28 +6311,28 @@
         <v>75</v>
       </c>
       <c r="AT23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV23" t="n">
         <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
@@ -6341,22 +6341,22 @@
         <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BF23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.199999999999999</v>
@@ -6365,28 +6365,28 @@
         <v>7.8</v>
       </c>
       <c r="BL23" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BM23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN23" t="n">
         <v>5.1</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP23" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT23" t="n">
         <v>7.6</v>
@@ -6395,26 +6395,26 @@
         <v>6.6</v>
       </c>
       <c r="BV23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -6451,46 +6451,46 @@
         <v>1.29</v>
       </c>
       <c r="H24" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
         <v>6.2</v>
       </c>
       <c r="K24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
@@ -6499,28 +6499,28 @@
         <v>4.4</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="Y24" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>820</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD24" t="n">
         <v>150</v>
       </c>
-      <c r="AA24" t="n">
-        <v>880</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>55</v>
-      </c>
       <c r="AE24" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AF24" t="n">
         <v>7.6</v>
@@ -6532,7 +6532,7 @@
         <v>38</v>
       </c>
       <c r="AI24" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ24" t="n">
         <v>9.6</v>
@@ -6544,25 +6544,25 @@
         <v>120</v>
       </c>
       <c r="AM24" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AN24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="AP24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ24" t="n">
         <v>36</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
         <v>7.8</v>
@@ -6574,7 +6574,7 @@
         <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX24" t="n">
         <v>6.8</v>
@@ -6583,13 +6583,13 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC24" t="n">
         <v>13</v>
@@ -6598,10 +6598,10 @@
         <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG24" t="n">
         <v>15</v>
@@ -6613,16 +6613,16 @@
         <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN24" t="n">
         <v>3.7</v>
@@ -6640,35 +6640,35 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BT24" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
         <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -6699,58 +6699,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
         <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
         <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X25" t="n">
         <v>10.5</v>
@@ -6759,7 +6759,7 @@
         <v>12.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -6768,28 +6768,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AF25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
         <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK25" t="n">
         <v>34</v>
@@ -6807,40 +6807,40 @@
         <v>500</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>6.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB25" t="n">
         <v>14.5</v>
@@ -6849,19 +6849,19 @@
         <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI25" t="n">
         <v>2.54</v>
@@ -6870,59 +6870,59 @@
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BN25" t="n">
         <v>5</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP25" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU25" t="n">
         <v>5.1</v>
       </c>
       <c r="BV25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G26" t="n">
         <v>1.21</v>
@@ -6962,49 +6962,49 @@
         <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T26" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
         <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X26" t="n">
         <v>30</v>
@@ -7013,7 +7013,7 @@
         <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
@@ -7034,16 +7034,16 @@
         <v>7.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH26" t="n">
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="AJ26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -7052,7 +7052,7 @@
         <v>85</v>
       </c>
       <c r="AM26" t="n">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="AN26" t="n">
         <v>3.95</v>
@@ -7073,25 +7073,25 @@
         <v>6.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW26" t="n">
         <v>6.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY26" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA26" t="n">
         <v>6.8</v>
@@ -7112,7 +7112,7 @@
         <v>3.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="n">
         <v>4.4</v>
@@ -7121,62 +7121,62 @@
         <v>3.95</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK26" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN26" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="BP26" t="n">
         <v>6</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BZ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -7198,239 +7198,239 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.26</v>
+        <v>5.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.28</v>
+        <v>6.4</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1.69</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.62</v>
+        <v>2.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.33</v>
+        <v>2.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.78</v>
+        <v>1.19</v>
       </c>
       <c r="X27" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL27" t="n">
         <v>110</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AM27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="n">
+      <c r="AR27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT27" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AU27" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AX27" t="n">
         <v>11</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ27" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BL27" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="BM27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BN27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY27" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP27" t="n">
+      <c r="BZ27" t="n">
         <v>25</v>
       </c>
-      <c r="BQ27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>60</v>
-      </c>
       <c r="CA27" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -7452,239 +7452,239 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR28" t="n">
         <v>5.8</v>
       </c>
-      <c r="G28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="AS28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ28" t="n">
         <v>4.2</v>
       </c>
-      <c r="K28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>170</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU28" t="n">
+      <c r="BR28" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT28" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>180</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>70</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR28" t="n">
+      <c r="BU28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BX28" t="n">
         <v>75</v>
       </c>
-      <c r="BS28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>30</v>
-      </c>
       <c r="BY28" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BZ28" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="CA28" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -7715,46 +7715,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
         <v>3.45</v>
       </c>
       <c r="L29" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="M29" t="n">
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O29" t="n">
         <v>1.56</v>
       </c>
       <c r="P29" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T29" t="n">
         <v>2.24</v>
@@ -7763,10 +7763,10 @@
         <v>1.67</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X29" t="n">
         <v>10</v>
@@ -7784,13 +7784,13 @@
         <v>6.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD29" t="n">
         <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF29" t="n">
         <v>11.5</v>
@@ -7799,13 +7799,13 @@
         <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI29" t="n">
         <v>130</v>
       </c>
       <c r="AJ29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK29" t="n">
         <v>32</v>
@@ -7817,7 +7817,7 @@
         <v>230</v>
       </c>
       <c r="AN29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO29" t="n">
         <v>150</v>
@@ -7829,10 +7829,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT29" t="n">
         <v>5.8</v>
@@ -7844,7 +7844,7 @@
         <v>17.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -7856,7 +7856,7 @@
         <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -7868,13 +7868,13 @@
         <v>44</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="n">
         <v>3.05</v>
@@ -7886,10 +7886,10 @@
         <v>13.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL29" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="BM29" t="n">
         <v>6</v>
@@ -7907,7 +7907,7 @@
         <v>4.7</v>
       </c>
       <c r="BR29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS29" t="n">
         <v>5.5</v>
@@ -7934,11 +7934,11 @@
         <v>50</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G30" t="n">
         <v>1.39</v>
@@ -7978,16 +7978,16 @@
         <v>10.5</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K30" t="n">
         <v>5.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
         <v>1.04</v>
@@ -7999,16 +7999,16 @@
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R30" t="n">
         <v>1.52</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T30" t="n">
         <v>2.02</v>
@@ -8017,10 +8017,10 @@
         <v>1.87</v>
       </c>
       <c r="V30" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -8035,7 +8035,7 @@
         <v>410</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
         <v>13.5</v>
@@ -8047,7 +8047,7 @@
         <v>180</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
@@ -8077,16 +8077,16 @@
         <v>250</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT30" t="n">
         <v>8.4</v>
@@ -8095,10 +8095,10 @@
         <v>10.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX30" t="n">
         <v>7.4</v>
@@ -8110,7 +8110,7 @@
         <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB30" t="n">
         <v>9.6</v>
@@ -8119,37 +8119,37 @@
         <v>13</v>
       </c>
       <c r="BD30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF30" t="n">
         <v>5</v>
       </c>
-      <c r="BE30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG30" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH30" t="n">
         <v>4.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ30" t="n">
         <v>14.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL30" t="n">
         <v>190</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO30" t="n">
         <v>3</v>
@@ -8161,38 +8161,38 @@
         <v>5.8</v>
       </c>
       <c r="BR30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT30" t="n">
         <v>16.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV30" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX30" t="n">
         <v>100</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ30" t="n">
         <v>15</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 00:00:41</t>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,61 +857,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Y2" t="n">
         <v>55</v>
@@ -920,28 +920,28 @@
         <v>160</v>
       </c>
       <c r="AA2" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD2" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AE2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
         <v>460</v>
@@ -950,31 +950,31 @@
         <v>12</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -986,101 +986,101 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
         <v>16.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1111,97 +1111,97 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G3" t="n">
         <v>3.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="H3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.58</v>
       </c>
-      <c r="I3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="R3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.55</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.59</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
         <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
         <v>22</v>
       </c>
-      <c r="AG3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21</v>
-      </c>
       <c r="AI3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>120</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>210</v>
       </c>
       <c r="AK3" t="n">
         <v>85</v>
@@ -1213,13 +1213,13 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>7.8</v>
@@ -1228,55 +1228,55 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>19</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="n">
         <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1288,19 +1288,19 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO3" t="n">
         <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,29 +1312,29 @@
         <v>5.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY3" t="n">
         <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1365,91 +1365,91 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U4" t="n">
         <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
         <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1467,10 +1467,10 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
@@ -1479,22 +1479,22 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1515,16 +1515,16 @@
         <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
         <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="n">
         <v>3.45</v>
@@ -1536,7 +1536,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1554,7 +1554,7 @@
         <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
@@ -1578,7 +1578,7 @@
         <v>38</v>
       </c>
       <c r="BY4" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>26</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
@@ -1643,49 +1643,49 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q5" t="n">
         <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
         <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
         <v>12.5</v>
@@ -1703,13 +1703,13 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
         <v>13.5</v>
@@ -1721,19 +1721,19 @@
         <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS5" t="n">
         <v>85</v>
@@ -1742,22 +1742,22 @@
         <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
         <v>50</v>
@@ -1790,13 +1790,13 @@
         <v>9.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
@@ -1808,22 +1808,22 @@
         <v>9</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW5" t="n">
         <v>12</v>
@@ -1832,17 +1832,17 @@
         <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>11</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="I6" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -1906,178 +1906,178 @@
         <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="n">
         <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG6" t="n">
         <v>18</v>
       </c>
-      <c r="AF6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>17</v>
       </c>
-      <c r="AH6" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AI6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ6" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
         <v>17</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BC6" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BD6" t="n">
         <v>42</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
         <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
@@ -2089,14 +2089,14 @@
         <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2127,97 +2127,97 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="H7" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I7" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
         <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
         <v>500</v>
       </c>
-      <c r="AF7" t="n">
-        <v>38</v>
-      </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>230</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -2232,125 +2232,125 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BB7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD7" t="n">
         <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BL7" t="n">
         <v>140</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BX7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2381,49 +2381,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
         <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
         <v>1.61</v>
@@ -2432,46 +2432,46 @@
         <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>500</v>
@@ -2480,131 +2480,131 @@
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.6</v>
       </c>
       <c r="AU8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7</v>
-      </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
         <v>7</v>
       </c>
       <c r="BG8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BT8" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX8" t="n">
         <v>140</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
         <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2662,13 +2662,13 @@
         <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
@@ -2677,10 +2677,10 @@
         <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
         <v>1.28</v>
@@ -2698,7 +2698,7 @@
         <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
         <v>9.199999999999999</v>
@@ -2707,31 +2707,31 @@
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>370</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
@@ -2740,43 +2740,43 @@
         <v>19.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX9" t="n">
         <v>11</v>
       </c>
-      <c r="AR9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BB9" t="n">
         <v>21</v>
@@ -2788,13 +2788,13 @@
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.5</v>
@@ -2806,13 +2806,13 @@
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL9" t="n">
         <v>160</v>
       </c>
       <c r="BM9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BN9" t="n">
         <v>5.2</v>
@@ -2824,41 +2824,41 @@
         <v>17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
         <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BZ9" t="n">
         <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2889,52 +2889,52 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
         <v>1.16</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I10" t="n">
         <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
@@ -2967,7 +2967,7 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2982,7 +2982,7 @@
         <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL10" t="n">
         <v>50</v>
@@ -2991,16 +2991,16 @@
         <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
         <v>4.2</v>
@@ -3009,110 +3009,110 @@
         <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW10" t="n">
         <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA10" t="n">
         <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BJ10" t="n">
         <v>17</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>950</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BV10" t="n">
         <v>180</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>120</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
@@ -3155,7 +3155,7 @@
         <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -3179,7 +3179,7 @@
         <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
         <v>3.7</v>
@@ -3194,7 +3194,7 @@
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
@@ -3206,13 +3206,13 @@
         <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>16.5</v>
@@ -3227,13 +3227,13 @@
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
         <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
         <v>32</v>
@@ -3287,16 +3287,16 @@
         <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3397,181 +3397,181 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.75</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
         <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
         <v>220</v>
       </c>
       <c r="AA12" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AB12" t="n">
         <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AE12" t="n">
         <v>480</v>
       </c>
       <c r="AF12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AI12" t="n">
         <v>450</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="AM12" t="n">
         <v>700</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="AZ12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BB12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>14</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>14.5</v>
       </c>
       <c r="BK12" t="n">
         <v>1.04</v>
       </c>
       <c r="BL12" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="BM12" t="n">
         <v>1.04</v>
@@ -3580,47 +3580,47 @@
         <v>4.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS12" t="n">
         <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU12" t="n">
         <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BW12" t="n">
         <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY12" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CA12" t="n">
         <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3651,220 +3651,220 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G13" t="n">
         <v>3.05</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.2</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.41</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.29</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
         <v>17.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AB13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
         <v>500</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>600</v>
       </c>
       <c r="AO13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE13" t="n">
         <v>55</v>
       </c>
-      <c r="AP13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="BF13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>10</v>
       </c>
-      <c r="AR13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BK13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL13" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BS13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
         <v>4.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BX13" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3905,43 +3905,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.32</v>
       </c>
-      <c r="I14" t="n">
-        <v>1.37</v>
-      </c>
       <c r="J14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="K14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
         <v>1.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S14" t="n">
         <v>2.04</v>
@@ -3950,127 +3950,127 @@
         <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AF14" t="n">
         <v>120</v>
       </c>
-      <c r="AC14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>540</v>
-      </c>
       <c r="AG14" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AH14" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AJ14" t="n">
         <v>350</v>
       </c>
       <c r="AK14" t="n">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="AL14" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AM14" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AP14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT14" t="n">
         <v>17</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AU14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV14" t="n">
         <v>9</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BE14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
         <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
@@ -4085,7 +4085,7 @@
         <v>7.2</v>
       </c>
       <c r="BN14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BO14" t="n">
         <v>4.9</v>
@@ -4094,7 +4094,7 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4109,26 +4109,26 @@
         <v>3.35</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX14" t="n">
         <v>20</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -4186,49 +4186,49 @@
         <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
         <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>12</v>
@@ -4240,13 +4240,13 @@
         <v>36</v>
       </c>
       <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH15" t="n">
-        <v>15</v>
-      </c>
       <c r="AI15" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
         <v>900</v>
@@ -4258,40 +4258,40 @@
         <v>95</v>
       </c>
       <c r="AM15" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
         <v>9.4</v>
       </c>
       <c r="AW15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX15" t="n">
         <v>13</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>12</v>
@@ -4300,89 +4300,89 @@
         <v>12</v>
       </c>
       <c r="BA15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB15" t="n">
         <v>18</v>
       </c>
-      <c r="BB15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BL15" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM15" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>21</v>
       </c>
-      <c r="BW15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>22</v>
-      </c>
       <c r="CA15" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G16" t="n">
         <v>1.7</v>
@@ -4422,7 +4422,7 @@
         <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
         <v>4.2</v>
@@ -4437,25 +4437,25 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
         <v>2.18</v>
@@ -4467,7 +4467,7 @@
         <v>2.42</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
         <v>25</v>
@@ -4494,7 +4494,7 @@
         <v>12</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -4506,7 +4506,7 @@
         <v>17.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>32</v>
@@ -4518,46 +4518,46 @@
         <v>8.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>19</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
         <v>17.5</v>
       </c>
-      <c r="AR16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>16</v>
-      </c>
       <c r="AW16" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
         <v>13.5</v>
@@ -4566,13 +4566,13 @@
         <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="n">
         <v>4.6</v>
@@ -4584,13 +4584,13 @@
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL16" t="n">
         <v>120</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
@@ -4599,7 +4599,7 @@
         <v>3.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ16" t="n">
         <v>3.85</v>
@@ -4608,25 +4608,25 @@
         <v>26</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV16" t="n">
         <v>48</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
         <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BZ16" t="n">
         <v>18.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4667,118 +4667,118 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G17" t="n">
         <v>1.91</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
         <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
         <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
         <v>85</v>
       </c>
       <c r="AM17" t="n">
-        <v>390</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>14</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>14.5</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -4787,25 +4787,25 @@
         <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY17" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
         <v>28</v>
@@ -4814,83 +4814,83 @@
         <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BF17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI17" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO17" t="n">
         <v>3.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS17" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA17" t="n">
         <v>13.5</v>
       </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>12</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.34</v>
@@ -4945,148 +4945,148 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
         <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BA18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF18" t="n">
         <v>12</v>
       </c>
-      <c r="AY18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>10</v>
-      </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>8.800000000000001</v>
@@ -5098,53 +5098,53 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP18" t="n">
         <v>15</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -5175,31 +5175,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.4</v>
       </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.21</v>
@@ -5208,133 +5208,133 @@
         <v>2.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S19" t="n">
         <v>2.58</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y19" t="n">
         <v>23</v>
       </c>
-      <c r="Y19" t="n">
-        <v>22</v>
-      </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL19" t="n">
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="AP19" t="n">
         <v>20</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX19" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12.5</v>
       </c>
       <c r="AY19" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
         <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BH19" t="n">
         <v>4.5</v>
@@ -5361,10 +5361,10 @@
         <v>4</v>
       </c>
       <c r="BP19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR19" t="n">
         <v>22</v>
@@ -5379,26 +5379,26 @@
         <v>5</v>
       </c>
       <c r="BV19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA19" t="n">
         <v>7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -5429,76 +5429,76 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.63</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.66</v>
-      </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA20" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
         <v>23</v>
@@ -5519,37 +5519,37 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL20" t="n">
         <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO20" t="n">
         <v>75</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
         <v>9.199999999999999</v>
@@ -5558,7 +5558,7 @@
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5567,92 +5567,92 @@
         <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
         <v>14</v>
       </c>
       <c r="BC20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG20" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>13</v>
-      </c>
       <c r="BH20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BJ20" t="n">
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BX20" t="n">
         <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BZ20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA20" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G21" t="n">
         <v>5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.1</v>
       </c>
       <c r="H21" t="n">
         <v>1.71</v>
@@ -5701,31 +5701,31 @@
         <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U21" t="n">
         <v>2.8</v>
@@ -5734,16 +5734,16 @@
         <v>2.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
         <v>19</v>
@@ -5761,7 +5761,7 @@
         <v>14.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG21" t="n">
         <v>19.5</v>
@@ -5776,31 +5776,31 @@
         <v>110</v>
       </c>
       <c r="AK21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
         <v>50</v>
       </c>
       <c r="AN21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO21" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AP21" t="n">
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -5836,16 +5836,16 @@
         <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF21" t="n">
         <v>32</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI21" t="n">
         <v>4.4</v>
@@ -5857,28 +5857,28 @@
         <v>8</v>
       </c>
       <c r="BL21" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BM21" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BN21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BP21" t="n">
         <v>32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BR21" t="n">
         <v>34</v>
       </c>
       <c r="BS21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT21" t="n">
         <v>5</v>
@@ -5896,17 +5896,17 @@
         <v>19</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>12</v>
       </c>
       <c r="CA21" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -5937,230 +5937,230 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G22" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H22" t="n">
         <v>2.8</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.47</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X22" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>60</v>
       </c>
-      <c r="AB22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>65</v>
-      </c>
       <c r="AK22" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AL22" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AN22" t="n">
         <v>110</v>
       </c>
       <c r="AO22" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR22" t="n">
         <v>14.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
         <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
         <v>15.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
       </c>
       <c r="BC22" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BG22" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>1.98</v>
       </c>
       <c r="H23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I23" t="n">
         <v>4.2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.3</v>
       </c>
       <c r="J23" t="n">
         <v>3.9</v>
@@ -6215,10 +6215,10 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P23" t="n">
         <v>2.24</v>
@@ -6233,13 +6233,13 @@
         <v>2.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
         <v>2.02</v>
@@ -6248,7 +6248,7 @@
         <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z23" t="n">
         <v>32</v>
@@ -6281,7 +6281,7 @@
         <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>18</v>
@@ -6290,19 +6290,19 @@
         <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="n">
         <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP23" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
         <v>30</v>
@@ -6335,10 +6335,10 @@
         <v>44</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD23" t="n">
         <v>27</v>
@@ -6350,71 +6350,71 @@
         <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH23" t="n">
         <v>3.8</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK23" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL23" t="n">
         <v>100</v>
       </c>
       <c r="BM23" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BO23" t="n">
         <v>4.5</v>
       </c>
       <c r="BP23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="BT23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV23" t="n">
         <v>32</v>
       </c>
       <c r="BW23" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BX23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY23" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BZ23" t="n">
         <v>20</v>
       </c>
       <c r="CA23" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
         <v>1.32</v>
@@ -6475,10 +6475,10 @@
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R24" t="n">
         <v>1.54</v>
@@ -6487,22 +6487,22 @@
         <v>2.72</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X24" t="n">
         <v>38</v>
       </c>
       <c r="Y24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z24" t="n">
         <v>160</v>
@@ -6514,70 +6514,70 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD24" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AE24" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AF24" t="n">
         <v>7.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
         <v>38</v>
       </c>
       <c r="AI24" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK24" t="n">
         <v>15.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AM24" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="n">
         <v>4.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>370</v>
+        <v>460</v>
       </c>
       <c r="AP24" t="n">
         <v>20</v>
       </c>
       <c r="AQ24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT24" t="n">
         <v>7.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV24" t="n">
         <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -6586,10 +6586,10 @@
         <v>30</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
         <v>13</v>
@@ -6598,31 +6598,31 @@
         <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG24" t="n">
         <v>15</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI24" t="n">
         <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN24" t="n">
         <v>3.7</v>
@@ -6631,7 +6631,7 @@
         <v>3.15</v>
       </c>
       <c r="BP24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ24" t="n">
         <v>5.7</v>
@@ -6640,35 +6640,35 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT24" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G25" t="n">
         <v>2.38</v>
@@ -6711,10 +6711,10 @@
         <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.51</v>
@@ -6729,7 +6729,7 @@
         <v>1.46</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
         <v>2.4</v>
@@ -6741,16 +6741,16 @@
         <v>4.7</v>
       </c>
       <c r="T25" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W25" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X25" t="n">
         <v>10.5</v>
@@ -6759,7 +6759,7 @@
         <v>12.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -6783,10 +6783,10 @@
         <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AJ25" t="n">
         <v>34</v>
@@ -6816,7 +6816,7 @@
         <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
         <v>7.2</v>
@@ -6828,7 +6828,7 @@
         <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -6837,10 +6837,10 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
         <v>14.5</v>
@@ -6849,22 +6849,22 @@
         <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH25" t="n">
         <v>2.94</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ25" t="n">
         <v>10.5</v>
@@ -6876,16 +6876,16 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN25" t="n">
         <v>5</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
         <v>9.6</v>
@@ -6894,7 +6894,7 @@
         <v>38</v>
       </c>
       <c r="BS25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT25" t="n">
         <v>6.6</v>
@@ -6906,23 +6906,23 @@
         <v>32</v>
       </c>
       <c r="BW25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
         <v>5.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.66</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.68</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
         <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X26" t="n">
         <v>30</v>
@@ -7022,7 +7022,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD26" t="n">
         <v>950</v>
@@ -7034,7 +7034,7 @@
         <v>7.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>950</v>
@@ -7055,7 +7055,7 @@
         <v>460</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -7067,10 +7067,10 @@
         <v>42</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT26" t="n">
         <v>7.4</v>
@@ -7079,10 +7079,10 @@
         <v>16</v>
       </c>
       <c r="AV26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW26" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
         <v>6.2</v>
@@ -7091,10 +7091,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA26" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
         <v>6.8</v>
@@ -7103,16 +7103,16 @@
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG26" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>7.2</v>
       </c>
       <c r="BH26" t="n">
         <v>4.4</v>
@@ -7121,16 +7121,16 @@
         <v>3.95</v>
       </c>
       <c r="BJ26" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN26" t="n">
         <v>3.4</v>
@@ -7139,7 +7139,7 @@
         <v>3.05</v>
       </c>
       <c r="BP26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BQ26" t="n">
         <v>4.6</v>
@@ -7154,29 +7154,29 @@
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BZ26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA26" t="n">
         <v>6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -7207,82 +7207,82 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G27" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H27" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R27" t="n">
         <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="W27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z27" t="n">
         <v>9</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AA27" t="n">
         <v>17</v>
       </c>
       <c r="AB27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
         <v>10.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF27" t="n">
         <v>46</v>
@@ -7291,7 +7291,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>40</v>
@@ -7303,49 +7303,49 @@
         <v>95</v>
       </c>
       <c r="AL27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM27" t="n">
         <v>150</v>
       </c>
       <c r="AN27" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AO27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU27" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
         <v>9.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY27" t="n">
         <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
         <v>32</v>
@@ -7354,22 +7354,22 @@
         <v>11.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI27" t="n">
         <v>2.92</v>
@@ -7378,59 +7378,59 @@
         <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL27" t="n">
         <v>180</v>
       </c>
       <c r="BM27" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BN27" t="n">
         <v>10.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP27" t="n">
         <v>65</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR27" t="n">
         <v>70</v>
       </c>
       <c r="BS27" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BT27" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BV27" t="n">
         <v>12.5</v>
       </c>
       <c r="BW27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY27" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>25</v>
       </c>
       <c r="CA27" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H28" t="n">
         <v>3.75</v>
@@ -7488,7 +7488,7 @@
         <v>2.62</v>
       </c>
       <c r="O28" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P28" t="n">
         <v>1.52</v>
@@ -7512,7 +7512,7 @@
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="X28" t="n">
         <v>9.800000000000001</v>
@@ -7530,7 +7530,7 @@
         <v>7.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
         <v>21</v>
@@ -7575,10 +7575,10 @@
         <v>8.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -7590,7 +7590,7 @@
         <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>11</v>
@@ -7599,28 +7599,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF28" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>6</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7635,7 +7635,7 @@
         <v>3.75</v>
       </c>
       <c r="BL28" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BM28" t="n">
         <v>5</v>
@@ -7644,7 +7644,7 @@
         <v>5.8</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP28" t="n">
         <v>25</v>
@@ -7656,7 +7656,7 @@
         <v>55</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT28" t="n">
         <v>8.199999999999999</v>
@@ -7677,14 +7677,14 @@
         <v>4.8</v>
       </c>
       <c r="BZ28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="CA28" t="n">
         <v>4.7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -7718,16 +7718,16 @@
         <v>2.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
         <v>3.45</v>
@@ -7739,37 +7739,37 @@
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
         <v>1.56</v>
       </c>
       <c r="P29" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R29" t="n">
         <v>1.19</v>
       </c>
       <c r="S29" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T29" t="n">
         <v>2.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V29" t="n">
         <v>1.26</v>
       </c>
       <c r="W29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
         <v>12</v>
@@ -7808,7 +7808,7 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL29" t="n">
         <v>75</v>
@@ -7832,7 +7832,7 @@
         <v>28</v>
       </c>
       <c r="AS29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
         <v>5.8</v>
@@ -7844,7 +7844,7 @@
         <v>17.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -7856,7 +7856,7 @@
         <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -7868,13 +7868,13 @@
         <v>44</v>
       </c>
       <c r="BE29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG29" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>9</v>
       </c>
       <c r="BH29" t="n">
         <v>3.05</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G30" t="n">
         <v>1.39</v>
@@ -7996,7 +7996,7 @@
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
         <v>2.36</v>
@@ -8014,7 +8014,7 @@
         <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
         <v>1.1</v>
@@ -8077,7 +8077,7 @@
         <v>250</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AQ30" t="n">
         <v>5.2</v>
@@ -8119,7 +8119,7 @@
         <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE30" t="n">
         <v>5.6</v>
@@ -8140,13 +8140,13 @@
         <v>14.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL30" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN30" t="n">
         <v>4.4</v>
@@ -8158,31 +8158,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ30" t="n">
-        <v>5.8</v>
+        <v>3.25</v>
       </c>
       <c r="BR30" t="n">
         <v>28</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV30" t="n">
         <v>110</v>
       </c>
       <c r="BW30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ30" t="n">
         <v>15</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-19.xlsx
@@ -857,28 +857,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
         <v>7.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>6.8</v>
@@ -896,10 +896,10 @@
         <v>1.81</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -908,109 +908,109 @@
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X2" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="AA2" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AE2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
       <c r="AH2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
         <v>460</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
         <v>3.4</v>
@@ -1028,59 +1028,59 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -1129,52 +1129,52 @@
         <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="n">
         <v>9.4</v>
@@ -1186,155 +1186,155 @@
         <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
         <v>500</v>
       </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>600</v>
-      </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
         <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="BE3" t="n">
         <v>30</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT3" t="n">
         <v>5.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BZ3" t="n">
         <v>50</v>
       </c>
       <c r="CA3" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="I4" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1383,40 +1383,40 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
         <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
         <v>15.5</v>
@@ -1425,10 +1425,10 @@
         <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
@@ -1440,16 +1440,16 @@
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1458,7 +1458,7 @@
         <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
@@ -1467,22 +1467,22 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1491,13 +1491,13 @@
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
@@ -1509,86 +1509,86 @@
         <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
         <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="n">
         <v>3.45</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BN4" t="n">
         <v>5.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4" t="n">
         <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="X5" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y5" t="n">
         <v>32</v>
       </c>
-      <c r="Y5" t="n">
-        <v>36</v>
-      </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
         <v>13.5</v>
       </c>
       <c r="AC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF5" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL5" t="n">
         <v>25</v>
       </c>
       <c r="AM5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS5" t="n">
         <v>75</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>85</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
         <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH5" t="n">
         <v>4.8</v>
       </c>
-      <c r="BG5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL5" t="n">
         <v>80</v>
       </c>
       <c r="BM5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BW5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>12</v>
       </c>
-      <c r="BX5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>11</v>
-      </c>
       <c r="CA5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.81</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.85</v>
       </c>
       <c r="J6" t="n">
         <v>4.1</v>
@@ -1897,64 +1897,64 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB6" t="n">
         <v>20</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
         <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
@@ -1966,43 +1966,43 @@
         <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
         <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
       </c>
       <c r="AS6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT6" t="n">
         <v>18</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>17</v>
       </c>
       <c r="AU6" t="n">
         <v>8.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
         <v>32</v>
@@ -2014,25 +2014,25 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BC6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BD6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE6" t="n">
         <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.9</v>
@@ -2041,62 +2041,62 @@
         <v>3.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR6" t="n">
         <v>40</v>
       </c>
       <c r="BS6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU6" t="n">
         <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>17.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2127,82 +2127,82 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.4</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB7" t="n">
         <v>23</v>
       </c>
-      <c r="AA7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
         <v>500</v>
@@ -2232,31 +2232,31 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -2274,25 +2274,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH7" t="n">
         <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
@@ -2304,53 +2304,53 @@
         <v>140</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BS7" t="n">
         <v>4.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BX7" t="n">
         <v>36</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>30</v>
       </c>
       <c r="CA7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
         <v>1.45</v>
@@ -2396,43 +2396,43 @@
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
         <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2447,19 +2447,19 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AG8" t="n">
         <v>36</v>
@@ -2468,13 +2468,13 @@
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ8" t="n">
         <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,34 +2483,34 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>23</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>6.4</v>
@@ -2519,92 +2519,92 @@
         <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>7.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>280</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP8" t="n">
         <v>9</v>
       </c>
-      <c r="BF8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>290</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BQ8" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
         <v>32</v>
       </c>
       <c 